--- a/lista_emails.xlsx
+++ b/lista_emails.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Y:\Wagner\Programações\RH\Questionário ENIND\App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8183F8F7-4853-44B9-BC14-974583621962}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB36BA9E-2B3F-489B-B58E-12AA809DE702}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4ABFC600-D865-440E-A0ED-FE29CA4E2163}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Planilha2" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha2!$A$1:$L$284</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha2!$A$1:$L$398</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,30 +38,8 @@
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3388" uniqueCount="437">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4756" uniqueCount="586">
   <si>
     <t>Participante</t>
   </si>
@@ -1372,6 +1350,453 @@
   </si>
   <si>
     <t>antonio.santos@enind.com.br</t>
+  </si>
+  <si>
+    <t>Alexandre Armelin</t>
+  </si>
+  <si>
+    <t>Amanda Nunes Paixao</t>
+  </si>
+  <si>
+    <t>Amanda Silva Costa Oliveira</t>
+  </si>
+  <si>
+    <t>Andre dos Santos Eusebio</t>
+  </si>
+  <si>
+    <t>Andre Luiz do Nascimento</t>
+  </si>
+  <si>
+    <t>Antonio Aloisio Ferreira dos Santos Filho</t>
+  </si>
+  <si>
+    <t>Antonio Luis Ribeiro de Almeida Junior</t>
+  </si>
+  <si>
+    <t>Augusto Cesar Nogueira Junqueira</t>
+  </si>
+  <si>
+    <t>Brendhel Almeida Silva</t>
+  </si>
+  <si>
+    <t>Bruno Pulino Lustosa</t>
+  </si>
+  <si>
+    <t>Cleiton Inacio Mathias</t>
+  </si>
+  <si>
+    <t>Daniel Casari Carlos</t>
+  </si>
+  <si>
+    <t>Jorge Antonio Ferreira da Mota</t>
+  </si>
+  <si>
+    <t>Eder da Silva Fernandes</t>
+  </si>
+  <si>
+    <t>Emerson Marcelo Alves da Cunha de Leo</t>
+  </si>
+  <si>
+    <t>Igor do Carmo Aranda</t>
+  </si>
+  <si>
+    <t>Ieza Amaral</t>
+  </si>
+  <si>
+    <t>Joao Pedro Faleco Rodrigues</t>
+  </si>
+  <si>
+    <t>Luciene Caetano da Rocha</t>
+  </si>
+  <si>
+    <t>Jose Martins Filho</t>
+  </si>
+  <si>
+    <t>Leandro Cabrini</t>
+  </si>
+  <si>
+    <t>Luan Henrique Alves de Carvalho</t>
+  </si>
+  <si>
+    <t>Marcelo da Silva Santos</t>
+  </si>
+  <si>
+    <t>Isabela Pinheiro da Silva</t>
+  </si>
+  <si>
+    <t>Marcos Alberto Ferreira Junior</t>
+  </si>
+  <si>
+    <t>Marcos Souza Queiroz</t>
+  </si>
+  <si>
+    <t>Mariana Gouvea da Silva Moreira</t>
+  </si>
+  <si>
+    <t>Matheus Ruan de Jesus Silva</t>
+  </si>
+  <si>
+    <t>Milena Alkmin</t>
+  </si>
+  <si>
+    <t>Natalia Gomes Dos Santos</t>
+  </si>
+  <si>
+    <t>Nicholas Rezende</t>
+  </si>
+  <si>
+    <t>Rebeca Oliveira Porto</t>
+  </si>
+  <si>
+    <t>Marcia Cristina Silva Santana</t>
+  </si>
+  <si>
+    <t>Ruan Filipe Amaral Ramos</t>
+  </si>
+  <si>
+    <t>Sergio Reis Porto</t>
+  </si>
+  <si>
+    <t>Thais Sousa de Oliveira</t>
+  </si>
+  <si>
+    <t>Vinicius Araujo da Silva</t>
+  </si>
+  <si>
+    <t>Wagner Araujo Sequeira Barreiro</t>
+  </si>
+  <si>
+    <t>alexandre.armelin@enind.com.br</t>
+  </si>
+  <si>
+    <t>amanda.paixao@enind.com.br</t>
+  </si>
+  <si>
+    <t>amanda.oliveira@enind.com.br</t>
+  </si>
+  <si>
+    <t>andre.eusebio@enind.com.br</t>
+  </si>
+  <si>
+    <t>andre.nascimento@enind.com.br</t>
+  </si>
+  <si>
+    <t>antonio.almeida@enind.com.br</t>
+  </si>
+  <si>
+    <t>augusto.junqueira@enind.com.br</t>
+  </si>
+  <si>
+    <t>brendhel.silva@enind.com.br</t>
+  </si>
+  <si>
+    <t>bruno.lustosa@enind.com.br</t>
+  </si>
+  <si>
+    <t>cleiton.mathias@enind.com.br</t>
+  </si>
+  <si>
+    <t>daniel.casari@enind.com.br</t>
+  </si>
+  <si>
+    <t>jorge.mota@enind.com.br</t>
+  </si>
+  <si>
+    <t>eder.fernandes@enind.com.br</t>
+  </si>
+  <si>
+    <t>emerson.leo@enind.com.br</t>
+  </si>
+  <si>
+    <t>igor.aranda@enind.com.br</t>
+  </si>
+  <si>
+    <t>ieza.amaral@enind.com.br</t>
+  </si>
+  <si>
+    <t>joao.rodrigues@enind.com.br</t>
+  </si>
+  <si>
+    <t>luciene.rocha@enind.com.br</t>
+  </si>
+  <si>
+    <t>jose.filho@enind.com.br</t>
+  </si>
+  <si>
+    <t>leandro.cabrini@enind.com.br</t>
+  </si>
+  <si>
+    <t>luan.carvalho@enind.com.br</t>
+  </si>
+  <si>
+    <t>marcelo.santos@enind.com.br</t>
+  </si>
+  <si>
+    <t>isabela.pinheiro@enind.com.br</t>
+  </si>
+  <si>
+    <t>marcos.junior@enind.com.br</t>
+  </si>
+  <si>
+    <t>marcos.queiroz@enind.com.br</t>
+  </si>
+  <si>
+    <t>mariana.moreira@enind.com.br</t>
+  </si>
+  <si>
+    <t>matheus.silva@enind.com.br</t>
+  </si>
+  <si>
+    <t>milena.alkmin@enind.com.br</t>
+  </si>
+  <si>
+    <t>natalia.santos@enind.com.br</t>
+  </si>
+  <si>
+    <t>nicholas.rezende@enind.com.br</t>
+  </si>
+  <si>
+    <t>rebeca.porto@enind.com.br</t>
+  </si>
+  <si>
+    <t>marcia.santana@enind.com.br</t>
+  </si>
+  <si>
+    <t>ruan.ramos@enind.com.br</t>
+  </si>
+  <si>
+    <t>sergio.porto@enind.com.br</t>
+  </si>
+  <si>
+    <t>thais.oliveira@enind.com.br</t>
+  </si>
+  <si>
+    <t>wagner.barreiro@enind.com.br</t>
+  </si>
+  <si>
+    <t>alexandre.armelin</t>
+  </si>
+  <si>
+    <t>amanda.paixao</t>
+  </si>
+  <si>
+    <t>amanda.oliveira</t>
+  </si>
+  <si>
+    <t>andre.eusebio</t>
+  </si>
+  <si>
+    <t>andre.nascimento</t>
+  </si>
+  <si>
+    <t>antonio.santos</t>
+  </si>
+  <si>
+    <t>antonio.almeida</t>
+  </si>
+  <si>
+    <t>augusto.junqueira</t>
+  </si>
+  <si>
+    <t>brendhel.silva</t>
+  </si>
+  <si>
+    <t>bruno.lustosa</t>
+  </si>
+  <si>
+    <t>cleiton.mathias</t>
+  </si>
+  <si>
+    <t>daniel.casari</t>
+  </si>
+  <si>
+    <t>jorge.mota</t>
+  </si>
+  <si>
+    <t>eder.fernandes</t>
+  </si>
+  <si>
+    <t>emerson.leo</t>
+  </si>
+  <si>
+    <t>igor.aranda</t>
+  </si>
+  <si>
+    <t>ieza.amaral</t>
+  </si>
+  <si>
+    <t>joao.rodrigues</t>
+  </si>
+  <si>
+    <t>luciene.rocha</t>
+  </si>
+  <si>
+    <t>jose.filho</t>
+  </si>
+  <si>
+    <t>leandro.cabrini</t>
+  </si>
+  <si>
+    <t>luan.carvalho</t>
+  </si>
+  <si>
+    <t>marcelo.santos</t>
+  </si>
+  <si>
+    <t>isabela.pinheiro</t>
+  </si>
+  <si>
+    <t>marcos.junior</t>
+  </si>
+  <si>
+    <t>marcos.queiroz</t>
+  </si>
+  <si>
+    <t>mariana.moreira</t>
+  </si>
+  <si>
+    <t>matheus.silva</t>
+  </si>
+  <si>
+    <t>milena.alkmin</t>
+  </si>
+  <si>
+    <t>natalia.santos</t>
+  </si>
+  <si>
+    <t>nicholas.rezende</t>
+  </si>
+  <si>
+    <t>rebeca.porto</t>
+  </si>
+  <si>
+    <t>marcia.santana</t>
+  </si>
+  <si>
+    <t>ruan.ramos</t>
+  </si>
+  <si>
+    <t>sergio.porto</t>
+  </si>
+  <si>
+    <t>thais.oliveira</t>
+  </si>
+  <si>
+    <t>wagner.barreiro</t>
+  </si>
+  <si>
+    <t>376aa!@</t>
+  </si>
+  <si>
+    <t>364ap!@</t>
+  </si>
+  <si>
+    <t>625ao!@</t>
+  </si>
+  <si>
+    <t>333ae!@</t>
+  </si>
+  <si>
+    <t>044an!@</t>
+  </si>
+  <si>
+    <t>600as!@</t>
+  </si>
+  <si>
+    <t>183aa!@</t>
+  </si>
+  <si>
+    <t>348aj!@</t>
+  </si>
+  <si>
+    <t>917bs!@</t>
+  </si>
+  <si>
+    <t>884bl!@</t>
+  </si>
+  <si>
+    <t>519cm!@</t>
+  </si>
+  <si>
+    <t>643dc!@</t>
+  </si>
+  <si>
+    <t>493jm!@</t>
+  </si>
+  <si>
+    <t>531ef!@</t>
+  </si>
+  <si>
+    <t>525el!@</t>
+  </si>
+  <si>
+    <t>335ia!@</t>
+  </si>
+  <si>
+    <t>670ia!@</t>
+  </si>
+  <si>
+    <t>716jr!@</t>
+  </si>
+  <si>
+    <t>661lr!@</t>
+  </si>
+  <si>
+    <t>076jf!@</t>
+  </si>
+  <si>
+    <t>043lc!@</t>
+  </si>
+  <si>
+    <t>820lc!@</t>
+  </si>
+  <si>
+    <t>930ms!@</t>
+  </si>
+  <si>
+    <t>286ip!@</t>
+  </si>
+  <si>
+    <t>664mj!@</t>
+  </si>
+  <si>
+    <t>398mq!@</t>
+  </si>
+  <si>
+    <t>543mm!@</t>
+  </si>
+  <si>
+    <t>191ms!@</t>
+  </si>
+  <si>
+    <t>555ma!@</t>
+  </si>
+  <si>
+    <t>509ns!@</t>
+  </si>
+  <si>
+    <t>710nr!@</t>
+  </si>
+  <si>
+    <t>001rp!@</t>
+  </si>
+  <si>
+    <t>634ms!@</t>
+  </si>
+  <si>
+    <t>106rr!@</t>
+  </si>
+  <si>
+    <t>647sp!@</t>
+  </si>
+  <si>
+    <t>677to!@</t>
+  </si>
+  <si>
+    <t>624vs!@</t>
+  </si>
+  <si>
+    <t>425wb!@</t>
   </si>
 </sst>
 </file>
@@ -1492,11 +1917,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F3ADC3C7-E9A3-417B-9D36-7AAC353CADC8}" name="Tabela1" displayName="Tabela1" ref="A1:L284" totalsRowShown="0">
-  <autoFilter ref="A1:L284" xr:uid="{F3ADC3C7-E9A3-417B-9D36-7AAC353CADC8}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L284">
-    <sortCondition ref="K1:K284"/>
-  </sortState>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F3ADC3C7-E9A3-417B-9D36-7AAC353CADC8}" name="Tabela1" displayName="Tabela1" ref="A1:L398" totalsRowShown="0">
+  <autoFilter ref="A1:L398" xr:uid="{F3ADC3C7-E9A3-417B-9D36-7AAC353CADC8}"/>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{1EE8BBD9-CC9C-488B-9D75-6363CD6C86F1}" name="Participante"/>
     <tableColumn id="2" xr3:uid="{D83259D8-309A-419C-B320-342D6BCF6C73}" name="Avaliador"/>
@@ -1832,7 +2254,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCA9C2C1-2B6C-4947-A048-82C1CA408DE6}">
-  <dimension ref="A1:P284"/>
+  <sheetPr codeName="Planilha1"/>
+  <dimension ref="A1:L398"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="37.5703125" bestFit="1" customWidth="1"/>
@@ -1847,7 +2270,7 @@
     <col min="12" max="12" width="10.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1885,7 +2308,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
@@ -1923,7 +2346,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
@@ -1960,12 +2383,8 @@
       <c r="L3" t="s">
         <v>429</v>
       </c>
-      <c r="P3" t="str" cm="1">
-        <f t="array" ref="P3:P74">_xlfn.UNIQUE(Tabela1[email_repres])</f>
-        <v>adenilson.castro@enind.com.br</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>15</v>
       </c>
@@ -2002,11 +2421,8 @@
       <c r="L4" t="s">
         <v>429</v>
       </c>
-      <c r="P4" t="str">
-        <v>alessandra.tambellini@enind.com.br</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>24</v>
       </c>
@@ -2043,11 +2459,8 @@
       <c r="L5" t="s">
         <v>428</v>
       </c>
-      <c r="P5" t="str">
-        <v>alexandro.araujo@enind.com.br</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>33</v>
       </c>
@@ -2084,11 +2497,8 @@
       <c r="L6" t="s">
         <v>428</v>
       </c>
-      <c r="P6" t="str">
-        <v>anderson.domingues@enind.com.br</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>40</v>
       </c>
@@ -2125,11 +2535,8 @@
       <c r="L7" t="s">
         <v>428</v>
       </c>
-      <c r="P7" t="str">
-        <v>antonio.santos@enind.com.br</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>207</v>
       </c>
@@ -2166,11 +2573,8 @@
       <c r="L8" t="s">
         <v>428</v>
       </c>
-      <c r="P8" t="str">
-        <v>augusto.freitas@enind.com.br</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>273</v>
       </c>
@@ -2207,11 +2611,8 @@
       <c r="L9" t="s">
         <v>428</v>
       </c>
-      <c r="P9" t="str">
-        <v>bruno.castro@enind.com.br</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>334</v>
       </c>
@@ -2248,11 +2649,8 @@
       <c r="L10" t="s">
         <v>428</v>
       </c>
-      <c r="P10" t="str">
-        <v>crislane.gama@enind.com.br</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>352</v>
       </c>
@@ -2289,11 +2687,8 @@
       <c r="L11" t="s">
         <v>428</v>
       </c>
-      <c r="P11" t="str">
-        <v>dayvis.coelho@enind.com.br</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>392</v>
       </c>
@@ -2330,11 +2725,8 @@
       <c r="L12" t="s">
         <v>428</v>
       </c>
-      <c r="P12" t="str">
-        <v>dayvson.silva@enind.com.br</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>47</v>
       </c>
@@ -2371,11 +2763,8 @@
       <c r="L13" t="s">
         <v>430</v>
       </c>
-      <c r="P13" t="str">
-        <v>diego.araujo@enind.com.br</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>53</v>
       </c>
@@ -2412,11 +2801,8 @@
       <c r="L14" t="s">
         <v>430</v>
       </c>
-      <c r="P14" t="str">
-        <v>diego.santos@enind.com.br</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>59</v>
       </c>
@@ -2453,11 +2839,8 @@
       <c r="L15" t="s">
         <v>428</v>
       </c>
-      <c r="P15" t="str">
-        <v>dionisio.junior@enind.com.br</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>66</v>
       </c>
@@ -2494,11 +2877,8 @@
       <c r="L16" t="s">
         <v>430</v>
       </c>
-      <c r="P16" t="str">
-        <v>ediberto.pescaroli@enindservicos.com.br</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>72</v>
       </c>
@@ -2535,11 +2915,8 @@
       <c r="L17" t="s">
         <v>430</v>
       </c>
-      <c r="P17" t="str">
-        <v>eliza.moreira@enind.com.br</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>77</v>
       </c>
@@ -2576,11 +2953,8 @@
       <c r="L18" t="s">
         <v>430</v>
       </c>
-      <c r="P18" t="str">
-        <v>ellian.nunes@enind.com.br</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>80</v>
       </c>
@@ -2617,11 +2991,8 @@
       <c r="L19" t="s">
         <v>428</v>
       </c>
-      <c r="P19" t="str">
-        <v>emerson.bonotto@enind.com.br</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>84</v>
       </c>
@@ -2658,11 +3029,8 @@
       <c r="L20" t="s">
         <v>428</v>
       </c>
-      <c r="P20" t="str">
-        <v>evandro.idalgo@enind.com.br</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>31</v>
       </c>
@@ -2699,11 +3067,8 @@
       <c r="L21" t="s">
         <v>429</v>
       </c>
-      <c r="P21" t="str">
-        <v>everaldo.pontes@enind.com.br</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>133</v>
       </c>
@@ -2740,11 +3105,8 @@
       <c r="L22" t="s">
         <v>429</v>
       </c>
-      <c r="P22" t="str">
-        <v>everaldo.silva@enind.com.br</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>90</v>
       </c>
@@ -2781,11 +3143,8 @@
       <c r="L23" t="s">
         <v>430</v>
       </c>
-      <c r="P23" t="str">
-        <v>everton.bitencourt@enind.com.br</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>97</v>
       </c>
@@ -2822,11 +3181,8 @@
       <c r="L24" t="s">
         <v>430</v>
       </c>
-      <c r="P24" t="str">
-        <v>fabiano.sousa@enind.com.br</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>109</v>
       </c>
@@ -2863,11 +3219,8 @@
       <c r="L25" t="s">
         <v>429</v>
       </c>
-      <c r="P25" t="str">
-        <v>fabio.carelli@enind.com.br</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>102</v>
       </c>
@@ -2904,11 +3257,8 @@
       <c r="L26" t="s">
         <v>429</v>
       </c>
-      <c r="P26" t="str">
-        <v>fabricio.bruschi@enind.com.br</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>106</v>
       </c>
@@ -2945,11 +3295,8 @@
       <c r="L27" t="s">
         <v>429</v>
       </c>
-      <c r="P27" t="str">
-        <v>fernando.correa@enind.com.br</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>31</v>
       </c>
@@ -2986,11 +3333,8 @@
       <c r="L28" t="s">
         <v>429</v>
       </c>
-      <c r="P28" t="str">
-        <v>gabriela.lima@enind.com.br</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>115</v>
       </c>
@@ -3027,11 +3371,8 @@
       <c r="L29" t="s">
         <v>428</v>
       </c>
-      <c r="P29" t="str">
-        <v>glaucia.pontes@enind.com.br</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>46</v>
       </c>
@@ -3068,11 +3409,8 @@
       <c r="L30" t="s">
         <v>430</v>
       </c>
-      <c r="P30" t="str">
-        <v>guilherme.luis@enind.com.br</v>
-      </c>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>45</v>
       </c>
@@ -3109,11 +3447,8 @@
       <c r="L31" t="s">
         <v>428</v>
       </c>
-      <c r="P31" t="str">
-        <v>guilherme.silva@enind.com.br</v>
-      </c>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>125</v>
       </c>
@@ -3150,11 +3485,8 @@
       <c r="L32" t="s">
         <v>428</v>
       </c>
-      <c r="P32" t="str">
-        <v>hillary.karen@enind.com.br</v>
-      </c>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>128</v>
       </c>
@@ -3191,11 +3523,8 @@
       <c r="L33" t="s">
         <v>428</v>
       </c>
-      <c r="P33" t="str">
-        <v>hilton.torres@enind.com.br</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>70</v>
       </c>
@@ -3232,11 +3561,8 @@
       <c r="L34" t="s">
         <v>428</v>
       </c>
-      <c r="P34" t="str">
-        <v>italo.andrade@enind.com.br</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>133</v>
       </c>
@@ -3273,11 +3599,8 @@
       <c r="L35" t="s">
         <v>429</v>
       </c>
-      <c r="P35" t="str">
-        <v>janderson.alves@enindservicos.com.br</v>
-      </c>
-    </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>136</v>
       </c>
@@ -3314,11 +3637,8 @@
       <c r="L36" t="s">
         <v>428</v>
       </c>
-      <c r="P36" t="str">
-        <v>jean.rocha@enind.com.br</v>
-      </c>
-    </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>39</v>
       </c>
@@ -3355,11 +3675,8 @@
       <c r="L37" t="s">
         <v>429</v>
       </c>
-      <c r="P37" t="str">
-        <v>joão.fernandes@enind.com.br</v>
-      </c>
-    </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>207</v>
       </c>
@@ -3396,11 +3713,8 @@
       <c r="L38" t="s">
         <v>428</v>
       </c>
-      <c r="P38" t="str">
-        <v>joaquim.souza@enind.com.br</v>
-      </c>
-    </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>334</v>
       </c>
@@ -3437,11 +3751,8 @@
       <c r="L39" t="s">
         <v>428</v>
       </c>
-      <c r="P39" t="str">
-        <v>jose.alves@enind.com.br</v>
-      </c>
-    </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>19</v>
       </c>
@@ -3478,11 +3789,8 @@
       <c r="L40" t="s">
         <v>430</v>
       </c>
-      <c r="P40" t="str">
-        <v>juliana.melo@enind.com.br</v>
-      </c>
-    </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>18</v>
       </c>
@@ -3519,11 +3827,8 @@
       <c r="L41" t="s">
         <v>429</v>
       </c>
-      <c r="P41" t="str">
-        <v>juliana.santos@enind.com.br</v>
-      </c>
-    </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>144</v>
       </c>
@@ -3560,11 +3865,8 @@
       <c r="L42" t="s">
         <v>428</v>
       </c>
-      <c r="P42" t="str">
-        <v>luana.silva@enind.com.br</v>
-      </c>
-    </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>47</v>
       </c>
@@ -3601,11 +3903,8 @@
       <c r="L43" t="s">
         <v>430</v>
       </c>
-      <c r="P43" t="str">
-        <v>lucas.almeida@enind.com.br</v>
-      </c>
-    </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>156</v>
       </c>
@@ -3642,11 +3941,8 @@
       <c r="L44" t="s">
         <v>430</v>
       </c>
-      <c r="P44" t="str">
-        <v>luciano.bastos@enind.com.br</v>
-      </c>
-    </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>119</v>
       </c>
@@ -3683,11 +3979,8 @@
       <c r="L45" t="s">
         <v>430</v>
       </c>
-      <c r="P45" t="str">
-        <v>lucio.farias@enind.com.br</v>
-      </c>
-    </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>20</v>
       </c>
@@ -3724,11 +4017,8 @@
       <c r="L46" t="s">
         <v>430</v>
       </c>
-      <c r="P46" t="str">
-        <v>marcelo.silva@enind.com.br</v>
-      </c>
-    </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>95</v>
       </c>
@@ -3765,11 +4055,8 @@
       <c r="L47" t="s">
         <v>430</v>
       </c>
-      <c r="P47" t="str">
-        <v>marcos.nunes@enind.com.br</v>
-      </c>
-    </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>88</v>
       </c>
@@ -3806,11 +4093,8 @@
       <c r="L48" t="s">
         <v>430</v>
       </c>
-      <c r="P48" t="str">
-        <v>marcos.silva@enind.com.br</v>
-      </c>
-    </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>297</v>
       </c>
@@ -3847,11 +4131,8 @@
       <c r="L49" t="s">
         <v>430</v>
       </c>
-      <c r="P49" t="str">
-        <v>maria.sousa@enind.com.br</v>
-      </c>
-    </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>64</v>
       </c>
@@ -3888,11 +4169,8 @@
       <c r="L50" t="s">
         <v>430</v>
       </c>
-      <c r="P50" t="str">
-        <v>mayara.santos@enind.com.br</v>
-      </c>
-    </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>216</v>
       </c>
@@ -3929,11 +4207,8 @@
       <c r="L51" t="s">
         <v>428</v>
       </c>
-      <c r="P51" t="str">
-        <v>miriam.carvalho@enind.com.br</v>
-      </c>
-    </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>38</v>
       </c>
@@ -3970,11 +4245,8 @@
       <c r="L52" t="s">
         <v>430</v>
       </c>
-      <c r="P52" t="str">
-        <v>murilo.guidi@enind.com.br</v>
-      </c>
-    </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>380</v>
       </c>
@@ -4011,11 +4283,8 @@
       <c r="L53" t="s">
         <v>428</v>
       </c>
-      <c r="P53" t="str">
-        <v>pablo.almeida@enind.com.br</v>
-      </c>
-    </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>161</v>
       </c>
@@ -4052,11 +4321,8 @@
       <c r="L54" t="s">
         <v>428</v>
       </c>
-      <c r="P54" t="str">
-        <v>pierre.marinho@enind.com.br</v>
-      </c>
-    </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>14</v>
       </c>
@@ -4093,11 +4359,8 @@
       <c r="L55" t="s">
         <v>430</v>
       </c>
-      <c r="P55" t="str">
-        <v>rafael.araujo@enind.com.br</v>
-      </c>
-    </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>169</v>
       </c>
@@ -4132,11 +4395,8 @@
       <c r="L56" t="s">
         <v>428</v>
       </c>
-      <c r="P56" t="str">
-        <v>renan.cunha@enind.com.br</v>
-      </c>
-    </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>3</v>
       </c>
@@ -4173,11 +4433,8 @@
       <c r="L57" t="s">
         <v>428</v>
       </c>
-      <c r="P57" t="str">
-        <v>rodolfo.moraes@enind.com.br</v>
-      </c>
-    </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>13</v>
       </c>
@@ -4214,11 +4471,8 @@
       <c r="L58" t="s">
         <v>428</v>
       </c>
-      <c r="P58" t="str">
-        <v>rodrigo.moralez@enind.com.br</v>
-      </c>
-    </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>169</v>
       </c>
@@ -4255,11 +4509,8 @@
       <c r="L59" t="s">
         <v>428</v>
       </c>
-      <c r="P59" t="str">
-        <v>ronierison.siqueira@enindservicos.com.br</v>
-      </c>
-    </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>89</v>
       </c>
@@ -4294,11 +4545,8 @@
       <c r="L60" t="s">
         <v>429</v>
       </c>
-      <c r="P60" t="str">
-        <v>talita.peixoto@enind.com.br</v>
-      </c>
-    </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>94</v>
       </c>
@@ -4333,11 +4581,8 @@
       <c r="L61" t="s">
         <v>429</v>
       </c>
-      <c r="P61" t="str">
-        <v>thais.alves@enind.com.br</v>
-      </c>
-    </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>58</v>
       </c>
@@ -4374,11 +4619,8 @@
       <c r="L62" t="s">
         <v>429</v>
       </c>
-      <c r="P62" t="str">
-        <v>thelma.alves@enind.com.br</v>
-      </c>
-    </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>96</v>
       </c>
@@ -4412,11 +4654,8 @@
       <c r="L63" t="s">
         <v>429</v>
       </c>
-      <c r="P63" t="str">
-        <v>thiago.oliveira@enind.com.br</v>
-      </c>
-    </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>101</v>
       </c>
@@ -4450,11 +4689,8 @@
       <c r="L64" t="s">
         <v>429</v>
       </c>
-      <c r="P64" t="str">
-        <v>thiago.rodrigues@enind.com.br</v>
-      </c>
-    </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>105</v>
       </c>
@@ -4489,11 +4725,8 @@
       <c r="L65" t="s">
         <v>429</v>
       </c>
-      <c r="P65" t="str">
-        <v>ubiara.batista@enind.com.br</v>
-      </c>
-    </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>174</v>
       </c>
@@ -4530,11 +4763,8 @@
       <c r="L66" t="s">
         <v>428</v>
       </c>
-      <c r="P66" t="str">
-        <v>valeria.souza@enind.com.br</v>
-      </c>
-    </row>
-    <row r="67" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>63</v>
       </c>
@@ -4571,11 +4801,8 @@
       <c r="L67" t="s">
         <v>428</v>
       </c>
-      <c r="P67" t="str">
-        <v>vinicius.silva@enind.com.br</v>
-      </c>
-    </row>
-    <row r="68" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>387</v>
       </c>
@@ -4612,11 +4839,8 @@
       <c r="L68" t="s">
         <v>428</v>
       </c>
-      <c r="P68" t="str">
-        <v>vinicius.xisto@enind.com.br</v>
-      </c>
-    </row>
-    <row r="69" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>89</v>
       </c>
@@ -4651,11 +4875,8 @@
       <c r="L69" t="s">
         <v>429</v>
       </c>
-      <c r="P69" t="str">
-        <v>w.cristal@enind.com.br</v>
-      </c>
-    </row>
-    <row r="70" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>94</v>
       </c>
@@ -4689,11 +4910,8 @@
       <c r="L70" t="s">
         <v>429</v>
       </c>
-      <c r="P70" t="str">
-        <v>wagner.ferreira@enind.com.br</v>
-      </c>
-    </row>
-    <row r="71" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>96</v>
       </c>
@@ -4727,11 +4945,8 @@
       <c r="L71" t="s">
         <v>429</v>
       </c>
-      <c r="P71" t="str">
-        <v>welton.martins@enind.com.br</v>
-      </c>
-    </row>
-    <row r="72" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>101</v>
       </c>
@@ -4765,11 +4980,8 @@
       <c r="L72" t="s">
         <v>429</v>
       </c>
-      <c r="P72" t="str">
-        <v>weshiley.a.silva@enind.com.br</v>
-      </c>
-    </row>
-    <row r="73" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>105</v>
       </c>
@@ -4803,11 +5015,8 @@
       <c r="L73" t="s">
         <v>429</v>
       </c>
-      <c r="P73" t="str">
-        <v>weslley.costa@enind.com.br</v>
-      </c>
-    </row>
-    <row r="74" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>23</v>
       </c>
@@ -4844,11 +5053,8 @@
       <c r="L74" t="s">
         <v>430</v>
       </c>
-      <c r="P74" t="str">
-        <v>wilson.fernandes@enind.com.br</v>
-      </c>
-    </row>
-    <row r="75" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
         <v>33</v>
       </c>
@@ -4886,7 +5092,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="76" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
         <v>22</v>
       </c>
@@ -4924,7 +5130,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="77" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
         <v>196</v>
       </c>
@@ -4962,7 +5168,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="78" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
         <v>51</v>
       </c>
@@ -5000,7 +5206,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="79" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
         <v>201</v>
       </c>
@@ -5038,7 +5244,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="80" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>71</v>
       </c>
@@ -12805,6 +13011,4338 @@
         <v>402</v>
       </c>
       <c r="L284" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="285" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A285" t="s">
+        <v>437</v>
+      </c>
+      <c r="B285" t="s">
+        <v>437</v>
+      </c>
+      <c r="C285" t="s">
+        <v>475</v>
+      </c>
+      <c r="D285" t="s">
+        <v>407</v>
+      </c>
+      <c r="E285" t="s">
+        <v>511</v>
+      </c>
+      <c r="F285" t="s">
+        <v>548</v>
+      </c>
+      <c r="G285" t="s">
+        <v>511</v>
+      </c>
+      <c r="H285" t="s">
+        <v>548</v>
+      </c>
+      <c r="I285" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J285" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K285" t="s">
+        <v>475</v>
+      </c>
+      <c r="L285" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="286" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A286" t="s">
+        <v>438</v>
+      </c>
+      <c r="B286" t="s">
+        <v>438</v>
+      </c>
+      <c r="C286" t="s">
+        <v>476</v>
+      </c>
+      <c r="D286" t="s">
+        <v>407</v>
+      </c>
+      <c r="E286" t="s">
+        <v>512</v>
+      </c>
+      <c r="F286" t="s">
+        <v>549</v>
+      </c>
+      <c r="G286" t="s">
+        <v>512</v>
+      </c>
+      <c r="H286" t="s">
+        <v>549</v>
+      </c>
+      <c r="I286" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J286" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K286" t="s">
+        <v>476</v>
+      </c>
+      <c r="L286" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="287" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A287" t="s">
+        <v>439</v>
+      </c>
+      <c r="B287" t="s">
+        <v>439</v>
+      </c>
+      <c r="C287" t="s">
+        <v>477</v>
+      </c>
+      <c r="D287" t="s">
+        <v>407</v>
+      </c>
+      <c r="E287" t="s">
+        <v>513</v>
+      </c>
+      <c r="F287" t="s">
+        <v>550</v>
+      </c>
+      <c r="G287" t="s">
+        <v>513</v>
+      </c>
+      <c r="H287" t="s">
+        <v>550</v>
+      </c>
+      <c r="I287" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J287" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K287" t="s">
+        <v>477</v>
+      </c>
+      <c r="L287" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="288" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A288" t="s">
+        <v>440</v>
+      </c>
+      <c r="B288" t="s">
+        <v>440</v>
+      </c>
+      <c r="C288" t="s">
+        <v>478</v>
+      </c>
+      <c r="D288" t="s">
+        <v>407</v>
+      </c>
+      <c r="E288" t="s">
+        <v>514</v>
+      </c>
+      <c r="F288" t="s">
+        <v>551</v>
+      </c>
+      <c r="G288" t="s">
+        <v>514</v>
+      </c>
+      <c r="H288" t="s">
+        <v>551</v>
+      </c>
+      <c r="I288" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J288" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K288" t="s">
+        <v>478</v>
+      </c>
+      <c r="L288" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="289" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A289" t="s">
+        <v>441</v>
+      </c>
+      <c r="B289" t="s">
+        <v>441</v>
+      </c>
+      <c r="C289" t="s">
+        <v>479</v>
+      </c>
+      <c r="D289" t="s">
+        <v>407</v>
+      </c>
+      <c r="E289" t="s">
+        <v>515</v>
+      </c>
+      <c r="F289" t="s">
+        <v>552</v>
+      </c>
+      <c r="G289" t="s">
+        <v>515</v>
+      </c>
+      <c r="H289" t="s">
+        <v>552</v>
+      </c>
+      <c r="I289" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J289" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K289" t="s">
+        <v>479</v>
+      </c>
+      <c r="L289" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="290" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A290" t="s">
+        <v>442</v>
+      </c>
+      <c r="B290" t="s">
+        <v>442</v>
+      </c>
+      <c r="C290" t="s">
+        <v>436</v>
+      </c>
+      <c r="D290" t="s">
+        <v>407</v>
+      </c>
+      <c r="E290" t="s">
+        <v>516</v>
+      </c>
+      <c r="F290" t="s">
+        <v>553</v>
+      </c>
+      <c r="G290" t="s">
+        <v>516</v>
+      </c>
+      <c r="H290" t="s">
+        <v>553</v>
+      </c>
+      <c r="I290" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J290" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K290" t="s">
+        <v>436</v>
+      </c>
+      <c r="L290" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="291" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A291" t="s">
+        <v>443</v>
+      </c>
+      <c r="B291" t="s">
+        <v>443</v>
+      </c>
+      <c r="C291" t="s">
+        <v>480</v>
+      </c>
+      <c r="D291" t="s">
+        <v>407</v>
+      </c>
+      <c r="E291" t="s">
+        <v>517</v>
+      </c>
+      <c r="F291" t="s">
+        <v>554</v>
+      </c>
+      <c r="G291" t="s">
+        <v>517</v>
+      </c>
+      <c r="H291" t="s">
+        <v>554</v>
+      </c>
+      <c r="I291" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J291" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K291" t="s">
+        <v>480</v>
+      </c>
+      <c r="L291" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="292" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A292" t="s">
+        <v>444</v>
+      </c>
+      <c r="B292" t="s">
+        <v>444</v>
+      </c>
+      <c r="C292" t="s">
+        <v>481</v>
+      </c>
+      <c r="D292" t="s">
+        <v>407</v>
+      </c>
+      <c r="E292" t="s">
+        <v>518</v>
+      </c>
+      <c r="F292" t="s">
+        <v>555</v>
+      </c>
+      <c r="G292" t="s">
+        <v>518</v>
+      </c>
+      <c r="H292" t="s">
+        <v>555</v>
+      </c>
+      <c r="I292" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J292" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K292" t="s">
+        <v>481</v>
+      </c>
+      <c r="L292" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="293" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A293" t="s">
+        <v>445</v>
+      </c>
+      <c r="B293" t="s">
+        <v>445</v>
+      </c>
+      <c r="C293" t="s">
+        <v>482</v>
+      </c>
+      <c r="D293" t="s">
+        <v>407</v>
+      </c>
+      <c r="E293" t="s">
+        <v>519</v>
+      </c>
+      <c r="F293" t="s">
+        <v>556</v>
+      </c>
+      <c r="G293" t="s">
+        <v>519</v>
+      </c>
+      <c r="H293" t="s">
+        <v>556</v>
+      </c>
+      <c r="I293" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J293" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K293" t="s">
+        <v>482</v>
+      </c>
+      <c r="L293" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="294" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A294" t="s">
+        <v>446</v>
+      </c>
+      <c r="B294" t="s">
+        <v>446</v>
+      </c>
+      <c r="C294" t="s">
+        <v>483</v>
+      </c>
+      <c r="D294" t="s">
+        <v>407</v>
+      </c>
+      <c r="E294" t="s">
+        <v>520</v>
+      </c>
+      <c r="F294" t="s">
+        <v>557</v>
+      </c>
+      <c r="G294" t="s">
+        <v>520</v>
+      </c>
+      <c r="H294" t="s">
+        <v>557</v>
+      </c>
+      <c r="I294" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J294" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K294" t="s">
+        <v>483</v>
+      </c>
+      <c r="L294" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="295" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A295" t="s">
+        <v>447</v>
+      </c>
+      <c r="B295" t="s">
+        <v>447</v>
+      </c>
+      <c r="C295" t="s">
+        <v>484</v>
+      </c>
+      <c r="D295" t="s">
+        <v>407</v>
+      </c>
+      <c r="E295" t="s">
+        <v>521</v>
+      </c>
+      <c r="F295" t="s">
+        <v>558</v>
+      </c>
+      <c r="G295" t="s">
+        <v>521</v>
+      </c>
+      <c r="H295" t="s">
+        <v>558</v>
+      </c>
+      <c r="I295" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J295" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K295" t="s">
+        <v>484</v>
+      </c>
+      <c r="L295" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="296" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A296" t="s">
+        <v>448</v>
+      </c>
+      <c r="B296" t="s">
+        <v>448</v>
+      </c>
+      <c r="C296" t="s">
+        <v>485</v>
+      </c>
+      <c r="D296" t="s">
+        <v>407</v>
+      </c>
+      <c r="E296" t="s">
+        <v>522</v>
+      </c>
+      <c r="F296" t="s">
+        <v>559</v>
+      </c>
+      <c r="G296" t="s">
+        <v>522</v>
+      </c>
+      <c r="H296" t="s">
+        <v>559</v>
+      </c>
+      <c r="I296" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J296" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K296" t="s">
+        <v>485</v>
+      </c>
+      <c r="L296" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="297" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A297" t="s">
+        <v>449</v>
+      </c>
+      <c r="B297" t="s">
+        <v>449</v>
+      </c>
+      <c r="C297" t="s">
+        <v>486</v>
+      </c>
+      <c r="D297" t="s">
+        <v>407</v>
+      </c>
+      <c r="E297" t="s">
+        <v>523</v>
+      </c>
+      <c r="F297" t="s">
+        <v>560</v>
+      </c>
+      <c r="G297" t="s">
+        <v>523</v>
+      </c>
+      <c r="H297" t="s">
+        <v>560</v>
+      </c>
+      <c r="I297" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J297" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K297" t="s">
+        <v>486</v>
+      </c>
+      <c r="L297" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="298" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A298" t="s">
+        <v>450</v>
+      </c>
+      <c r="B298" t="s">
+        <v>450</v>
+      </c>
+      <c r="C298" t="s">
+        <v>487</v>
+      </c>
+      <c r="D298" t="s">
+        <v>407</v>
+      </c>
+      <c r="E298" t="s">
+        <v>524</v>
+      </c>
+      <c r="F298" t="s">
+        <v>561</v>
+      </c>
+      <c r="G298" t="s">
+        <v>524</v>
+      </c>
+      <c r="H298" t="s">
+        <v>561</v>
+      </c>
+      <c r="I298" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J298" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K298" t="s">
+        <v>487</v>
+      </c>
+      <c r="L298" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="299" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A299" t="s">
+        <v>451</v>
+      </c>
+      <c r="B299" t="s">
+        <v>451</v>
+      </c>
+      <c r="C299" t="s">
+        <v>488</v>
+      </c>
+      <c r="D299" t="s">
+        <v>407</v>
+      </c>
+      <c r="E299" t="s">
+        <v>525</v>
+      </c>
+      <c r="F299" t="s">
+        <v>562</v>
+      </c>
+      <c r="G299" t="s">
+        <v>525</v>
+      </c>
+      <c r="H299" t="s">
+        <v>562</v>
+      </c>
+      <c r="I299" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J299" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K299" t="s">
+        <v>488</v>
+      </c>
+      <c r="L299" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="300" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A300" t="s">
+        <v>452</v>
+      </c>
+      <c r="B300" t="s">
+        <v>452</v>
+      </c>
+      <c r="C300" t="s">
+        <v>489</v>
+      </c>
+      <c r="D300" t="s">
+        <v>407</v>
+      </c>
+      <c r="E300" t="s">
+        <v>526</v>
+      </c>
+      <c r="F300" t="s">
+        <v>563</v>
+      </c>
+      <c r="G300" t="s">
+        <v>526</v>
+      </c>
+      <c r="H300" t="s">
+        <v>563</v>
+      </c>
+      <c r="I300" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J300" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K300" t="s">
+        <v>489</v>
+      </c>
+      <c r="L300" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="301" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A301" t="s">
+        <v>453</v>
+      </c>
+      <c r="B301" t="s">
+        <v>453</v>
+      </c>
+      <c r="C301" t="s">
+        <v>490</v>
+      </c>
+      <c r="D301" t="s">
+        <v>407</v>
+      </c>
+      <c r="E301" t="s">
+        <v>527</v>
+      </c>
+      <c r="F301" t="s">
+        <v>564</v>
+      </c>
+      <c r="G301" t="s">
+        <v>527</v>
+      </c>
+      <c r="H301" t="s">
+        <v>564</v>
+      </c>
+      <c r="I301" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J301" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K301" t="s">
+        <v>490</v>
+      </c>
+      <c r="L301" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="302" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A302" t="s">
+        <v>454</v>
+      </c>
+      <c r="B302" t="s">
+        <v>454</v>
+      </c>
+      <c r="C302" t="s">
+        <v>491</v>
+      </c>
+      <c r="D302" t="s">
+        <v>407</v>
+      </c>
+      <c r="E302" t="s">
+        <v>528</v>
+      </c>
+      <c r="F302" t="s">
+        <v>565</v>
+      </c>
+      <c r="G302" t="s">
+        <v>528</v>
+      </c>
+      <c r="H302" t="s">
+        <v>565</v>
+      </c>
+      <c r="I302" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J302" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K302" t="s">
+        <v>491</v>
+      </c>
+      <c r="L302" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="303" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A303" t="s">
+        <v>455</v>
+      </c>
+      <c r="B303" t="s">
+        <v>455</v>
+      </c>
+      <c r="C303" t="s">
+        <v>492</v>
+      </c>
+      <c r="D303" t="s">
+        <v>407</v>
+      </c>
+      <c r="E303" t="s">
+        <v>529</v>
+      </c>
+      <c r="F303" t="s">
+        <v>566</v>
+      </c>
+      <c r="G303" t="s">
+        <v>529</v>
+      </c>
+      <c r="H303" t="s">
+        <v>566</v>
+      </c>
+      <c r="I303" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J303" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K303" t="s">
+        <v>492</v>
+      </c>
+      <c r="L303" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="304" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A304" t="s">
+        <v>456</v>
+      </c>
+      <c r="B304" t="s">
+        <v>456</v>
+      </c>
+      <c r="C304" t="s">
+        <v>493</v>
+      </c>
+      <c r="D304" t="s">
+        <v>407</v>
+      </c>
+      <c r="E304" t="s">
+        <v>530</v>
+      </c>
+      <c r="F304" t="s">
+        <v>567</v>
+      </c>
+      <c r="G304" t="s">
+        <v>530</v>
+      </c>
+      <c r="H304" t="s">
+        <v>567</v>
+      </c>
+      <c r="I304" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J304" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K304" t="s">
+        <v>493</v>
+      </c>
+      <c r="L304" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="305" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A305" t="s">
+        <v>457</v>
+      </c>
+      <c r="B305" t="s">
+        <v>457</v>
+      </c>
+      <c r="C305" t="s">
+        <v>494</v>
+      </c>
+      <c r="D305" t="s">
+        <v>407</v>
+      </c>
+      <c r="E305" t="s">
+        <v>531</v>
+      </c>
+      <c r="F305" t="s">
+        <v>568</v>
+      </c>
+      <c r="G305" t="s">
+        <v>531</v>
+      </c>
+      <c r="H305" t="s">
+        <v>568</v>
+      </c>
+      <c r="I305" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J305" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K305" t="s">
+        <v>494</v>
+      </c>
+      <c r="L305" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="306" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A306" t="s">
+        <v>458</v>
+      </c>
+      <c r="B306" t="s">
+        <v>458</v>
+      </c>
+      <c r="C306" t="s">
+        <v>495</v>
+      </c>
+      <c r="D306" t="s">
+        <v>407</v>
+      </c>
+      <c r="E306" t="s">
+        <v>532</v>
+      </c>
+      <c r="F306" t="s">
+        <v>569</v>
+      </c>
+      <c r="G306" t="s">
+        <v>532</v>
+      </c>
+      <c r="H306" t="s">
+        <v>569</v>
+      </c>
+      <c r="I306" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J306" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K306" t="s">
+        <v>495</v>
+      </c>
+      <c r="L306" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="307" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A307" t="s">
+        <v>459</v>
+      </c>
+      <c r="B307" t="s">
+        <v>459</v>
+      </c>
+      <c r="C307" t="s">
+        <v>496</v>
+      </c>
+      <c r="D307" t="s">
+        <v>407</v>
+      </c>
+      <c r="E307" t="s">
+        <v>533</v>
+      </c>
+      <c r="F307" t="s">
+        <v>570</v>
+      </c>
+      <c r="G307" t="s">
+        <v>533</v>
+      </c>
+      <c r="H307" t="s">
+        <v>570</v>
+      </c>
+      <c r="I307" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J307" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K307" t="s">
+        <v>496</v>
+      </c>
+      <c r="L307" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="308" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A308" t="s">
+        <v>460</v>
+      </c>
+      <c r="B308" t="s">
+        <v>460</v>
+      </c>
+      <c r="C308" t="s">
+        <v>497</v>
+      </c>
+      <c r="D308" t="s">
+        <v>407</v>
+      </c>
+      <c r="E308" t="s">
+        <v>534</v>
+      </c>
+      <c r="F308" t="s">
+        <v>571</v>
+      </c>
+      <c r="G308" t="s">
+        <v>534</v>
+      </c>
+      <c r="H308" t="s">
+        <v>571</v>
+      </c>
+      <c r="I308" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J308" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K308" t="s">
+        <v>497</v>
+      </c>
+      <c r="L308" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="309" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A309" t="s">
+        <v>461</v>
+      </c>
+      <c r="B309" t="s">
+        <v>461</v>
+      </c>
+      <c r="C309" t="s">
+        <v>498</v>
+      </c>
+      <c r="D309" t="s">
+        <v>407</v>
+      </c>
+      <c r="E309" t="s">
+        <v>535</v>
+      </c>
+      <c r="F309" t="s">
+        <v>572</v>
+      </c>
+      <c r="G309" t="s">
+        <v>535</v>
+      </c>
+      <c r="H309" t="s">
+        <v>572</v>
+      </c>
+      <c r="I309" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J309" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K309" t="s">
+        <v>498</v>
+      </c>
+      <c r="L309" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="310" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A310" t="s">
+        <v>462</v>
+      </c>
+      <c r="B310" t="s">
+        <v>462</v>
+      </c>
+      <c r="C310" t="s">
+        <v>499</v>
+      </c>
+      <c r="D310" t="s">
+        <v>407</v>
+      </c>
+      <c r="E310" t="s">
+        <v>536</v>
+      </c>
+      <c r="F310" t="s">
+        <v>573</v>
+      </c>
+      <c r="G310" t="s">
+        <v>536</v>
+      </c>
+      <c r="H310" t="s">
+        <v>573</v>
+      </c>
+      <c r="I310" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J310" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K310" t="s">
+        <v>499</v>
+      </c>
+      <c r="L310" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="311" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A311" t="s">
+        <v>463</v>
+      </c>
+      <c r="B311" t="s">
+        <v>463</v>
+      </c>
+      <c r="C311" t="s">
+        <v>500</v>
+      </c>
+      <c r="D311" t="s">
+        <v>407</v>
+      </c>
+      <c r="E311" t="s">
+        <v>537</v>
+      </c>
+      <c r="F311" t="s">
+        <v>574</v>
+      </c>
+      <c r="G311" t="s">
+        <v>537</v>
+      </c>
+      <c r="H311" t="s">
+        <v>574</v>
+      </c>
+      <c r="I311" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J311" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K311" t="s">
+        <v>500</v>
+      </c>
+      <c r="L311" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="312" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A312" t="s">
+        <v>464</v>
+      </c>
+      <c r="B312" t="s">
+        <v>464</v>
+      </c>
+      <c r="C312" t="s">
+        <v>501</v>
+      </c>
+      <c r="D312" t="s">
+        <v>407</v>
+      </c>
+      <c r="E312" t="s">
+        <v>538</v>
+      </c>
+      <c r="F312" t="s">
+        <v>575</v>
+      </c>
+      <c r="G312" t="s">
+        <v>538</v>
+      </c>
+      <c r="H312" t="s">
+        <v>575</v>
+      </c>
+      <c r="I312" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J312" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K312" t="s">
+        <v>501</v>
+      </c>
+      <c r="L312" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="313" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A313" t="s">
+        <v>465</v>
+      </c>
+      <c r="B313" t="s">
+        <v>465</v>
+      </c>
+      <c r="C313" t="s">
+        <v>502</v>
+      </c>
+      <c r="D313" t="s">
+        <v>407</v>
+      </c>
+      <c r="E313" t="s">
+        <v>539</v>
+      </c>
+      <c r="F313" t="s">
+        <v>576</v>
+      </c>
+      <c r="G313" t="s">
+        <v>539</v>
+      </c>
+      <c r="H313" t="s">
+        <v>576</v>
+      </c>
+      <c r="I313" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J313" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K313" t="s">
+        <v>502</v>
+      </c>
+      <c r="L313" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="314" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A314" t="s">
+        <v>466</v>
+      </c>
+      <c r="B314" t="s">
+        <v>466</v>
+      </c>
+      <c r="C314" t="s">
+        <v>503</v>
+      </c>
+      <c r="D314" t="s">
+        <v>407</v>
+      </c>
+      <c r="E314" t="s">
+        <v>540</v>
+      </c>
+      <c r="F314" t="s">
+        <v>577</v>
+      </c>
+      <c r="G314" t="s">
+        <v>540</v>
+      </c>
+      <c r="H314" t="s">
+        <v>577</v>
+      </c>
+      <c r="I314" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J314" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K314" t="s">
+        <v>503</v>
+      </c>
+      <c r="L314" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="315" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A315" t="s">
+        <v>467</v>
+      </c>
+      <c r="B315" t="s">
+        <v>467</v>
+      </c>
+      <c r="C315" t="s">
+        <v>504</v>
+      </c>
+      <c r="D315" t="s">
+        <v>407</v>
+      </c>
+      <c r="E315" t="s">
+        <v>541</v>
+      </c>
+      <c r="F315" t="s">
+        <v>578</v>
+      </c>
+      <c r="G315" t="s">
+        <v>541</v>
+      </c>
+      <c r="H315" t="s">
+        <v>578</v>
+      </c>
+      <c r="I315" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J315" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K315" t="s">
+        <v>504</v>
+      </c>
+      <c r="L315" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="316" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A316" t="s">
+        <v>468</v>
+      </c>
+      <c r="B316" t="s">
+        <v>468</v>
+      </c>
+      <c r="C316" t="s">
+        <v>505</v>
+      </c>
+      <c r="D316" t="s">
+        <v>407</v>
+      </c>
+      <c r="E316" t="s">
+        <v>542</v>
+      </c>
+      <c r="F316" t="s">
+        <v>579</v>
+      </c>
+      <c r="G316" t="s">
+        <v>542</v>
+      </c>
+      <c r="H316" t="s">
+        <v>579</v>
+      </c>
+      <c r="I316" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J316" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K316" t="s">
+        <v>505</v>
+      </c>
+      <c r="L316" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="317" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A317" t="s">
+        <v>469</v>
+      </c>
+      <c r="B317" t="s">
+        <v>469</v>
+      </c>
+      <c r="C317" t="s">
+        <v>506</v>
+      </c>
+      <c r="D317" t="s">
+        <v>407</v>
+      </c>
+      <c r="E317" t="s">
+        <v>543</v>
+      </c>
+      <c r="F317" t="s">
+        <v>580</v>
+      </c>
+      <c r="G317" t="s">
+        <v>543</v>
+      </c>
+      <c r="H317" t="s">
+        <v>580</v>
+      </c>
+      <c r="I317" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J317" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K317" t="s">
+        <v>506</v>
+      </c>
+      <c r="L317" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="318" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A318" t="s">
+        <v>470</v>
+      </c>
+      <c r="B318" t="s">
+        <v>470</v>
+      </c>
+      <c r="C318" t="s">
+        <v>507</v>
+      </c>
+      <c r="D318" t="s">
+        <v>407</v>
+      </c>
+      <c r="E318" t="s">
+        <v>544</v>
+      </c>
+      <c r="F318" t="s">
+        <v>581</v>
+      </c>
+      <c r="G318" t="s">
+        <v>544</v>
+      </c>
+      <c r="H318" t="s">
+        <v>581</v>
+      </c>
+      <c r="I318" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J318" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K318" t="s">
+        <v>507</v>
+      </c>
+      <c r="L318" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="319" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A319" t="s">
+        <v>471</v>
+      </c>
+      <c r="B319" t="s">
+        <v>471</v>
+      </c>
+      <c r="C319" t="s">
+        <v>508</v>
+      </c>
+      <c r="D319" t="s">
+        <v>407</v>
+      </c>
+      <c r="E319" t="s">
+        <v>545</v>
+      </c>
+      <c r="F319" t="s">
+        <v>582</v>
+      </c>
+      <c r="G319" t="s">
+        <v>545</v>
+      </c>
+      <c r="H319" t="s">
+        <v>582</v>
+      </c>
+      <c r="I319" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J319" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K319" t="s">
+        <v>508</v>
+      </c>
+      <c r="L319" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="320" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A320" t="s">
+        <v>472</v>
+      </c>
+      <c r="B320" t="s">
+        <v>472</v>
+      </c>
+      <c r="C320" t="s">
+        <v>509</v>
+      </c>
+      <c r="D320" t="s">
+        <v>407</v>
+      </c>
+      <c r="E320" t="s">
+        <v>546</v>
+      </c>
+      <c r="F320" t="s">
+        <v>583</v>
+      </c>
+      <c r="G320" t="s">
+        <v>546</v>
+      </c>
+      <c r="H320" t="s">
+        <v>583</v>
+      </c>
+      <c r="I320" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J320" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K320" t="s">
+        <v>509</v>
+      </c>
+      <c r="L320" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="321" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A321" t="s">
+        <v>473</v>
+      </c>
+      <c r="B321" t="s">
+        <v>473</v>
+      </c>
+      <c r="C321" t="s">
+        <v>393</v>
+      </c>
+      <c r="D321" t="s">
+        <v>407</v>
+      </c>
+      <c r="E321" t="s">
+        <v>394</v>
+      </c>
+      <c r="F321" t="s">
+        <v>584</v>
+      </c>
+      <c r="G321" t="s">
+        <v>394</v>
+      </c>
+      <c r="H321" t="s">
+        <v>584</v>
+      </c>
+      <c r="I321" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J321" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K321" t="s">
+        <v>393</v>
+      </c>
+      <c r="L321" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="322" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A322" t="s">
+        <v>474</v>
+      </c>
+      <c r="B322" t="s">
+        <v>474</v>
+      </c>
+      <c r="C322" t="s">
+        <v>510</v>
+      </c>
+      <c r="D322" t="s">
+        <v>407</v>
+      </c>
+      <c r="E322" t="s">
+        <v>547</v>
+      </c>
+      <c r="F322" t="s">
+        <v>585</v>
+      </c>
+      <c r="G322" t="s">
+        <v>547</v>
+      </c>
+      <c r="H322" t="s">
+        <v>585</v>
+      </c>
+      <c r="I322" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J322" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K322" t="s">
+        <v>510</v>
+      </c>
+      <c r="L322" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="323" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A323" t="s">
+        <v>437</v>
+      </c>
+      <c r="B323" t="s">
+        <v>20</v>
+      </c>
+      <c r="C323" t="s">
+        <v>399</v>
+      </c>
+      <c r="D323" t="s">
+        <v>410</v>
+      </c>
+      <c r="E323" t="s">
+        <v>150</v>
+      </c>
+      <c r="F323" t="s">
+        <v>151</v>
+      </c>
+      <c r="G323" t="s">
+        <v>511</v>
+      </c>
+      <c r="H323" t="s">
+        <v>548</v>
+      </c>
+      <c r="I323" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J323" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K323" t="s">
+        <v>399</v>
+      </c>
+      <c r="L323" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="324" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A324" t="s">
+        <v>438</v>
+      </c>
+      <c r="B324" t="s">
+        <v>64</v>
+      </c>
+      <c r="C324" t="s">
+        <v>369</v>
+      </c>
+      <c r="D324" t="s">
+        <v>410</v>
+      </c>
+      <c r="E324" t="s">
+        <v>370</v>
+      </c>
+      <c r="F324" t="s">
+        <v>371</v>
+      </c>
+      <c r="G324" t="s">
+        <v>512</v>
+      </c>
+      <c r="H324" t="s">
+        <v>549</v>
+      </c>
+      <c r="I324" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J324" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K324" t="s">
+        <v>369</v>
+      </c>
+      <c r="L324" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="325" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A325" t="s">
+        <v>439</v>
+      </c>
+      <c r="B325" t="s">
+        <v>225</v>
+      </c>
+      <c r="C325" t="s">
+        <v>226</v>
+      </c>
+      <c r="D325" t="s">
+        <v>410</v>
+      </c>
+      <c r="E325" t="s">
+        <v>227</v>
+      </c>
+      <c r="F325" t="s">
+        <v>228</v>
+      </c>
+      <c r="G325" t="s">
+        <v>513</v>
+      </c>
+      <c r="H325" t="s">
+        <v>550</v>
+      </c>
+      <c r="I325" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J325" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K325" t="s">
+        <v>226</v>
+      </c>
+      <c r="L325" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="326" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A326" t="s">
+        <v>440</v>
+      </c>
+      <c r="B326" t="s">
+        <v>47</v>
+      </c>
+      <c r="C326" t="s">
+        <v>48</v>
+      </c>
+      <c r="D326" t="s">
+        <v>410</v>
+      </c>
+      <c r="E326" t="s">
+        <v>49</v>
+      </c>
+      <c r="F326" t="s">
+        <v>50</v>
+      </c>
+      <c r="G326" t="s">
+        <v>514</v>
+      </c>
+      <c r="H326" t="s">
+        <v>551</v>
+      </c>
+      <c r="I326" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J326" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K326" t="s">
+        <v>48</v>
+      </c>
+      <c r="L326" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="327" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A327" t="s">
+        <v>441</v>
+      </c>
+      <c r="B327" t="s">
+        <v>119</v>
+      </c>
+      <c r="C327" t="s">
+        <v>379</v>
+      </c>
+      <c r="D327" t="s">
+        <v>410</v>
+      </c>
+      <c r="E327" t="s">
+        <v>159</v>
+      </c>
+      <c r="F327" t="s">
+        <v>160</v>
+      </c>
+      <c r="G327" t="s">
+        <v>515</v>
+      </c>
+      <c r="H327" t="s">
+        <v>552</v>
+      </c>
+      <c r="I327" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J327" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K327" t="s">
+        <v>379</v>
+      </c>
+      <c r="L327" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="328" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A328" t="s">
+        <v>442</v>
+      </c>
+      <c r="B328" t="s">
+        <v>64</v>
+      </c>
+      <c r="C328" t="s">
+        <v>369</v>
+      </c>
+      <c r="D328" t="s">
+        <v>410</v>
+      </c>
+      <c r="E328" t="s">
+        <v>370</v>
+      </c>
+      <c r="F328" t="s">
+        <v>371</v>
+      </c>
+      <c r="G328" t="s">
+        <v>516</v>
+      </c>
+      <c r="H328" t="s">
+        <v>553</v>
+      </c>
+      <c r="I328" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J328" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K328" t="s">
+        <v>369</v>
+      </c>
+      <c r="L328" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="329" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A329" t="s">
+        <v>443</v>
+      </c>
+      <c r="B329" t="s">
+        <v>446</v>
+      </c>
+      <c r="C329" t="s">
+        <v>483</v>
+      </c>
+      <c r="D329" t="s">
+        <v>410</v>
+      </c>
+      <c r="E329" t="s">
+        <v>520</v>
+      </c>
+      <c r="F329" t="s">
+        <v>557</v>
+      </c>
+      <c r="G329" t="s">
+        <v>517</v>
+      </c>
+      <c r="H329" t="s">
+        <v>554</v>
+      </c>
+      <c r="I329" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J329" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K329" t="s">
+        <v>483</v>
+      </c>
+      <c r="L329" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="330" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A330" t="s">
+        <v>444</v>
+      </c>
+      <c r="B330" t="s">
+        <v>47</v>
+      </c>
+      <c r="C330" t="s">
+        <v>48</v>
+      </c>
+      <c r="D330" t="s">
+        <v>410</v>
+      </c>
+      <c r="E330" t="s">
+        <v>49</v>
+      </c>
+      <c r="F330" t="s">
+        <v>50</v>
+      </c>
+      <c r="G330" t="s">
+        <v>518</v>
+      </c>
+      <c r="H330" t="s">
+        <v>555</v>
+      </c>
+      <c r="I330" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J330" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K330" t="s">
+        <v>48</v>
+      </c>
+      <c r="L330" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="331" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A331" t="s">
+        <v>445</v>
+      </c>
+      <c r="B331" t="s">
+        <v>216</v>
+      </c>
+      <c r="C331" t="s">
+        <v>351</v>
+      </c>
+      <c r="D331" t="s">
+        <v>410</v>
+      </c>
+      <c r="E331" t="s">
+        <v>217</v>
+      </c>
+      <c r="F331" t="s">
+        <v>218</v>
+      </c>
+      <c r="G331" t="s">
+        <v>519</v>
+      </c>
+      <c r="H331" t="s">
+        <v>556</v>
+      </c>
+      <c r="I331" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J331" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K331" t="s">
+        <v>351</v>
+      </c>
+      <c r="L331" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="332" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A332" t="s">
+        <v>446</v>
+      </c>
+      <c r="B332" t="s">
+        <v>148</v>
+      </c>
+      <c r="C332" t="s">
+        <v>149</v>
+      </c>
+      <c r="D332" t="s">
+        <v>410</v>
+      </c>
+      <c r="E332" t="s">
+        <v>411</v>
+      </c>
+      <c r="F332" t="s">
+        <v>412</v>
+      </c>
+      <c r="G332" t="s">
+        <v>520</v>
+      </c>
+      <c r="H332" t="s">
+        <v>557</v>
+      </c>
+      <c r="I332" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J332" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K332" t="s">
+        <v>149</v>
+      </c>
+      <c r="L332" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="333" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A333" t="s">
+        <v>447</v>
+      </c>
+      <c r="B333" t="s">
+        <v>297</v>
+      </c>
+      <c r="C333" t="s">
+        <v>298</v>
+      </c>
+      <c r="D333" t="s">
+        <v>410</v>
+      </c>
+      <c r="E333" t="s">
+        <v>299</v>
+      </c>
+      <c r="F333" t="s">
+        <v>300</v>
+      </c>
+      <c r="G333" t="s">
+        <v>521</v>
+      </c>
+      <c r="H333" t="s">
+        <v>558</v>
+      </c>
+      <c r="I333" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J333" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K333" t="s">
+        <v>298</v>
+      </c>
+      <c r="L333" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="334" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A334" t="s">
+        <v>448</v>
+      </c>
+      <c r="B334" t="s">
+        <v>148</v>
+      </c>
+      <c r="C334" t="s">
+        <v>149</v>
+      </c>
+      <c r="D334" t="s">
+        <v>410</v>
+      </c>
+      <c r="E334" t="s">
+        <v>411</v>
+      </c>
+      <c r="F334" t="s">
+        <v>412</v>
+      </c>
+      <c r="G334" t="s">
+        <v>522</v>
+      </c>
+      <c r="H334" t="s">
+        <v>559</v>
+      </c>
+      <c r="I334" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J334" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K334" t="s">
+        <v>149</v>
+      </c>
+      <c r="L334" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="335" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A335" t="s">
+        <v>449</v>
+      </c>
+      <c r="B335" t="s">
+        <v>64</v>
+      </c>
+      <c r="C335" t="s">
+        <v>369</v>
+      </c>
+      <c r="D335" t="s">
+        <v>410</v>
+      </c>
+      <c r="E335" t="s">
+        <v>370</v>
+      </c>
+      <c r="F335" t="s">
+        <v>371</v>
+      </c>
+      <c r="G335" t="s">
+        <v>523</v>
+      </c>
+      <c r="H335" t="s">
+        <v>560</v>
+      </c>
+      <c r="I335" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J335" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K335" t="s">
+        <v>369</v>
+      </c>
+      <c r="L335" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="336" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A336" t="s">
+        <v>450</v>
+      </c>
+      <c r="B336" t="s">
+        <v>119</v>
+      </c>
+      <c r="C336" t="s">
+        <v>379</v>
+      </c>
+      <c r="D336" t="s">
+        <v>410</v>
+      </c>
+      <c r="E336" t="s">
+        <v>159</v>
+      </c>
+      <c r="F336" t="s">
+        <v>160</v>
+      </c>
+      <c r="G336" t="s">
+        <v>524</v>
+      </c>
+      <c r="H336" t="s">
+        <v>561</v>
+      </c>
+      <c r="I336" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J336" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K336" t="s">
+        <v>379</v>
+      </c>
+      <c r="L336" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="337" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A337" t="s">
+        <v>451</v>
+      </c>
+      <c r="B337" t="s">
+        <v>119</v>
+      </c>
+      <c r="C337" t="s">
+        <v>379</v>
+      </c>
+      <c r="D337" t="s">
+        <v>410</v>
+      </c>
+      <c r="E337" t="s">
+        <v>159</v>
+      </c>
+      <c r="F337" t="s">
+        <v>160</v>
+      </c>
+      <c r="G337" t="s">
+        <v>525</v>
+      </c>
+      <c r="H337" t="s">
+        <v>562</v>
+      </c>
+      <c r="I337" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J337" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K337" t="s">
+        <v>379</v>
+      </c>
+      <c r="L337" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="338" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A338" t="s">
+        <v>452</v>
+      </c>
+      <c r="B338" t="s">
+        <v>95</v>
+      </c>
+      <c r="C338" t="s">
+        <v>401</v>
+      </c>
+      <c r="D338" t="s">
+        <v>410</v>
+      </c>
+      <c r="E338" t="s">
+        <v>152</v>
+      </c>
+      <c r="F338" t="s">
+        <v>153</v>
+      </c>
+      <c r="G338" t="s">
+        <v>526</v>
+      </c>
+      <c r="H338" t="s">
+        <v>563</v>
+      </c>
+      <c r="I338" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J338" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K338" t="s">
+        <v>401</v>
+      </c>
+      <c r="L338" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="339" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A339" t="s">
+        <v>453</v>
+      </c>
+      <c r="B339" t="s">
+        <v>235</v>
+      </c>
+      <c r="C339" t="s">
+        <v>236</v>
+      </c>
+      <c r="D339" t="s">
+        <v>410</v>
+      </c>
+      <c r="E339" t="s">
+        <v>237</v>
+      </c>
+      <c r="F339" t="s">
+        <v>238</v>
+      </c>
+      <c r="G339" t="s">
+        <v>527</v>
+      </c>
+      <c r="H339" t="s">
+        <v>564</v>
+      </c>
+      <c r="I339" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J339" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K339" t="s">
+        <v>236</v>
+      </c>
+      <c r="L339" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="340" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A340" t="s">
+        <v>454</v>
+      </c>
+      <c r="B340" t="s">
+        <v>64</v>
+      </c>
+      <c r="C340" t="s">
+        <v>369</v>
+      </c>
+      <c r="D340" t="s">
+        <v>410</v>
+      </c>
+      <c r="E340" t="s">
+        <v>370</v>
+      </c>
+      <c r="F340" t="s">
+        <v>371</v>
+      </c>
+      <c r="G340" t="s">
+        <v>528</v>
+      </c>
+      <c r="H340" t="s">
+        <v>565</v>
+      </c>
+      <c r="I340" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J340" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K340" t="s">
+        <v>369</v>
+      </c>
+      <c r="L340" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="341" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A341" t="s">
+        <v>455</v>
+      </c>
+      <c r="B341" t="s">
+        <v>64</v>
+      </c>
+      <c r="C341" t="s">
+        <v>369</v>
+      </c>
+      <c r="D341" t="s">
+        <v>410</v>
+      </c>
+      <c r="E341" t="s">
+        <v>370</v>
+      </c>
+      <c r="F341" t="s">
+        <v>371</v>
+      </c>
+      <c r="G341" t="s">
+        <v>529</v>
+      </c>
+      <c r="H341" t="s">
+        <v>566</v>
+      </c>
+      <c r="I341" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J341" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K341" t="s">
+        <v>369</v>
+      </c>
+      <c r="L341" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="342" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A342" t="s">
+        <v>456</v>
+      </c>
+      <c r="B342" t="s">
+        <v>119</v>
+      </c>
+      <c r="C342" t="s">
+        <v>379</v>
+      </c>
+      <c r="D342" t="s">
+        <v>410</v>
+      </c>
+      <c r="E342" t="s">
+        <v>159</v>
+      </c>
+      <c r="F342" t="s">
+        <v>160</v>
+      </c>
+      <c r="G342" t="s">
+        <v>530</v>
+      </c>
+      <c r="H342" t="s">
+        <v>567</v>
+      </c>
+      <c r="I342" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J342" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K342" t="s">
+        <v>379</v>
+      </c>
+      <c r="L342" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="343" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A343" t="s">
+        <v>457</v>
+      </c>
+      <c r="B343" t="s">
+        <v>446</v>
+      </c>
+      <c r="C343" t="s">
+        <v>483</v>
+      </c>
+      <c r="D343" t="s">
+        <v>410</v>
+      </c>
+      <c r="E343" t="s">
+        <v>520</v>
+      </c>
+      <c r="F343" t="s">
+        <v>557</v>
+      </c>
+      <c r="G343" t="s">
+        <v>531</v>
+      </c>
+      <c r="H343" t="s">
+        <v>568</v>
+      </c>
+      <c r="I343" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J343" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K343" t="s">
+        <v>483</v>
+      </c>
+      <c r="L343" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="344" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A344" t="s">
+        <v>458</v>
+      </c>
+      <c r="B344" t="s">
+        <v>47</v>
+      </c>
+      <c r="C344" t="s">
+        <v>48</v>
+      </c>
+      <c r="D344" t="s">
+        <v>410</v>
+      </c>
+      <c r="E344" t="s">
+        <v>49</v>
+      </c>
+      <c r="F344" t="s">
+        <v>50</v>
+      </c>
+      <c r="G344" t="s">
+        <v>532</v>
+      </c>
+      <c r="H344" t="s">
+        <v>569</v>
+      </c>
+      <c r="I344" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J344" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K344" t="s">
+        <v>48</v>
+      </c>
+      <c r="L344" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="345" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A345" t="s">
+        <v>459</v>
+      </c>
+      <c r="B345" t="s">
+        <v>235</v>
+      </c>
+      <c r="C345" t="s">
+        <v>236</v>
+      </c>
+      <c r="D345" t="s">
+        <v>410</v>
+      </c>
+      <c r="E345" t="s">
+        <v>237</v>
+      </c>
+      <c r="F345" t="s">
+        <v>238</v>
+      </c>
+      <c r="G345" t="s">
+        <v>533</v>
+      </c>
+      <c r="H345" t="s">
+        <v>570</v>
+      </c>
+      <c r="I345" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J345" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K345" t="s">
+        <v>236</v>
+      </c>
+      <c r="L345" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="346" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A346" t="s">
+        <v>460</v>
+      </c>
+      <c r="B346" t="s">
+        <v>64</v>
+      </c>
+      <c r="C346" t="s">
+        <v>369</v>
+      </c>
+      <c r="D346" t="s">
+        <v>410</v>
+      </c>
+      <c r="E346" t="s">
+        <v>370</v>
+      </c>
+      <c r="F346" t="s">
+        <v>371</v>
+      </c>
+      <c r="G346" t="s">
+        <v>534</v>
+      </c>
+      <c r="H346" t="s">
+        <v>571</v>
+      </c>
+      <c r="I346" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J346" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K346" t="s">
+        <v>369</v>
+      </c>
+      <c r="L346" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="347" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A347" t="s">
+        <v>461</v>
+      </c>
+      <c r="B347" t="s">
+        <v>448</v>
+      </c>
+      <c r="C347" t="s">
+        <v>485</v>
+      </c>
+      <c r="D347" t="s">
+        <v>410</v>
+      </c>
+      <c r="E347" t="s">
+        <v>522</v>
+      </c>
+      <c r="F347" t="s">
+        <v>559</v>
+      </c>
+      <c r="G347" t="s">
+        <v>535</v>
+      </c>
+      <c r="H347" t="s">
+        <v>572</v>
+      </c>
+      <c r="I347" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J347" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K347" t="s">
+        <v>485</v>
+      </c>
+      <c r="L347" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="348" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A348" t="s">
+        <v>462</v>
+      </c>
+      <c r="B348" t="s">
+        <v>119</v>
+      </c>
+      <c r="C348" t="s">
+        <v>379</v>
+      </c>
+      <c r="D348" t="s">
+        <v>410</v>
+      </c>
+      <c r="E348" t="s">
+        <v>159</v>
+      </c>
+      <c r="F348" t="s">
+        <v>160</v>
+      </c>
+      <c r="G348" t="s">
+        <v>536</v>
+      </c>
+      <c r="H348" t="s">
+        <v>573</v>
+      </c>
+      <c r="I348" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J348" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K348" t="s">
+        <v>379</v>
+      </c>
+      <c r="L348" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="349" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A349" t="s">
+        <v>463</v>
+      </c>
+      <c r="B349" t="s">
+        <v>446</v>
+      </c>
+      <c r="C349" t="s">
+        <v>483</v>
+      </c>
+      <c r="D349" t="s">
+        <v>410</v>
+      </c>
+      <c r="E349" t="s">
+        <v>520</v>
+      </c>
+      <c r="F349" t="s">
+        <v>557</v>
+      </c>
+      <c r="G349" t="s">
+        <v>537</v>
+      </c>
+      <c r="H349" t="s">
+        <v>574</v>
+      </c>
+      <c r="I349" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J349" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K349" t="s">
+        <v>483</v>
+      </c>
+      <c r="L349" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="350" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A350" t="s">
+        <v>464</v>
+      </c>
+      <c r="B350" t="s">
+        <v>325</v>
+      </c>
+      <c r="C350" t="s">
+        <v>326</v>
+      </c>
+      <c r="D350" t="s">
+        <v>410</v>
+      </c>
+      <c r="E350" t="s">
+        <v>327</v>
+      </c>
+      <c r="F350" t="s">
+        <v>328</v>
+      </c>
+      <c r="G350" t="s">
+        <v>538</v>
+      </c>
+      <c r="H350" t="s">
+        <v>575</v>
+      </c>
+      <c r="I350" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J350" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K350" t="s">
+        <v>326</v>
+      </c>
+      <c r="L350" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="351" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A351" t="s">
+        <v>465</v>
+      </c>
+      <c r="B351" t="s">
+        <v>325</v>
+      </c>
+      <c r="C351" t="s">
+        <v>326</v>
+      </c>
+      <c r="D351" t="s">
+        <v>410</v>
+      </c>
+      <c r="E351" t="s">
+        <v>327</v>
+      </c>
+      <c r="F351" t="s">
+        <v>328</v>
+      </c>
+      <c r="G351" t="s">
+        <v>539</v>
+      </c>
+      <c r="H351" t="s">
+        <v>576</v>
+      </c>
+      <c r="I351" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J351" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K351" t="s">
+        <v>326</v>
+      </c>
+      <c r="L351" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="352" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A352" t="s">
+        <v>466</v>
+      </c>
+      <c r="B352" t="s">
+        <v>297</v>
+      </c>
+      <c r="C352" t="s">
+        <v>298</v>
+      </c>
+      <c r="D352" t="s">
+        <v>410</v>
+      </c>
+      <c r="E352" t="s">
+        <v>299</v>
+      </c>
+      <c r="F352" t="s">
+        <v>300</v>
+      </c>
+      <c r="G352" t="s">
+        <v>540</v>
+      </c>
+      <c r="H352" t="s">
+        <v>577</v>
+      </c>
+      <c r="I352" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J352" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K352" t="s">
+        <v>298</v>
+      </c>
+      <c r="L352" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="353" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A353" t="s">
+        <v>467</v>
+      </c>
+      <c r="B353" t="s">
+        <v>47</v>
+      </c>
+      <c r="C353" t="s">
+        <v>48</v>
+      </c>
+      <c r="D353" t="s">
+        <v>410</v>
+      </c>
+      <c r="E353" t="s">
+        <v>49</v>
+      </c>
+      <c r="F353" t="s">
+        <v>50</v>
+      </c>
+      <c r="G353" t="s">
+        <v>541</v>
+      </c>
+      <c r="H353" t="s">
+        <v>578</v>
+      </c>
+      <c r="I353" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J353" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K353" t="s">
+        <v>48</v>
+      </c>
+      <c r="L353" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="354" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A354" t="s">
+        <v>468</v>
+      </c>
+      <c r="B354" t="s">
+        <v>225</v>
+      </c>
+      <c r="C354" t="s">
+        <v>226</v>
+      </c>
+      <c r="D354" t="s">
+        <v>410</v>
+      </c>
+      <c r="E354" t="s">
+        <v>227</v>
+      </c>
+      <c r="F354" t="s">
+        <v>228</v>
+      </c>
+      <c r="G354" t="s">
+        <v>542</v>
+      </c>
+      <c r="H354" t="s">
+        <v>579</v>
+      </c>
+      <c r="I354" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J354" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K354" t="s">
+        <v>226</v>
+      </c>
+      <c r="L354" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="355" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A355" t="s">
+        <v>469</v>
+      </c>
+      <c r="B355" t="s">
+        <v>64</v>
+      </c>
+      <c r="C355" t="s">
+        <v>369</v>
+      </c>
+      <c r="D355" t="s">
+        <v>410</v>
+      </c>
+      <c r="E355" t="s">
+        <v>370</v>
+      </c>
+      <c r="F355" t="s">
+        <v>371</v>
+      </c>
+      <c r="G355" t="s">
+        <v>543</v>
+      </c>
+      <c r="H355" t="s">
+        <v>580</v>
+      </c>
+      <c r="I355" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J355" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K355" t="s">
+        <v>369</v>
+      </c>
+      <c r="L355" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="356" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A356" t="s">
+        <v>470</v>
+      </c>
+      <c r="B356" t="s">
+        <v>325</v>
+      </c>
+      <c r="C356" t="s">
+        <v>326</v>
+      </c>
+      <c r="D356" t="s">
+        <v>410</v>
+      </c>
+      <c r="E356" t="s">
+        <v>327</v>
+      </c>
+      <c r="F356" t="s">
+        <v>328</v>
+      </c>
+      <c r="G356" t="s">
+        <v>544</v>
+      </c>
+      <c r="H356" t="s">
+        <v>581</v>
+      </c>
+      <c r="I356" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J356" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K356" t="s">
+        <v>326</v>
+      </c>
+      <c r="L356" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="357" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A357" t="s">
+        <v>471</v>
+      </c>
+      <c r="B357" t="s">
+        <v>446</v>
+      </c>
+      <c r="C357" t="s">
+        <v>483</v>
+      </c>
+      <c r="D357" t="s">
+        <v>410</v>
+      </c>
+      <c r="E357" t="s">
+        <v>520</v>
+      </c>
+      <c r="F357" t="s">
+        <v>557</v>
+      </c>
+      <c r="G357" t="s">
+        <v>545</v>
+      </c>
+      <c r="H357" t="s">
+        <v>582</v>
+      </c>
+      <c r="I357" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J357" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K357" t="s">
+        <v>483</v>
+      </c>
+      <c r="L357" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="358" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A358" t="s">
+        <v>472</v>
+      </c>
+      <c r="B358" t="s">
+        <v>38</v>
+      </c>
+      <c r="C358" t="s">
+        <v>391</v>
+      </c>
+      <c r="D358" t="s">
+        <v>410</v>
+      </c>
+      <c r="E358" t="s">
+        <v>349</v>
+      </c>
+      <c r="F358" t="s">
+        <v>350</v>
+      </c>
+      <c r="G358" t="s">
+        <v>546</v>
+      </c>
+      <c r="H358" t="s">
+        <v>583</v>
+      </c>
+      <c r="I358" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J358" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K358" t="s">
+        <v>391</v>
+      </c>
+      <c r="L358" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="359" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A359" t="s">
+        <v>473</v>
+      </c>
+      <c r="B359" t="s">
+        <v>372</v>
+      </c>
+      <c r="C359" t="s">
+        <v>396</v>
+      </c>
+      <c r="D359" t="s">
+        <v>410</v>
+      </c>
+      <c r="E359" t="s">
+        <v>373</v>
+      </c>
+      <c r="F359" t="s">
+        <v>374</v>
+      </c>
+      <c r="G359" t="s">
+        <v>394</v>
+      </c>
+      <c r="H359" t="s">
+        <v>584</v>
+      </c>
+      <c r="I359" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J359" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K359" t="s">
+        <v>396</v>
+      </c>
+      <c r="L359" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="360" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A360" t="s">
+        <v>474</v>
+      </c>
+      <c r="B360" t="s">
+        <v>446</v>
+      </c>
+      <c r="C360" t="s">
+        <v>483</v>
+      </c>
+      <c r="D360" t="s">
+        <v>410</v>
+      </c>
+      <c r="E360" t="s">
+        <v>520</v>
+      </c>
+      <c r="F360" t="s">
+        <v>557</v>
+      </c>
+      <c r="G360" t="s">
+        <v>547</v>
+      </c>
+      <c r="H360" t="s">
+        <v>585</v>
+      </c>
+      <c r="I360" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J360" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K360" t="s">
+        <v>483</v>
+      </c>
+      <c r="L360" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="361" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A361" t="s">
+        <v>437</v>
+      </c>
+      <c r="B361" t="s">
+        <v>64</v>
+      </c>
+      <c r="C361" t="s">
+        <v>369</v>
+      </c>
+      <c r="D361" t="s">
+        <v>423</v>
+      </c>
+      <c r="E361" t="s">
+        <v>370</v>
+      </c>
+      <c r="F361" t="s">
+        <v>371</v>
+      </c>
+      <c r="G361" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="H361" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="I361" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J361" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K361" t="s">
+        <v>369</v>
+      </c>
+      <c r="L361" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="362" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A362" t="s">
+        <v>438</v>
+      </c>
+      <c r="B362" t="s">
+        <v>38</v>
+      </c>
+      <c r="C362" t="s">
+        <v>391</v>
+      </c>
+      <c r="D362" t="s">
+        <v>423</v>
+      </c>
+      <c r="E362" t="s">
+        <v>349</v>
+      </c>
+      <c r="F362" t="s">
+        <v>350</v>
+      </c>
+      <c r="G362" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="H362" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="I362" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J362" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K362" t="s">
+        <v>391</v>
+      </c>
+      <c r="L362" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="363" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A363" t="s">
+        <v>439</v>
+      </c>
+      <c r="B363" t="s">
+        <v>297</v>
+      </c>
+      <c r="C363" t="s">
+        <v>298</v>
+      </c>
+      <c r="D363" t="s">
+        <v>423</v>
+      </c>
+      <c r="E363" t="s">
+        <v>299</v>
+      </c>
+      <c r="F363" t="s">
+        <v>300</v>
+      </c>
+      <c r="G363" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="H363" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="I363" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J363" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K363" t="s">
+        <v>298</v>
+      </c>
+      <c r="L363" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="364" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A364" t="s">
+        <v>440</v>
+      </c>
+      <c r="B364" t="s">
+        <v>148</v>
+      </c>
+      <c r="C364" t="s">
+        <v>149</v>
+      </c>
+      <c r="D364" t="s">
+        <v>423</v>
+      </c>
+      <c r="E364" t="s">
+        <v>411</v>
+      </c>
+      <c r="F364" t="s">
+        <v>412</v>
+      </c>
+      <c r="G364" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="H364" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="I364" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J364" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K364" t="s">
+        <v>149</v>
+      </c>
+      <c r="L364" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="365" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A365" t="s">
+        <v>441</v>
+      </c>
+      <c r="B365" t="s">
+        <v>380</v>
+      </c>
+      <c r="C365" t="s">
+        <v>398</v>
+      </c>
+      <c r="D365" t="s">
+        <v>423</v>
+      </c>
+      <c r="E365" t="s">
+        <v>381</v>
+      </c>
+      <c r="F365" t="s">
+        <v>382</v>
+      </c>
+      <c r="G365" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="H365" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="I365" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J365" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K365" t="s">
+        <v>398</v>
+      </c>
+      <c r="L365" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="366" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A366" t="s">
+        <v>442</v>
+      </c>
+      <c r="B366" t="s">
+        <v>403</v>
+      </c>
+      <c r="C366" t="s">
+        <v>404</v>
+      </c>
+      <c r="D366" t="s">
+        <v>423</v>
+      </c>
+      <c r="E366" t="s">
+        <v>424</v>
+      </c>
+      <c r="F366" t="s">
+        <v>425</v>
+      </c>
+      <c r="G366" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="H366" s="2" t="s">
+        <v>553</v>
+      </c>
+      <c r="I366" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J366" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K366" t="s">
+        <v>404</v>
+      </c>
+      <c r="L366" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="367" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A367" t="s">
+        <v>443</v>
+      </c>
+      <c r="B367" t="s">
+        <v>229</v>
+      </c>
+      <c r="C367" t="s">
+        <v>348</v>
+      </c>
+      <c r="D367" t="s">
+        <v>423</v>
+      </c>
+      <c r="E367" t="s">
+        <v>421</v>
+      </c>
+      <c r="F367" t="s">
+        <v>422</v>
+      </c>
+      <c r="G367" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="H367" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="I367" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J367" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K367" t="s">
+        <v>348</v>
+      </c>
+      <c r="L367" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="368" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A368" t="s">
+        <v>444</v>
+      </c>
+      <c r="B368" t="s">
+        <v>119</v>
+      </c>
+      <c r="C368" t="s">
+        <v>379</v>
+      </c>
+      <c r="D368" t="s">
+        <v>423</v>
+      </c>
+      <c r="E368" t="s">
+        <v>159</v>
+      </c>
+      <c r="F368" t="s">
+        <v>160</v>
+      </c>
+      <c r="G368" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="H368" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="I368" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J368" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K368" t="s">
+        <v>379</v>
+      </c>
+      <c r="L368" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="369" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A369" t="s">
+        <v>445</v>
+      </c>
+      <c r="B369" t="s">
+        <v>211</v>
+      </c>
+      <c r="C369" t="s">
+        <v>212</v>
+      </c>
+      <c r="D369" t="s">
+        <v>423</v>
+      </c>
+      <c r="E369" t="s">
+        <v>213</v>
+      </c>
+      <c r="F369" t="s">
+        <v>214</v>
+      </c>
+      <c r="G369" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="H369" s="2" t="s">
+        <v>556</v>
+      </c>
+      <c r="I369" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J369" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K369" t="s">
+        <v>212</v>
+      </c>
+      <c r="L369" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="370" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A370" t="s">
+        <v>446</v>
+      </c>
+      <c r="B370" t="s">
+        <v>229</v>
+      </c>
+      <c r="C370" t="s">
+        <v>348</v>
+      </c>
+      <c r="D370" t="s">
+        <v>423</v>
+      </c>
+      <c r="E370" t="s">
+        <v>421</v>
+      </c>
+      <c r="F370" t="s">
+        <v>422</v>
+      </c>
+      <c r="G370" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="H370" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="I370" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J370" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K370" t="s">
+        <v>348</v>
+      </c>
+      <c r="L370" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="371" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A371" t="s">
+        <v>447</v>
+      </c>
+      <c r="B371" t="s">
+        <v>229</v>
+      </c>
+      <c r="C371" t="s">
+        <v>348</v>
+      </c>
+      <c r="D371" t="s">
+        <v>423</v>
+      </c>
+      <c r="E371" t="s">
+        <v>421</v>
+      </c>
+      <c r="F371" t="s">
+        <v>422</v>
+      </c>
+      <c r="G371" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="H371" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="I371" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J371" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K371" t="s">
+        <v>348</v>
+      </c>
+      <c r="L371" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="372" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A372" t="s">
+        <v>448</v>
+      </c>
+      <c r="B372" t="s">
+        <v>229</v>
+      </c>
+      <c r="C372" t="s">
+        <v>348</v>
+      </c>
+      <c r="D372" t="s">
+        <v>423</v>
+      </c>
+      <c r="E372" t="s">
+        <v>421</v>
+      </c>
+      <c r="F372" t="s">
+        <v>422</v>
+      </c>
+      <c r="G372" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="H372" s="2" t="s">
+        <v>559</v>
+      </c>
+      <c r="I372" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J372" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K372" t="s">
+        <v>348</v>
+      </c>
+      <c r="L372" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="373" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A373" t="s">
+        <v>449</v>
+      </c>
+      <c r="B373" t="s">
+        <v>20</v>
+      </c>
+      <c r="C373" t="s">
+        <v>399</v>
+      </c>
+      <c r="D373" t="s">
+        <v>423</v>
+      </c>
+      <c r="E373" t="s">
+        <v>150</v>
+      </c>
+      <c r="F373" t="s">
+        <v>151</v>
+      </c>
+      <c r="G373" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="H373" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="I373" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J373" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K373" t="s">
+        <v>399</v>
+      </c>
+      <c r="L373" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="374" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A374" t="s">
+        <v>450</v>
+      </c>
+      <c r="B374" t="s">
+        <v>380</v>
+      </c>
+      <c r="C374" t="s">
+        <v>398</v>
+      </c>
+      <c r="D374" t="s">
+        <v>423</v>
+      </c>
+      <c r="E374" t="s">
+        <v>381</v>
+      </c>
+      <c r="F374" t="s">
+        <v>382</v>
+      </c>
+      <c r="G374" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="H374" s="2" t="s">
+        <v>561</v>
+      </c>
+      <c r="I374" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J374" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K374" t="s">
+        <v>398</v>
+      </c>
+      <c r="L374" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="375" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A375" t="s">
+        <v>451</v>
+      </c>
+      <c r="B375" t="s">
+        <v>380</v>
+      </c>
+      <c r="C375" t="s">
+        <v>398</v>
+      </c>
+      <c r="D375" t="s">
+        <v>423</v>
+      </c>
+      <c r="E375" t="s">
+        <v>381</v>
+      </c>
+      <c r="F375" t="s">
+        <v>382</v>
+      </c>
+      <c r="G375" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="H375" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="I375" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J375" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K375" t="s">
+        <v>398</v>
+      </c>
+      <c r="L375" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="376" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A376" t="s">
+        <v>452</v>
+      </c>
+      <c r="B376" t="s">
+        <v>64</v>
+      </c>
+      <c r="C376" t="s">
+        <v>369</v>
+      </c>
+      <c r="D376" t="s">
+        <v>423</v>
+      </c>
+      <c r="E376" t="s">
+        <v>370</v>
+      </c>
+      <c r="F376" t="s">
+        <v>371</v>
+      </c>
+      <c r="G376" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="H376" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="I376" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J376" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K376" t="s">
+        <v>369</v>
+      </c>
+      <c r="L376" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="377" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A377" t="s">
+        <v>453</v>
+      </c>
+      <c r="B377" t="s">
+        <v>229</v>
+      </c>
+      <c r="C377" t="s">
+        <v>348</v>
+      </c>
+      <c r="D377" t="s">
+        <v>423</v>
+      </c>
+      <c r="E377" t="s">
+        <v>421</v>
+      </c>
+      <c r="F377" t="s">
+        <v>422</v>
+      </c>
+      <c r="G377" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="H377" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="I377" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J377" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K377" t="s">
+        <v>348</v>
+      </c>
+      <c r="L377" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="378" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A378" t="s">
+        <v>454</v>
+      </c>
+      <c r="B378" t="s">
+        <v>95</v>
+      </c>
+      <c r="C378" t="s">
+        <v>401</v>
+      </c>
+      <c r="D378" t="s">
+        <v>423</v>
+      </c>
+      <c r="E378" t="s">
+        <v>152</v>
+      </c>
+      <c r="F378" t="s">
+        <v>153</v>
+      </c>
+      <c r="G378" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="H378" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="I378" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J378" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K378" t="s">
+        <v>401</v>
+      </c>
+      <c r="L378" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="379" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A379" t="s">
+        <v>455</v>
+      </c>
+      <c r="B379" t="s">
+        <v>95</v>
+      </c>
+      <c r="C379" t="s">
+        <v>401</v>
+      </c>
+      <c r="D379" t="s">
+        <v>423</v>
+      </c>
+      <c r="E379" t="s">
+        <v>152</v>
+      </c>
+      <c r="F379" t="s">
+        <v>153</v>
+      </c>
+      <c r="G379" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="H379" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="I379" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J379" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K379" t="s">
+        <v>401</v>
+      </c>
+      <c r="L379" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="380" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A380" t="s">
+        <v>456</v>
+      </c>
+      <c r="B380" t="s">
+        <v>380</v>
+      </c>
+      <c r="C380" t="s">
+        <v>398</v>
+      </c>
+      <c r="D380" t="s">
+        <v>423</v>
+      </c>
+      <c r="E380" t="s">
+        <v>381</v>
+      </c>
+      <c r="F380" t="s">
+        <v>382</v>
+      </c>
+      <c r="G380" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="H380" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="I380" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J380" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K380" t="s">
+        <v>398</v>
+      </c>
+      <c r="L380" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="381" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A381" t="s">
+        <v>457</v>
+      </c>
+      <c r="B381" t="s">
+        <v>229</v>
+      </c>
+      <c r="C381" t="s">
+        <v>348</v>
+      </c>
+      <c r="D381" t="s">
+        <v>423</v>
+      </c>
+      <c r="E381" t="s">
+        <v>421</v>
+      </c>
+      <c r="F381" t="s">
+        <v>422</v>
+      </c>
+      <c r="G381" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="H381" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="I381" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J381" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K381" t="s">
+        <v>348</v>
+      </c>
+      <c r="L381" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="382" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A382" t="s">
+        <v>458</v>
+      </c>
+      <c r="B382" t="s">
+        <v>448</v>
+      </c>
+      <c r="C382" t="s">
+        <v>485</v>
+      </c>
+      <c r="D382" t="s">
+        <v>423</v>
+      </c>
+      <c r="E382" t="s">
+        <v>522</v>
+      </c>
+      <c r="F382" t="s">
+        <v>559</v>
+      </c>
+      <c r="G382" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="H382" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="I382" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J382" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K382" t="s">
+        <v>485</v>
+      </c>
+      <c r="L382" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="383" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A383" t="s">
+        <v>459</v>
+      </c>
+      <c r="B383" t="s">
+        <v>229</v>
+      </c>
+      <c r="C383" t="s">
+        <v>348</v>
+      </c>
+      <c r="D383" t="s">
+        <v>423</v>
+      </c>
+      <c r="E383" t="s">
+        <v>421</v>
+      </c>
+      <c r="F383" t="s">
+        <v>422</v>
+      </c>
+      <c r="G383" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="H383" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="I383" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J383" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K383" t="s">
+        <v>348</v>
+      </c>
+      <c r="L383" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="384" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A384" t="s">
+        <v>460</v>
+      </c>
+      <c r="B384" t="s">
+        <v>88</v>
+      </c>
+      <c r="C384" t="s">
+        <v>402</v>
+      </c>
+      <c r="D384" t="s">
+        <v>423</v>
+      </c>
+      <c r="E384" t="s">
+        <v>154</v>
+      </c>
+      <c r="F384" t="s">
+        <v>155</v>
+      </c>
+      <c r="G384" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="H384" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="I384" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J384" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K384" t="s">
+        <v>402</v>
+      </c>
+      <c r="L384" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="385" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A385" t="s">
+        <v>461</v>
+      </c>
+      <c r="B385" t="s">
+        <v>47</v>
+      </c>
+      <c r="C385" t="s">
+        <v>48</v>
+      </c>
+      <c r="D385" t="s">
+        <v>423</v>
+      </c>
+      <c r="E385" t="s">
+        <v>49</v>
+      </c>
+      <c r="F385" t="s">
+        <v>50</v>
+      </c>
+      <c r="G385" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="H385" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="I385" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J385" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K385" t="s">
+        <v>48</v>
+      </c>
+      <c r="L385" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="386" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A386" t="s">
+        <v>462</v>
+      </c>
+      <c r="B386" t="s">
+        <v>380</v>
+      </c>
+      <c r="C386" t="s">
+        <v>398</v>
+      </c>
+      <c r="D386" t="s">
+        <v>423</v>
+      </c>
+      <c r="E386" t="s">
+        <v>381</v>
+      </c>
+      <c r="F386" t="s">
+        <v>382</v>
+      </c>
+      <c r="G386" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="H386" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="I386" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J386" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K386" t="s">
+        <v>398</v>
+      </c>
+      <c r="L386" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="387" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A387" t="s">
+        <v>463</v>
+      </c>
+      <c r="B387" t="s">
+        <v>229</v>
+      </c>
+      <c r="C387" t="s">
+        <v>348</v>
+      </c>
+      <c r="D387" t="s">
+        <v>423</v>
+      </c>
+      <c r="E387" t="s">
+        <v>421</v>
+      </c>
+      <c r="F387" t="s">
+        <v>422</v>
+      </c>
+      <c r="G387" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="H387" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="I387" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J387" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K387" t="s">
+        <v>348</v>
+      </c>
+      <c r="L387" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="388" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A388" t="s">
+        <v>464</v>
+      </c>
+      <c r="B388" t="s">
+        <v>165</v>
+      </c>
+      <c r="C388" t="s">
+        <v>308</v>
+      </c>
+      <c r="D388" t="s">
+        <v>423</v>
+      </c>
+      <c r="E388" t="s">
+        <v>309</v>
+      </c>
+      <c r="F388" t="s">
+        <v>310</v>
+      </c>
+      <c r="G388" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="H388" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="I388" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J388" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K388" t="s">
+        <v>308</v>
+      </c>
+      <c r="L388" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="389" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A389" t="s">
+        <v>465</v>
+      </c>
+      <c r="B389" t="s">
+        <v>165</v>
+      </c>
+      <c r="C389" t="s">
+        <v>308</v>
+      </c>
+      <c r="D389" t="s">
+        <v>423</v>
+      </c>
+      <c r="E389" t="s">
+        <v>309</v>
+      </c>
+      <c r="F389" t="s">
+        <v>310</v>
+      </c>
+      <c r="G389" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="H389" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="I389" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J389" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K389" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="L389" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="390" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A390" t="s">
+        <v>466</v>
+      </c>
+      <c r="B390" t="s">
+        <v>229</v>
+      </c>
+      <c r="C390" t="s">
+        <v>348</v>
+      </c>
+      <c r="D390" t="s">
+        <v>423</v>
+      </c>
+      <c r="E390" t="s">
+        <v>421</v>
+      </c>
+      <c r="F390" t="s">
+        <v>422</v>
+      </c>
+      <c r="G390" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="H390" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="I390" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J390" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K390" t="s">
+        <v>348</v>
+      </c>
+      <c r="L390" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="391" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A391" t="s">
+        <v>467</v>
+      </c>
+      <c r="B391" t="s">
+        <v>448</v>
+      </c>
+      <c r="C391" t="s">
+        <v>485</v>
+      </c>
+      <c r="D391" t="s">
+        <v>423</v>
+      </c>
+      <c r="E391" t="s">
+        <v>522</v>
+      </c>
+      <c r="F391" t="s">
+        <v>559</v>
+      </c>
+      <c r="G391" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="H391" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="I391" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J391" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K391" t="s">
+        <v>485</v>
+      </c>
+      <c r="L391" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="392" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A392" t="s">
+        <v>468</v>
+      </c>
+      <c r="B392" t="s">
+        <v>297</v>
+      </c>
+      <c r="C392" t="s">
+        <v>298</v>
+      </c>
+      <c r="D392" t="s">
+        <v>423</v>
+      </c>
+      <c r="E392" t="s">
+        <v>299</v>
+      </c>
+      <c r="F392" t="s">
+        <v>300</v>
+      </c>
+      <c r="G392" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="H392" s="2" t="s">
+        <v>579</v>
+      </c>
+      <c r="I392" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J392" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K392" t="s">
+        <v>298</v>
+      </c>
+      <c r="L392" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="393" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A393" t="s">
+        <v>469</v>
+      </c>
+      <c r="B393" t="s">
+        <v>88</v>
+      </c>
+      <c r="C393" t="s">
+        <v>402</v>
+      </c>
+      <c r="D393" t="s">
+        <v>423</v>
+      </c>
+      <c r="E393" t="s">
+        <v>154</v>
+      </c>
+      <c r="F393" t="s">
+        <v>155</v>
+      </c>
+      <c r="G393" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="H393" s="2" t="s">
+        <v>580</v>
+      </c>
+      <c r="I393" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J393" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K393" t="s">
+        <v>402</v>
+      </c>
+      <c r="L393" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="394" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A394" t="s">
+        <v>470</v>
+      </c>
+      <c r="B394" t="s">
+        <v>165</v>
+      </c>
+      <c r="C394" t="s">
+        <v>308</v>
+      </c>
+      <c r="D394" t="s">
+        <v>423</v>
+      </c>
+      <c r="E394" t="s">
+        <v>309</v>
+      </c>
+      <c r="F394" t="s">
+        <v>310</v>
+      </c>
+      <c r="G394" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="H394" s="2" t="s">
+        <v>581</v>
+      </c>
+      <c r="I394" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J394" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K394" t="s">
+        <v>308</v>
+      </c>
+      <c r="L394" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="395" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A395" t="s">
+        <v>471</v>
+      </c>
+      <c r="B395" t="s">
+        <v>229</v>
+      </c>
+      <c r="C395" t="s">
+        <v>348</v>
+      </c>
+      <c r="D395" t="s">
+        <v>423</v>
+      </c>
+      <c r="E395" t="s">
+        <v>421</v>
+      </c>
+      <c r="F395" t="s">
+        <v>422</v>
+      </c>
+      <c r="G395" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="H395" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="I395" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J395" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K395" t="s">
+        <v>348</v>
+      </c>
+      <c r="L395" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="396" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A396" t="s">
+        <v>472</v>
+      </c>
+      <c r="B396" t="s">
+        <v>229</v>
+      </c>
+      <c r="C396" t="s">
+        <v>348</v>
+      </c>
+      <c r="D396" t="s">
+        <v>423</v>
+      </c>
+      <c r="E396" t="s">
+        <v>421</v>
+      </c>
+      <c r="F396" t="s">
+        <v>422</v>
+      </c>
+      <c r="G396" s="2" t="s">
+        <v>546</v>
+      </c>
+      <c r="H396" s="2" t="s">
+        <v>583</v>
+      </c>
+      <c r="I396" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J396" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K396" t="s">
+        <v>348</v>
+      </c>
+      <c r="L396" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="397" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A397" t="s">
+        <v>473</v>
+      </c>
+      <c r="B397" t="s">
+        <v>64</v>
+      </c>
+      <c r="C397" t="s">
+        <v>369</v>
+      </c>
+      <c r="D397" t="s">
+        <v>423</v>
+      </c>
+      <c r="E397" t="s">
+        <v>370</v>
+      </c>
+      <c r="F397" t="s">
+        <v>371</v>
+      </c>
+      <c r="G397" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="H397" s="2" t="s">
+        <v>584</v>
+      </c>
+      <c r="I397" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J397" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K397" t="s">
+        <v>369</v>
+      </c>
+      <c r="L397" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="398" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A398" t="s">
+        <v>474</v>
+      </c>
+      <c r="B398" t="s">
+        <v>229</v>
+      </c>
+      <c r="C398" t="s">
+        <v>348</v>
+      </c>
+      <c r="D398" t="s">
+        <v>423</v>
+      </c>
+      <c r="E398" t="s">
+        <v>421</v>
+      </c>
+      <c r="F398" t="s">
+        <v>422</v>
+      </c>
+      <c r="G398" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="H398" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="I398" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J398" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K398" t="s">
+        <v>348</v>
+      </c>
+      <c r="L398" t="s">
         <v>428</v>
       </c>
     </row>
@@ -12831,10 +17369,11 @@
     <hyperlink ref="K144" r:id="rId11" xr:uid="{238DCD60-B5B6-4BD5-B2D6-48536AF9F667}"/>
     <hyperlink ref="K146" r:id="rId12" xr:uid="{FA0BE04D-ACA5-4D25-B3BC-690007E40812}"/>
     <hyperlink ref="K256" r:id="rId13" xr:uid="{80DA185F-D7E7-4537-A466-7ADC2B6C98BE}"/>
+    <hyperlink ref="K389" r:id="rId14" xr:uid="{9DE20185-22E7-4B36-AA47-9396DC30E6D9}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <tableParts count="1">
-    <tablePart r:id="rId14"/>
+    <tablePart r:id="rId15"/>
   </tableParts>
 </worksheet>
 </file>
--- a/lista_emails.xlsx
+++ b/lista_emails.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Y:\Wagner\Programações\RH\Questionário ENIND\App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F77E2AA-06DF-4850-8047-F0F39D260184}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1555464B-3D82-46A5-8903-00C7E46BC366}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4ABFC600-D865-440E-A0ED-FE29CA4E2163}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5925" uniqueCount="739">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5926" uniqueCount="740">
   <si>
     <t>Participante</t>
   </si>
@@ -2263,6 +2263,9 @@
   </si>
   <si>
     <t>Sql Atuliza_Email</t>
+  </si>
+  <si>
+    <t>Coluna1</t>
   </si>
 </sst>
 </file>
@@ -2367,14 +2370,6 @@
   </cellStyles>
   <dxfs count="13">
     <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <font>
         <color rgb="FF006100"/>
       </font>
@@ -2393,6 +2388,9 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -2442,9 +2440,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F3ADC3C7-E9A3-417B-9D36-7AAC353CADC8}" name="Tabela1" displayName="Tabela1" ref="A1:P391" totalsRowShown="0">
-  <autoFilter ref="A1:P391" xr:uid="{F3ADC3C7-E9A3-417B-9D36-7AAC353CADC8}"/>
-  <tableColumns count="16">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F3ADC3C7-E9A3-417B-9D36-7AAC353CADC8}" name="Tabela1" displayName="Tabela1" ref="A1:Q391" totalsRowShown="0">
+  <autoFilter ref="A1:Q391" xr:uid="{F3ADC3C7-E9A3-417B-9D36-7AAC353CADC8}"/>
+  <tableColumns count="17">
     <tableColumn id="1" xr3:uid="{1EE8BBD9-CC9C-488B-9D75-6363CD6C86F1}" name="Participante"/>
     <tableColumn id="2" xr3:uid="{D83259D8-309A-419C-B320-342D6BCF6C73}" name="Avaliador"/>
     <tableColumn id="3" xr3:uid="{F718E0AE-C693-46A2-BFA3-CF2210C246D1}" name="Email"/>
@@ -2476,6 +2474,9 @@
     </tableColumn>
     <tableColumn id="16" xr3:uid="{C6408CAE-2C43-411D-B4E3-2615A2678B61}" name="Atualizado?" dataDxfId="3">
       <calculatedColumnFormula>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="17" xr3:uid="{0B58B674-A96E-4F08-9366-C51A679445EC}" name="Coluna1" dataDxfId="2">
+      <calculatedColumnFormula>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -2800,7 +2801,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCA9C2C1-2B6C-4947-A048-82C1CA408DE6}">
   <sheetPr codeName="Planilha1"/>
-  <dimension ref="A1:P391"/>
+  <dimension ref="A1:Q391"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="37.5703125" bestFit="1" customWidth="1"/>
@@ -2817,9 +2818,10 @@
     <col min="14" max="14" width="37.5703125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="39.85546875" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -2868,8 +2870,11 @@
       <c r="P1" t="s">
         <v>733</v>
       </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q1" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
@@ -2926,8 +2931,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q2" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
@@ -2984,8 +2993,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q3" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>19</v>
       </c>
@@ -3042,8 +3055,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q4" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>316</v>
       </c>
@@ -3100,8 +3117,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q5" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>27</v>
       </c>
@@ -3158,8 +3179,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q6" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>318</v>
       </c>
@@ -3216,8 +3241,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q7" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>317</v>
       </c>
@@ -3274,8 +3303,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q8" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>33</v>
       </c>
@@ -3332,8 +3365,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q9" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>319</v>
       </c>
@@ -3390,8 +3427,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q10" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>320</v>
       </c>
@@ -3448,8 +3489,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q11" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>322</v>
       </c>
@@ -3506,8 +3551,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q12" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>148</v>
       </c>
@@ -3564,8 +3613,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q13" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>193</v>
       </c>
@@ -3622,8 +3675,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q14" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>237</v>
       </c>
@@ -3680,8 +3737,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q15" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>251</v>
       </c>
@@ -3738,8 +3799,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q16" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>281</v>
       </c>
@@ -3796,8 +3861,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q17" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>321</v>
       </c>
@@ -3854,8 +3923,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q18" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>65</v>
       </c>
@@ -3913,8 +3986,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q19" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>38</v>
       </c>
@@ -3971,8 +4048,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q20" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>319</v>
       </c>
@@ -4029,8 +4110,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q21" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>323</v>
       </c>
@@ -4087,8 +4172,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q22" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>337</v>
       </c>
@@ -4145,8 +4234,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q23" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>346</v>
       </c>
@@ -4203,8 +4296,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q24" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>340</v>
       </c>
@@ -4261,8 +4358,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q25" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>336</v>
       </c>
@@ -4320,8 +4421,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q26" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>323</v>
       </c>
@@ -4378,8 +4483,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q27" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>324</v>
       </c>
@@ -4436,8 +4545,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q28" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>43</v>
       </c>
@@ -4494,8 +4607,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q29" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>325</v>
       </c>
@@ -4552,8 +4669,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q30" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>322</v>
       </c>
@@ -4610,8 +4731,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q31" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>336</v>
       </c>
@@ -4669,8 +4794,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q32" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>342</v>
       </c>
@@ -4727,8 +4856,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q33" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>350</v>
       </c>
@@ -4785,8 +4918,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q34" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>353</v>
       </c>
@@ -4843,8 +4980,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q35" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>326</v>
       </c>
@@ -4901,8 +5042,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q36" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>48</v>
       </c>
@@ -4959,8 +5104,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q37" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>327</v>
       </c>
@@ -5017,8 +5166,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q38" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>340</v>
       </c>
@@ -5075,8 +5228,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q39" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>337</v>
       </c>
@@ -5133,8 +5290,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q40" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>346</v>
       </c>
@@ -5191,8 +5352,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q41" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>54</v>
       </c>
@@ -5249,8 +5414,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q42" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>59</v>
       </c>
@@ -5307,8 +5476,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q43" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>63</v>
       </c>
@@ -5365,8 +5538,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q44" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>68</v>
       </c>
@@ -5423,8 +5600,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q45" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>102</v>
       </c>
@@ -5481,8 +5662,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q46" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>25</v>
       </c>
@@ -5540,8 +5725,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q47" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>65</v>
       </c>
@@ -5599,8 +5788,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q48" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>73</v>
       </c>
@@ -5657,8 +5850,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q49" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>79</v>
       </c>
@@ -5715,8 +5912,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q50" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>88</v>
       </c>
@@ -5773,8 +5974,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q51" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>83</v>
       </c>
@@ -5831,8 +6036,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q52" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>86</v>
       </c>
@@ -5889,8 +6098,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q53" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>329</v>
       </c>
@@ -5926,7 +6139,7 @@
         <v>16</v>
       </c>
       <c r="K54" t="s">
-        <v>366</v>
+        <v>428</v>
       </c>
       <c r="L54" t="s">
         <v>307</v>
@@ -5947,8 +6160,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q54" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>91</v>
       </c>
@@ -6005,8 +6222,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q55" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>37</v>
       </c>
@@ -6063,8 +6284,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q56" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>97</v>
       </c>
@@ -6121,8 +6346,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q57" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>99</v>
       </c>
@@ -6179,8 +6408,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q58" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>57</v>
       </c>
@@ -6237,8 +6470,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q59" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>102</v>
       </c>
@@ -6295,8 +6532,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q60" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>104</v>
       </c>
@@ -6353,8 +6594,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q61" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>32</v>
       </c>
@@ -6411,8 +6656,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q62" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>148</v>
       </c>
@@ -6469,8 +6718,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q63" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>237</v>
       </c>
@@ -6527,8 +6780,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q64" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>14</v>
       </c>
@@ -6585,8 +6842,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q65" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>13</v>
       </c>
@@ -6643,8 +6904,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="67" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q66" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>109</v>
       </c>
@@ -6701,8 +6966,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="68" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q67" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>330</v>
       </c>
@@ -6759,8 +7028,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="69" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q68" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>38</v>
       </c>
@@ -6817,8 +7090,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="70" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q69" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>94</v>
       </c>
@@ -6875,8 +7152,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="71" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q70" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>15</v>
       </c>
@@ -6933,8 +7214,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="72" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q71" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>77</v>
       </c>
@@ -6991,8 +7276,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="73" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q72" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
         <v>71</v>
       </c>
@@ -7049,8 +7338,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="74" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q73" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>209</v>
       </c>
@@ -7107,8 +7400,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="75" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q74" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>155</v>
       </c>
@@ -7165,8 +7462,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="76" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q75" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>272</v>
       </c>
@@ -7223,8 +7524,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="77" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q76" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>325</v>
       </c>
@@ -7281,8 +7586,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="78" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q77" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>327</v>
       </c>
@@ -7339,8 +7648,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="79" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q78" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>319</v>
       </c>
@@ -7397,8 +7710,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="80" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q79" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
         <v>31</v>
       </c>
@@ -7456,8 +7773,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="81" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q80" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>274</v>
       </c>
@@ -7515,8 +7836,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="82" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q81" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
         <v>117</v>
       </c>
@@ -7574,8 +7899,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="83" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q82" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
         <v>52</v>
       </c>
@@ -7633,8 +7962,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="84" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q83" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
         <v>120</v>
       </c>
@@ -7691,8 +8024,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="85" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q84" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
         <v>10</v>
       </c>
@@ -7749,8 +8086,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="86" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q85" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
         <v>126</v>
       </c>
@@ -7786,7 +8127,7 @@
         <v>6</v>
       </c>
       <c r="K86" t="s">
-        <v>124</v>
+        <v>430</v>
       </c>
       <c r="L86" t="s">
         <v>307</v>
@@ -7807,8 +8148,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="87" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q86" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
         <v>3</v>
       </c>
@@ -7865,8 +8210,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="88" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q87" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>9</v>
       </c>
@@ -7923,8 +8272,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="89" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q88" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
         <v>126</v>
       </c>
@@ -7981,8 +8334,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="90" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q89" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
         <v>72</v>
       </c>
@@ -8018,7 +8375,7 @@
         <v>16</v>
       </c>
       <c r="K90" t="s">
-        <v>124</v>
+        <v>430</v>
       </c>
       <c r="L90" t="s">
         <v>308</v>
@@ -8039,8 +8396,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="91" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q90" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
         <v>76</v>
       </c>
@@ -8076,7 +8437,7 @@
         <v>16</v>
       </c>
       <c r="K91" t="s">
-        <v>124</v>
+        <v>430</v>
       </c>
       <c r="L91" t="s">
         <v>308</v>
@@ -8097,8 +8458,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="92" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q91" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>47</v>
       </c>
@@ -8155,8 +8520,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="93" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q92" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>78</v>
       </c>
@@ -8192,7 +8561,7 @@
         <v>16</v>
       </c>
       <c r="K93" t="s">
-        <v>124</v>
+        <v>430</v>
       </c>
       <c r="L93" t="s">
         <v>308</v>
@@ -8213,8 +8582,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="94" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q93" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>82</v>
       </c>
@@ -8250,7 +8623,7 @@
         <v>16</v>
       </c>
       <c r="K94" t="s">
-        <v>124</v>
+        <v>430</v>
       </c>
       <c r="L94" t="s">
         <v>308</v>
@@ -8271,8 +8644,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="95" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q94" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
         <v>85</v>
       </c>
@@ -8308,7 +8685,7 @@
         <v>16</v>
       </c>
       <c r="K95" t="s">
-        <v>124</v>
+        <v>430</v>
       </c>
       <c r="L95" t="s">
         <v>308</v>
@@ -8329,8 +8706,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="96" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q95" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>129</v>
       </c>
@@ -8387,8 +8768,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="97" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q96" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>51</v>
       </c>
@@ -8445,8 +8830,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="98" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q97" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>277</v>
       </c>
@@ -8503,8 +8892,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="99" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q98" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
         <v>72</v>
       </c>
@@ -8561,8 +8954,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="100" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q99" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>76</v>
       </c>
@@ -8619,8 +9016,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="101" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q100" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>78</v>
       </c>
@@ -8677,8 +9078,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="102" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q101" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>82</v>
       </c>
@@ -8735,8 +9140,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="103" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q102" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>85</v>
       </c>
@@ -8793,8 +9202,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="104" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q103" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
         <v>18</v>
       </c>
@@ -8851,8 +9264,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="105" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q104" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
         <v>27</v>
       </c>
@@ -8909,8 +9326,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="106" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q105" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
         <v>17</v>
       </c>
@@ -8967,8 +9388,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="107" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q106" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
         <v>141</v>
       </c>
@@ -9025,8 +9450,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="108" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q107" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
         <v>41</v>
       </c>
@@ -9083,8 +9512,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="109" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q108" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
         <v>144</v>
       </c>
@@ -9141,8 +9574,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="110" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q109" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>58</v>
       </c>
@@ -9199,8 +9636,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="111" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q110" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
         <v>193</v>
       </c>
@@ -9257,8 +9698,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="112" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q111" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>251</v>
       </c>
@@ -9315,8 +9760,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="113" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q112" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>148</v>
       </c>
@@ -9373,8 +9822,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="114" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q113" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>151</v>
       </c>
@@ -9431,8 +9884,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="115" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q114" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>167</v>
       </c>
@@ -9489,8 +9946,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="116" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q115" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>324</v>
       </c>
@@ -9547,8 +10008,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="117" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q116" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
         <v>151</v>
       </c>
@@ -9605,8 +10070,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="118" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q117" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
         <v>155</v>
       </c>
@@ -9663,8 +10132,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="119" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q118" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
         <v>33</v>
       </c>
@@ -9721,8 +10194,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="120" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q119" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
         <v>147</v>
       </c>
@@ -9779,8 +10256,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="121" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q120" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
         <v>169</v>
       </c>
@@ -9837,8 +10318,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="122" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q121" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>257</v>
       </c>
@@ -9896,8 +10381,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="123" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q122" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>240</v>
       </c>
@@ -9955,8 +10444,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="124" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q123" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
         <v>147</v>
       </c>
@@ -10013,8 +10506,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="125" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q124" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>18</v>
       </c>
@@ -10071,8 +10568,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="126" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q125" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
         <v>19</v>
       </c>
@@ -10130,8 +10631,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="127" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q126" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
         <v>159</v>
       </c>
@@ -10189,8 +10694,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="128" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q127" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
         <v>161</v>
       </c>
@@ -10247,8 +10756,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="129" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q128" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>318</v>
       </c>
@@ -10305,8 +10818,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="130" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q129" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>347</v>
       </c>
@@ -10363,8 +10880,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="131" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q130" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>345</v>
       </c>
@@ -10422,8 +10943,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="132" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q131" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
         <v>159</v>
       </c>
@@ -10480,8 +11005,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="133" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q132" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
         <v>117</v>
       </c>
@@ -10538,8 +11067,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="134" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q133" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
         <v>14</v>
       </c>
@@ -10597,8 +11130,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="135" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q134" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="135" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
         <v>167</v>
       </c>
@@ -10655,8 +11192,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="136" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q135" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
         <v>13</v>
       </c>
@@ -10713,8 +11254,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="137" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q136" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
         <v>169</v>
       </c>
@@ -10771,8 +11316,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="138" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q137" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>332</v>
       </c>
@@ -10829,8 +11378,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="139" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q138" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>338</v>
       </c>
@@ -10887,8 +11440,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="140" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q139" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
         <v>63</v>
       </c>
@@ -10945,8 +11502,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="141" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q140" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="141" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>8</v>
       </c>
@@ -11003,8 +11564,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="142" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q141" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="142" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>53</v>
       </c>
@@ -11061,8 +11626,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="143" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q142" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
         <v>175</v>
       </c>
@@ -11119,8 +11688,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="144" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q143" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
         <v>189</v>
       </c>
@@ -11177,8 +11750,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="145" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q144" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>7</v>
       </c>
@@ -11235,8 +11812,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="146" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q145" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="146" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
         <v>187</v>
       </c>
@@ -11293,8 +11874,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="147" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q146" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
         <v>30</v>
       </c>
@@ -11351,8 +11936,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="148" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q147" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="148" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
         <v>32</v>
       </c>
@@ -11409,8 +11998,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="149" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q148" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="149" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
         <v>109</v>
       </c>
@@ -11467,8 +12060,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="150" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q149" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="150" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
         <v>42</v>
       </c>
@@ -11525,8 +12122,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="151" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q150" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="151" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
         <v>46</v>
       </c>
@@ -11583,8 +12184,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="152" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q151" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="152" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>181</v>
       </c>
@@ -11641,8 +12246,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="153" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q152" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="153" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>53</v>
       </c>
@@ -11699,8 +12308,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="154" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q153" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="154" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
         <v>191</v>
       </c>
@@ -11757,8 +12370,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="155" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q154" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
         <v>185</v>
       </c>
@@ -11815,8 +12432,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="156" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q155" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="156" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
         <v>189</v>
       </c>
@@ -11873,8 +12494,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="157" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q156" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="157" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A157" s="2" t="s">
         <v>187</v>
       </c>
@@ -11931,8 +12556,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="158" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q157" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="158" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>191</v>
       </c>
@@ -11989,8 +12618,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="159" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q158" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="159" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>11</v>
       </c>
@@ -12047,8 +12680,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="160" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q159" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="160" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>281</v>
       </c>
@@ -12105,8 +12742,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="161" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q160" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="161" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
         <v>73</v>
       </c>
@@ -12164,8 +12805,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="162" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q161" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="162" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>332</v>
       </c>
@@ -12222,8 +12867,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="163" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q162" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="163" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>331</v>
       </c>
@@ -12280,8 +12929,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="164" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q163" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="164" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>339</v>
       </c>
@@ -12338,8 +12991,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="165" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q164" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="165" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>193</v>
       </c>
@@ -12396,8 +13053,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="166" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q165" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="166" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>196</v>
       </c>
@@ -12454,8 +13115,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="167" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q166" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="167" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A167" s="2" t="s">
         <v>23</v>
       </c>
@@ -12512,8 +13177,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="168" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q167" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="168" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A168" s="2" t="s">
         <v>48</v>
       </c>
@@ -12570,8 +13239,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="169" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q168" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="169" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="s">
         <v>22</v>
       </c>
@@ -12628,8 +13301,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="170" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q169" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="170" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>79</v>
       </c>
@@ -12686,8 +13363,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="171" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q170" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="171" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A171" s="2" t="s">
         <v>70</v>
       </c>
@@ -12744,8 +13425,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="172" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q171" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>203</v>
       </c>
@@ -12802,8 +13487,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="173" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q172" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="173" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A173" s="2" t="s">
         <v>62</v>
       </c>
@@ -12860,8 +13549,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="174" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q173" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="174" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A174" s="2" t="s">
         <v>88</v>
       </c>
@@ -12918,8 +13611,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="175" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q174" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="175" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A175" s="2" t="s">
         <v>83</v>
       </c>
@@ -12976,8 +13673,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="176" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q175" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="176" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A176" s="2" t="s">
         <v>70</v>
       </c>
@@ -13034,8 +13735,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="177" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q176" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="177" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>86</v>
       </c>
@@ -13092,8 +13797,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="178" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q177" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="178" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>206</v>
       </c>
@@ -13150,8 +13859,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="179" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q178" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="179" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>333</v>
       </c>
@@ -13208,8 +13921,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="180" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q179" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="180" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A180" s="2" t="s">
         <v>209</v>
       </c>
@@ -13266,8 +13983,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="181" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q180" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="181" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A181" s="2" t="s">
         <v>161</v>
       </c>
@@ -13324,8 +14045,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="182" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q181" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="182" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A182" s="2" t="s">
         <v>212</v>
       </c>
@@ -13382,8 +14107,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="183" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q182" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="183" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>326</v>
       </c>
@@ -13440,8 +14169,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="184" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q183" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="184" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>318</v>
       </c>
@@ -13498,8 +14231,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="185" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q184" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="185" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>347</v>
       </c>
@@ -13556,8 +14293,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="186" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q185" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="186" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>345</v>
       </c>
@@ -13615,8 +14356,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="187" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q186" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="187" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>328</v>
       </c>
@@ -13673,8 +14418,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="188" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q187" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="188" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A188" s="2" t="s">
         <v>99</v>
       </c>
@@ -13731,8 +14480,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="189" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q188" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="189" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>335</v>
       </c>
@@ -13768,7 +14521,7 @@
         <v>16</v>
       </c>
       <c r="K189" t="s">
-        <v>372</v>
+        <v>434</v>
       </c>
       <c r="L189" t="s">
         <v>307</v>
@@ -13783,14 +14536,18 @@
       </c>
       <c r="O189" t="str">
         <f>IF(IFERROR(VLOOKUP(Tabela1[[#This Row],[Novo_Avaliador]],Usuários!$A:$B,2,FALSE),"")="","",IFERROR(VLOOKUP(Tabela1[[#This Row],[Novo_Avaliador]],Usuários!$A:$B,2,FALSE),""))</f>
-        <v>jose.filho@enind.com.br</v>
+        <v>jose.martins@enindservicos.com.br</v>
       </c>
       <c r="P189" t="str">
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="190" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q189" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="190" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>212</v>
       </c>
@@ -13847,8 +14604,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="191" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q190" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="191" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>65</v>
       </c>
@@ -13905,8 +14666,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="192" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q191" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="192" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>336</v>
       </c>
@@ -13963,8 +14728,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="193" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q192" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="193" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>337</v>
       </c>
@@ -14021,8 +14790,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="194" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q193" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="194" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A194" s="2" t="s">
         <v>68</v>
       </c>
@@ -14079,8 +14852,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="195" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q194" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="195" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A195" s="2" t="s">
         <v>123</v>
       </c>
@@ -14137,8 +14914,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="196" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q195" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="196" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A196" s="2" t="s">
         <v>220</v>
       </c>
@@ -14195,8 +14976,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="197" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q196" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="197" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>120</v>
       </c>
@@ -14253,8 +15038,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="198" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q197" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="198" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>343</v>
       </c>
@@ -14311,8 +15100,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="199" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q198" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="199" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>344</v>
       </c>
@@ -14369,8 +15162,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="200" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q199" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="200" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>349</v>
       </c>
@@ -14427,8 +15224,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="201" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q200" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="201" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A201" s="2" t="s">
         <v>222</v>
       </c>
@@ -14485,8 +15286,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="202" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q201" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="202" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>225</v>
       </c>
@@ -14544,8 +15349,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="203" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q202" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="203" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>334</v>
       </c>
@@ -14602,8 +15411,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="204" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q203" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="204" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A204" s="2" t="s">
         <v>227</v>
       </c>
@@ -14660,8 +15473,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="205" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q204" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="205" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>338</v>
       </c>
@@ -14718,8 +15535,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="206" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q205" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="206" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A206" s="2" t="s">
         <v>230</v>
       </c>
@@ -14776,8 +15597,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="207" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q206" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="207" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A207" s="2" t="s">
         <v>120</v>
       </c>
@@ -14834,8 +15659,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="208" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q207" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="208" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>220</v>
       </c>
@@ -14892,8 +15721,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="209" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q208" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="209" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>343</v>
       </c>
@@ -14950,8 +15783,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="210" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q209" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="210" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>344</v>
       </c>
@@ -15008,8 +15845,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="211" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q210" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="211" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>349</v>
       </c>
@@ -15066,8 +15907,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="212" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q211" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="212" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>348</v>
       </c>
@@ -15124,8 +15969,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="213" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q212" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="213" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>340</v>
       </c>
@@ -15182,8 +16031,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="214" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q213" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="214" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A214" s="2" t="s">
         <v>225</v>
       </c>
@@ -15240,8 +16093,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="215" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q214" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="215" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>341</v>
       </c>
@@ -15298,8 +16155,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="216" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q215" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="216" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A216" s="2" t="s">
         <v>234</v>
       </c>
@@ -15356,8 +16217,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="217" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q216" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="217" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A217" s="2" t="s">
         <v>237</v>
       </c>
@@ -15414,8 +16279,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="218" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q217" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="218" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>342</v>
       </c>
@@ -15472,8 +16341,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="219" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q218" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="219" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>343</v>
       </c>
@@ -15530,8 +16403,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="220" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q219" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="220" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A220" s="2" t="s">
         <v>240</v>
       </c>
@@ -15588,8 +16465,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="221" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q220" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="221" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>344</v>
       </c>
@@ -15646,8 +16527,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="222" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q221" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="222" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A222" s="2" t="s">
         <v>185</v>
       </c>
@@ -15704,8 +16589,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="223" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q222" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="223" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A223" s="2" t="s">
         <v>167</v>
       </c>
@@ -15762,8 +16651,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="224" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q223" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="224" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>345</v>
       </c>
@@ -15820,8 +16713,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="225" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q224" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="225" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>346</v>
       </c>
@@ -15878,8 +16775,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="226" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q225" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="226" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A226" s="2" t="s">
         <v>245</v>
       </c>
@@ -15936,8 +16837,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="227" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q226" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="227" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>31</v>
       </c>
@@ -15995,8 +16900,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="228" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q227" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="228" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A228" s="2" t="s">
         <v>169</v>
       </c>
@@ -16053,8 +16962,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="229" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q228" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="229" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A229" s="2" t="s">
         <v>209</v>
       </c>
@@ -16111,8 +17024,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="230" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q229" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="230" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A230" s="2" t="s">
         <v>161</v>
       </c>
@@ -16169,8 +17086,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="231" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q230" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="231" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>212</v>
       </c>
@@ -16227,8 +17148,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="232" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q231" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="232" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>245</v>
       </c>
@@ -16285,8 +17210,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="233" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q232" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="233" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>268</v>
       </c>
@@ -16343,8 +17272,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="234" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q233" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="234" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>322</v>
       </c>
@@ -16401,8 +17334,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="235" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q234" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="235" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>325</v>
       </c>
@@ -16459,8 +17396,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="236" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q235" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="236" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>326</v>
       </c>
@@ -16517,8 +17458,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="237" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q236" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="237" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>327</v>
       </c>
@@ -16575,8 +17520,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="238" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q237" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="238" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>332</v>
       </c>
@@ -16633,8 +17582,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="239" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q238" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="239" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>338</v>
       </c>
@@ -16691,8 +17644,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="240" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q239" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="240" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>342</v>
       </c>
@@ -16749,8 +17706,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="241" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q240" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="241" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>350</v>
       </c>
@@ -16807,8 +17768,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="242" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q241" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="242" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>351</v>
       </c>
@@ -16865,8 +17830,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="243" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q242" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="243" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>353</v>
       </c>
@@ -16923,8 +17892,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="244" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q243" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="244" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A244" s="2" t="s">
         <v>155</v>
       </c>
@@ -16981,8 +17954,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="245" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q244" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="245" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>324</v>
       </c>
@@ -17039,8 +18016,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="246" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q245" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="246" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>347</v>
       </c>
@@ -17097,8 +18078,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="247" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q246" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="247" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>251</v>
       </c>
@@ -17155,8 +18140,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="248" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q247" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="248" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>254</v>
       </c>
@@ -17213,8 +18202,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="249" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q248" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="249" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>257</v>
       </c>
@@ -17272,8 +18265,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="250" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q249" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="250" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A250" s="2" t="s">
         <v>19</v>
       </c>
@@ -17331,8 +18328,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="251" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q250" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="251" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A251" s="2" t="s">
         <v>159</v>
       </c>
@@ -17390,8 +18391,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="252" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q251" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="252" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>18</v>
       </c>
@@ -17448,8 +18453,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="253" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q252" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="253" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A253" s="2" t="s">
         <v>147</v>
       </c>
@@ -17506,8 +18515,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="254" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q253" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="254" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>17</v>
       </c>
@@ -17564,8 +18577,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="255" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q254" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="255" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A255" s="2" t="s">
         <v>141</v>
       </c>
@@ -17622,8 +18639,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="256" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q255" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="256" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>41</v>
       </c>
@@ -17680,8 +18701,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="257" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q256" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="257" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A257" s="2" t="s">
         <v>144</v>
       </c>
@@ -17738,8 +18763,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="258" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q257" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="258" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>58</v>
       </c>
@@ -17796,8 +18825,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="259" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q258" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="259" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A259" s="2" t="s">
         <v>240</v>
       </c>
@@ -17855,8 +18888,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="260" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q259" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="260" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A260" s="2" t="s">
         <v>260</v>
       </c>
@@ -17913,8 +18950,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="261" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q260" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="261" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>349</v>
       </c>
@@ -17971,8 +19012,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="262" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q261" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="262" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>350</v>
       </c>
@@ -18029,8 +19074,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="263" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q262" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="263" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A263" s="2" t="s">
         <v>220</v>
       </c>
@@ -18087,8 +19136,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="264" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q263" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="264" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A264" s="2" t="s">
         <v>52</v>
       </c>
@@ -18145,8 +19198,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="265" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q264" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="265" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A265" s="2" t="s">
         <v>234</v>
       </c>
@@ -18204,8 +19261,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="266" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q265" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="266" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A266" s="2" t="s">
         <v>266</v>
       </c>
@@ -18262,8 +19323,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="267" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q266" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="267" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>48</v>
       </c>
@@ -18320,8 +19385,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="268" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q267" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="268" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A268" s="2" t="s">
         <v>109</v>
       </c>
@@ -18378,8 +19447,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="269" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q268" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="269" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>185</v>
       </c>
@@ -18436,8 +19509,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="270" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q269" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="270" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>317</v>
       </c>
@@ -18494,8 +19571,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="271" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q270" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="271" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>321</v>
       </c>
@@ -18552,8 +19633,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="272" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q271" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="272" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>328</v>
       </c>
@@ -18610,8 +19695,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="273" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q272" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="273" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>333</v>
       </c>
@@ -18668,8 +19757,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="274" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q273" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="274" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>334</v>
       </c>
@@ -18726,8 +19819,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="275" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q274" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="275" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>339</v>
       </c>
@@ -18784,8 +19881,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="276" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q275" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="276" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>348</v>
       </c>
@@ -18842,8 +19943,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="277" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q276" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="277" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>316</v>
       </c>
@@ -18900,8 +20005,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="278" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q277" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="278" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>331</v>
       </c>
@@ -18958,8 +20067,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="279" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q278" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="279" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>352</v>
       </c>
@@ -19016,8 +20129,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="280" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q279" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="280" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
         <v>351</v>
       </c>
@@ -19074,8 +20191,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="281" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q280" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="281" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A281" s="2" t="s">
         <v>268</v>
       </c>
@@ -19132,8 +20253,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="282" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q281" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="282" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A282" s="2" t="s">
         <v>94</v>
       </c>
@@ -19190,8 +20315,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="283" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q282" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="283" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A283" s="2" t="s">
         <v>274</v>
       </c>
@@ -19249,8 +20378,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="284" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q283" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="284" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
         <v>272</v>
       </c>
@@ -19307,8 +20440,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="285" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q284" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="285" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A285" s="2" t="s">
         <v>196</v>
       </c>
@@ -19365,8 +20502,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="286" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q285" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="286" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>260</v>
       </c>
@@ -19423,8 +20564,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="287" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q286" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="287" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
         <v>320</v>
       </c>
@@ -19481,8 +20626,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="288" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q287" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="288" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
         <v>329</v>
       </c>
@@ -19539,8 +20688,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="289" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q288" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="289" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>330</v>
       </c>
@@ -19597,8 +20750,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="290" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q289" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="290" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
         <v>335</v>
       </c>
@@ -19655,8 +20812,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="291" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q290" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="291" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>341</v>
       </c>
@@ -19713,8 +20874,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="292" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q291" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="292" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
         <v>323</v>
       </c>
@@ -19771,8 +20936,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="293" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q292" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="293" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
         <v>91</v>
       </c>
@@ -19830,8 +20999,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="294" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q293" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="294" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A294" s="2" t="s">
         <v>274</v>
       </c>
@@ -19888,8 +21061,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="295" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q294" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="295" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A295" s="2" t="s">
         <v>277</v>
       </c>
@@ -19946,8 +21123,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="296" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q295" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="296" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A296" s="2" t="s">
         <v>31</v>
       </c>
@@ -20004,8 +21185,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="297" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q296" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="297" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A297" s="2" t="s">
         <v>245</v>
       </c>
@@ -20062,8 +21247,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="298" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q297" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="298" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A298" s="2" t="s">
         <v>268</v>
       </c>
@@ -20120,8 +21309,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="299" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q298" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="299" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A299" s="2" t="s">
         <v>27</v>
       </c>
@@ -20178,8 +21371,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="300" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q299" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="300" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
         <v>68</v>
       </c>
@@ -20236,8 +21433,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="301" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q300" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="301" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
         <v>351</v>
       </c>
@@ -20294,8 +21495,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="302" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q301" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="302" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
         <v>317</v>
       </c>
@@ -20352,8 +21557,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="303" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q302" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="303" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A303" s="2" t="s">
         <v>281</v>
       </c>
@@ -20410,8 +21619,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="304" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q303" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="304" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
         <v>352</v>
       </c>
@@ -20468,8 +21681,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="305" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q304" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="305" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A305" s="2" t="s">
         <v>266</v>
       </c>
@@ -20526,8 +21743,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="306" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q305" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="306" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
         <v>352</v>
       </c>
@@ -20584,8 +21805,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="307" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q306" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="307" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
         <v>117</v>
       </c>
@@ -20643,8 +21868,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="308" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q307" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="308" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
         <v>52</v>
       </c>
@@ -20702,8 +21931,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="309" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q308" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="309" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A309" s="2" t="s">
         <v>38</v>
       </c>
@@ -20760,8 +21993,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="310" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q309" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="310" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
         <v>151</v>
       </c>
@@ -20818,8 +22055,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="311" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q310" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="311" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
         <v>94</v>
       </c>
@@ -20855,7 +22096,7 @@
         <v>16</v>
       </c>
       <c r="K311" t="s">
-        <v>292</v>
+        <v>248</v>
       </c>
       <c r="L311" t="s">
         <v>309</v>
@@ -20876,8 +22117,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="312" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q311" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="312" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
         <v>15</v>
       </c>
@@ -20934,8 +22179,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="313" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q312" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="313" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
         <v>77</v>
       </c>
@@ -20992,8 +22241,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="314" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q313" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="314" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
         <v>71</v>
       </c>
@@ -21050,8 +22303,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="315" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q314" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="315" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
         <v>321</v>
       </c>
@@ -21108,8 +22365,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="316" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q315" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="316" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A316" s="2" t="s">
         <v>222</v>
       </c>
@@ -21167,8 +22428,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="317" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q316" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="317" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
         <v>353</v>
       </c>
@@ -21225,8 +22490,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="318" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q317" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="318" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A318" s="2" t="s">
         <v>91</v>
       </c>
@@ -21284,8 +22553,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="319" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q318" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="319" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A319" s="2" t="s">
         <v>272</v>
       </c>
@@ -21342,8 +22615,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="320" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q319" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="320" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A320" s="2" t="s">
         <v>196</v>
       </c>
@@ -21400,8 +22677,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="321" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q320" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="321" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A321" s="2" t="s">
         <v>260</v>
       </c>
@@ -21458,8 +22739,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="322" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q321" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="322" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
         <v>320</v>
       </c>
@@ -21516,8 +22801,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="323" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q322" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="323" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
         <v>329</v>
       </c>
@@ -21574,8 +22863,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="324" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q323" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="324" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
         <v>330</v>
       </c>
@@ -21632,8 +22925,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="325" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q324" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="325" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
         <v>335</v>
       </c>
@@ -21690,8 +22987,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="326" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q325" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="326" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
         <v>341</v>
       </c>
@@ -21748,8 +23049,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="327" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q326" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="327" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
         <v>222</v>
       </c>
@@ -21807,8 +23112,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="328" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q327" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="328" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A328" s="2" t="s">
         <v>15</v>
       </c>
@@ -21865,8 +23174,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="329" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q328" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="329" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A329" s="2" t="s">
         <v>10</v>
       </c>
@@ -21923,8 +23236,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="330" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q329" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="330" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
         <v>254</v>
       </c>
@@ -21981,8 +23298,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="331" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q330" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="331" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A331" s="2" t="s">
         <v>3</v>
       </c>
@@ -22039,8 +23360,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="332" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q331" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="332" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A332" s="2" t="s">
         <v>9</v>
       </c>
@@ -22097,8 +23422,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="333" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q332" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="333" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A333" s="2" t="s">
         <v>43</v>
       </c>
@@ -22155,8 +23484,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="334" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q333" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="334" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
         <v>126</v>
       </c>
@@ -22213,8 +23546,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="335" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q334" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="335" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A335" s="2" t="s">
         <v>23</v>
       </c>
@@ -22271,8 +23608,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="336" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q335" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="336" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
         <v>129</v>
       </c>
@@ -22329,8 +23670,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="337" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q336" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="337" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
         <v>51</v>
       </c>
@@ -22387,8 +23732,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="338" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q337" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="338" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
         <v>57</v>
       </c>
@@ -22445,8 +23794,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="339" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q338" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="339" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
         <v>277</v>
       </c>
@@ -22503,8 +23856,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="340" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q339" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="340" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
         <v>266</v>
       </c>
@@ -22561,8 +23918,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="341" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q340" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="341" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
         <v>206</v>
       </c>
@@ -22619,8 +23980,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="342" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q341" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="342" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
         <v>316</v>
       </c>
@@ -22677,8 +24042,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="343" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q342" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="343" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
         <v>328</v>
       </c>
@@ -22735,8 +24104,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="344" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q343" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="344" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A344" s="2" t="s">
         <v>37</v>
       </c>
@@ -22794,8 +24167,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="345" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q344" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="345" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
         <v>123</v>
       </c>
@@ -22853,8 +24230,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="346" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q345" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="346" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
         <v>225</v>
       </c>
@@ -22912,8 +24293,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="347" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q346" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="347" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A347" s="2" t="s">
         <v>257</v>
       </c>
@@ -22970,8 +24355,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="348" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q347" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="348" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A348" s="2" t="s">
         <v>33</v>
       </c>
@@ -23028,8 +24417,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="349" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q348" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="349" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
         <v>25</v>
       </c>
@@ -23087,8 +24480,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="350" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q349" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="350" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A350" s="2" t="s">
         <v>123</v>
       </c>
@@ -23146,8 +24543,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="351" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q350" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="351" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
         <v>54</v>
       </c>
@@ -23205,8 +24606,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="352" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q351" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="352" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A352" s="2" t="s">
         <v>77</v>
       </c>
@@ -23263,8 +24668,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="353" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q352" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="353" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A353" s="2" t="s">
         <v>59</v>
       </c>
@@ -23321,8 +24730,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="354" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q353" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="354" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A354" s="2" t="s">
         <v>63</v>
       </c>
@@ -23379,8 +24792,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="355" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q354" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="355" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A355" s="2" t="s">
         <v>8</v>
       </c>
@@ -23437,8 +24854,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="356" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q355" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="356" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
         <v>47</v>
       </c>
@@ -23495,8 +24916,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="357" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q356" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="357" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
         <v>227</v>
       </c>
@@ -23553,8 +24978,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="358" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q357" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="358" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
         <v>230</v>
       </c>
@@ -23611,8 +25040,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="359" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q358" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="359" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
         <v>331</v>
       </c>
@@ -23669,8 +25102,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="360" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q359" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="360" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
         <v>333</v>
       </c>
@@ -23727,8 +25164,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="361" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q360" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="361" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
         <v>334</v>
       </c>
@@ -23785,8 +25226,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="362" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q361" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="362" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A362" s="2" t="s">
         <v>37</v>
       </c>
@@ -23844,8 +25289,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="363" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q362" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="363" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
         <v>234</v>
       </c>
@@ -23903,8 +25352,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="364" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q363" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="364" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A364" s="2" t="s">
         <v>73</v>
       </c>
@@ -23962,8 +25415,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="365" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q364" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="365" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A365" s="2" t="s">
         <v>14</v>
       </c>
@@ -24021,8 +25478,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="366" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q365" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="366" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A366" s="2" t="s">
         <v>71</v>
       </c>
@@ -24079,8 +25540,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="367" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q366" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="367" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
         <v>43</v>
       </c>
@@ -24137,8 +25602,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="368" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q367" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="368" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A368" s="2" t="s">
         <v>54</v>
       </c>
@@ -24196,8 +25665,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="369" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q368" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="369" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A369" s="2" t="s">
         <v>8</v>
       </c>
@@ -24254,8 +25727,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="370" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q369" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="370" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A370" s="2" t="s">
         <v>23</v>
       </c>
@@ -24312,8 +25789,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="371" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q370" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="371" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A371" s="2" t="s">
         <v>227</v>
       </c>
@@ -24370,8 +25851,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="372" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q371" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="372" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A372" s="2" t="s">
         <v>230</v>
       </c>
@@ -24428,8 +25913,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="373" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q372" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="373" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A373" s="2" t="s">
         <v>175</v>
       </c>
@@ -24486,8 +25975,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="374" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q373" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="374" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A374" s="2" t="s">
         <v>7</v>
       </c>
@@ -24544,8 +26037,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="375" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q374" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="375" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
         <v>22</v>
       </c>
@@ -24602,8 +26099,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="376" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q375" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="376" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
         <v>59</v>
       </c>
@@ -24660,8 +26161,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="377" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q376" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="377" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
         <v>30</v>
       </c>
@@ -24718,8 +26223,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="378" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q377" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="378" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A378" s="2" t="s">
         <v>79</v>
       </c>
@@ -24776,8 +26285,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="379" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q378" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="379" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
         <v>10</v>
       </c>
@@ -24834,8 +26347,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="380" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q379" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="380" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A380" s="2" t="s">
         <v>42</v>
       </c>
@@ -24892,8 +26409,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="381" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q380" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="381" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A381" s="2" t="s">
         <v>97</v>
       </c>
@@ -24950,8 +26471,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="382" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q381" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="382" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A382" s="2" t="s">
         <v>46</v>
       </c>
@@ -25008,8 +26533,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="383" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q382" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="383" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
         <v>203</v>
       </c>
@@ -25066,8 +26595,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="384" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q383" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="384" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
         <v>99</v>
       </c>
@@ -25124,8 +26657,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="385" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q384" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="385" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
         <v>181</v>
       </c>
@@ -25182,8 +26719,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="386" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q385" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="386" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
         <v>53</v>
       </c>
@@ -25240,8 +26781,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="387" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q386" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="387" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
         <v>104</v>
       </c>
@@ -25298,8 +26843,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="388" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q387" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="388" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
         <v>254</v>
       </c>
@@ -25356,8 +26905,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="389" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q388" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="389" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
         <v>62</v>
       </c>
@@ -25414,8 +26967,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="390" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q389" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="390" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
         <v>339</v>
       </c>
@@ -25472,8 +27029,12 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
-    </row>
-    <row r="391" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q390" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="391" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
         <v>348</v>
       </c>
@@ -25530,14 +27091,18 @@
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
         <v>Sim</v>
       </c>
+      <c r="Q391" t="b">
+        <f>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</f>
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="I1:J1048576">
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
       <formula>"Não"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="4" operator="equal">
       <formula>"Sim"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -25557,8 +27122,9 @@
     <hyperlink ref="K199" r:id="rId13" xr:uid="{9DE20185-22E7-4B36-AA47-9396DC30E6D9}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId14"/>
   <tableParts count="1">
-    <tablePart r:id="rId14"/>
+    <tablePart r:id="rId15"/>
   </tableParts>
 </worksheet>
 </file>
@@ -30462,6 +32028,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8A1FF41-FE38-442B-8F1A-E5C01AF500AB}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:M155"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -30509,7 +32076,7 @@
         <v>738</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>71</v>
       </c>
@@ -30535,7 +32102,7 @@
       </c>
       <c r="J2" t="str">
         <f ca="1">TEXT(RANDBETWEEN(1,999),"000") &amp; LEFT(H2,1) &amp; MID(H2,FIND(".",H2,1)+1,1) &amp; "!@"</f>
-        <v>643wf!@</v>
+        <v>887wf!@</v>
       </c>
       <c r="K2" t="str">
         <f>"Update QuestRH_Pessoas set Senha = '" &amp; I2 &amp; "' Where Nome = '" &amp; A2 &amp; "';"</f>
@@ -30545,7 +32112,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>77</v>
       </c>
@@ -30571,7 +32138,7 @@
       </c>
       <c r="J3" t="str">
         <f t="shared" ref="J3:J66" ca="1" si="0">TEXT(RANDBETWEEN(1,999),"000") &amp; LEFT(H3,1) &amp; MID(H3,FIND(".",H3,1)+1,1) &amp; "!@"</f>
-        <v>945wc!@</v>
+        <v>372wc!@</v>
       </c>
       <c r="K3" t="str">
         <f t="shared" ref="K3:K66" si="1">"Update QuestRH_Pessoas set Senha = '" &amp; I3 &amp; "' Where Nome = '" &amp; A3 &amp; "';"</f>
@@ -30581,7 +32148,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>257</v>
       </c>
@@ -30607,7 +32174,7 @@
       </c>
       <c r="J4" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>096ws!@</v>
+        <v>872ws!@</v>
       </c>
       <c r="K4" t="str">
         <f t="shared" si="1"/>
@@ -30617,7 +32184,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>15</v>
       </c>
@@ -30643,7 +32210,7 @@
       </c>
       <c r="J5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>373wm!@</v>
+        <v>546wm!@</v>
       </c>
       <c r="K5" t="str">
         <f t="shared" si="1"/>
@@ -30653,7 +32220,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>272</v>
       </c>
@@ -30679,7 +32246,7 @@
       </c>
       <c r="J6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>684wf!@</v>
+        <v>743wf!@</v>
       </c>
       <c r="K6" t="str">
         <f t="shared" si="1"/>
@@ -30689,7 +32256,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>291</v>
       </c>
@@ -30715,7 +32282,7 @@
       </c>
       <c r="J7" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>755wc!@</v>
+        <v>303wc!@</v>
       </c>
       <c r="K7" t="str">
         <f t="shared" si="1"/>
@@ -30725,7 +32292,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>266</v>
       </c>
@@ -30751,7 +32318,7 @@
       </c>
       <c r="J8" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>195vx!@</v>
+        <v>536vx!@</v>
       </c>
       <c r="K8" t="str">
         <f t="shared" si="1"/>
@@ -30761,7 +32328,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>31</v>
       </c>
@@ -30787,7 +32354,7 @@
       </c>
       <c r="J9" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>132vs!@</v>
+        <v>973vs!@</v>
       </c>
       <c r="K9" t="str">
         <f t="shared" si="1"/>
@@ -30797,7 +32364,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>277</v>
       </c>
@@ -30823,7 +32390,7 @@
       </c>
       <c r="J10" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>510ub!@</v>
+        <v>969ub!@</v>
       </c>
       <c r="K10" t="str">
         <f t="shared" si="1"/>
@@ -30833,7 +32400,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>94</v>
       </c>
@@ -30859,7 +32426,7 @@
       </c>
       <c r="J11" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>647to!@</v>
+        <v>760to!@</v>
       </c>
       <c r="K11" t="str">
         <f t="shared" si="1"/>
@@ -30869,7 +32436,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>268</v>
       </c>
@@ -30895,7 +32462,7 @@
       </c>
       <c r="J12" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>860ta!@</v>
+        <v>532ta!@</v>
       </c>
       <c r="K12" t="str">
         <f t="shared" si="1"/>
@@ -30905,7 +32472,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>52</v>
       </c>
@@ -30931,7 +32498,7 @@
       </c>
       <c r="J13" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>764ta!@</v>
+        <v>140ta!@</v>
       </c>
       <c r="K13" t="str">
         <f t="shared" si="1"/>
@@ -30941,7 +32508,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>220</v>
       </c>
@@ -30967,7 +32534,7 @@
       </c>
       <c r="J14" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>376tp!@</v>
+        <v>854tp!@</v>
       </c>
       <c r="K14" t="str">
         <f t="shared" si="1"/>
@@ -30977,7 +32544,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>260</v>
       </c>
@@ -31003,7 +32570,7 @@
       </c>
       <c r="J15" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>204rs!@</v>
+        <v>904rs!@</v>
       </c>
       <c r="K15" t="str">
         <f t="shared" si="1"/>
@@ -31013,7 +32580,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>24</v>
       </c>
@@ -31039,7 +32606,7 @@
       </c>
       <c r="J16" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>052rm!@</v>
+        <v>117rm!@</v>
       </c>
       <c r="K16" t="str">
         <f t="shared" si="1"/>
@@ -31049,7 +32616,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>254</v>
       </c>
@@ -31075,7 +32642,7 @@
       </c>
       <c r="J17" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>507rm!@</v>
+        <v>073rm!@</v>
       </c>
       <c r="K17" t="str">
         <f t="shared" si="1"/>
@@ -31085,7 +32652,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>155</v>
       </c>
@@ -31111,7 +32678,7 @@
       </c>
       <c r="J18" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>101ra!@</v>
+        <v>657ra!@</v>
       </c>
       <c r="K18" t="str">
         <f t="shared" si="1"/>
@@ -31121,7 +32688,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>164</v>
       </c>
@@ -31147,7 +32714,7 @@
       </c>
       <c r="J19" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>121pm!@</v>
+        <v>834pm!@</v>
       </c>
       <c r="K19" t="str">
         <f t="shared" si="1"/>
@@ -31157,7 +32724,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>245</v>
       </c>
@@ -31183,7 +32750,7 @@
       </c>
       <c r="J20" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>894pa!@</v>
+        <v>913pa!@</v>
       </c>
       <c r="K20" t="str">
         <f t="shared" si="1"/>
@@ -31193,7 +32760,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>167</v>
       </c>
@@ -31219,7 +32786,7 @@
       </c>
       <c r="J21" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>780mg!@</v>
+        <v>328mg!@</v>
       </c>
       <c r="K21" t="str">
         <f t="shared" si="1"/>
@@ -31229,7 +32796,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>185</v>
       </c>
@@ -31255,7 +32822,7 @@
       </c>
       <c r="J22" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>330mc!@</v>
+        <v>976mc!@</v>
       </c>
       <c r="K22" t="str">
         <f t="shared" si="1"/>
@@ -31265,7 +32832,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>240</v>
       </c>
@@ -31291,7 +32858,7 @@
       </c>
       <c r="J23" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>129ms!@</v>
+        <v>441ms!@</v>
       </c>
       <c r="K23" t="str">
         <f t="shared" si="1"/>
@@ -31301,7 +32868,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>234</v>
       </c>
@@ -31327,7 +32894,7 @@
       </c>
       <c r="J24" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>066ms!@</v>
+        <v>923ms!@</v>
       </c>
       <c r="K24" t="str">
         <f t="shared" si="1"/>
@@ -31337,7 +32904,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>53</v>
       </c>
@@ -31361,7 +32928,7 @@
       </c>
       <c r="J25" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>792mb!@</v>
+        <v>903mb!@</v>
       </c>
       <c r="K25" t="str">
         <f t="shared" si="1"/>
@@ -31371,7 +32938,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>230</v>
       </c>
@@ -31397,7 +32964,7 @@
       </c>
       <c r="J26" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>336ms!@</v>
+        <v>055ms!@</v>
       </c>
       <c r="K26" t="str">
         <f t="shared" si="1"/>
@@ -31407,7 +32974,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>227</v>
       </c>
@@ -31433,7 +33000,7 @@
       </c>
       <c r="J27" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>359lf!@</v>
+        <v>286lf!@</v>
       </c>
       <c r="K27" t="str">
         <f t="shared" si="1"/>
@@ -31443,7 +33010,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>222</v>
       </c>
@@ -31469,7 +33036,7 @@
       </c>
       <c r="J28" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>182lb!@</v>
+        <v>620lb!@</v>
       </c>
       <c r="K28" t="str">
         <f t="shared" si="1"/>
@@ -31479,7 +33046,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>123</v>
       </c>
@@ -31505,7 +33072,7 @@
       </c>
       <c r="J29" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>987la!@</v>
+        <v>148la!@</v>
       </c>
       <c r="K29" t="str">
         <f t="shared" si="1"/>
@@ -31515,7 +33082,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>68</v>
       </c>
@@ -31541,7 +33108,7 @@
       </c>
       <c r="J30" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>876ls!@</v>
+        <v>833ls!@</v>
       </c>
       <c r="K30" t="str">
         <f t="shared" si="1"/>
@@ -31551,7 +33118,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>65</v>
       </c>
@@ -31577,7 +33144,7 @@
       </c>
       <c r="J31" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>541js!@</v>
+        <v>872js!@</v>
       </c>
       <c r="K31" t="str">
         <f t="shared" si="1"/>
@@ -31587,7 +33154,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>212</v>
       </c>
@@ -31613,7 +33180,7 @@
       </c>
       <c r="J32" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>559jm!@</v>
+        <v>188jm!@</v>
       </c>
       <c r="K32" t="str">
         <f t="shared" si="1"/>
@@ -31623,7 +33190,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>99</v>
       </c>
@@ -31649,7 +33216,7 @@
       </c>
       <c r="J33" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>208ja!@</v>
+        <v>367ja!@</v>
       </c>
       <c r="K33" t="str">
         <f t="shared" si="1"/>
@@ -31659,7 +33226,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>209</v>
       </c>
@@ -31685,7 +33252,7 @@
       </c>
       <c r="J34" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>408js!@</v>
+        <v>810js!@</v>
       </c>
       <c r="K34" t="str">
         <f t="shared" si="1"/>
@@ -31695,7 +33262,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>67</v>
       </c>
@@ -31721,7 +33288,7 @@
       </c>
       <c r="J35" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>944jf!@</v>
+        <v>888jf!@</v>
       </c>
       <c r="K35" t="str">
         <f t="shared" si="1"/>
@@ -31731,7 +33298,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>23</v>
       </c>
@@ -31757,7 +33324,7 @@
       </c>
       <c r="J36" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>667jr!@</v>
+        <v>012jr!@</v>
       </c>
       <c r="K36" t="str">
         <f t="shared" si="1"/>
@@ -31767,7 +33334,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>196</v>
       </c>
@@ -31793,7 +33360,7 @@
       </c>
       <c r="J37" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>467ja!@</v>
+        <v>713ja!@</v>
       </c>
       <c r="K37" t="str">
         <f t="shared" si="1"/>
@@ -31803,7 +33370,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>8</v>
       </c>
@@ -31829,7 +33396,7 @@
       </c>
       <c r="J38" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>003ht!@</v>
+        <v>807ht!@</v>
       </c>
       <c r="K38" t="str">
         <f t="shared" si="1"/>
@@ -31839,7 +33406,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>63</v>
       </c>
@@ -31865,7 +33432,7 @@
       </c>
       <c r="J39" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>147hk!@</v>
+        <v>346hk!@</v>
       </c>
       <c r="K39" t="str">
         <f t="shared" si="1"/>
@@ -31875,7 +33442,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>117</v>
       </c>
@@ -31901,7 +33468,7 @@
       </c>
       <c r="J40" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>593gl!@</v>
+        <v>890gl!@</v>
       </c>
       <c r="K40" t="str">
         <f t="shared" si="1"/>
@@ -31911,7 +33478,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>159</v>
       </c>
@@ -31937,7 +33504,7 @@
       </c>
       <c r="J41" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>576gp!@</v>
+        <v>068gp!@</v>
       </c>
       <c r="K41" t="str">
         <f t="shared" si="1"/>
@@ -31947,7 +33514,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>161</v>
       </c>
@@ -31973,7 +33540,7 @@
       </c>
       <c r="J42" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>272gl!@</v>
+        <v>883gl!@</v>
       </c>
       <c r="K42" t="str">
         <f t="shared" si="1"/>
@@ -31983,7 +33550,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>147</v>
       </c>
@@ -32009,7 +33576,7 @@
       </c>
       <c r="J43" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>662fc!@</v>
+        <v>701fc!@</v>
       </c>
       <c r="K43" t="str">
         <f t="shared" si="1"/>
@@ -32019,7 +33586,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>36</v>
       </c>
@@ -32045,7 +33612,7 @@
       </c>
       <c r="J44" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>633fb!@</v>
+        <v>546fb!@</v>
       </c>
       <c r="K44" t="str">
         <f t="shared" si="1"/>
@@ -32055,7 +33622,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>151</v>
       </c>
@@ -32081,7 +33648,7 @@
       </c>
       <c r="J45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>281fc!@</v>
+        <v>058fc!@</v>
       </c>
       <c r="K45" t="str">
         <f t="shared" si="1"/>
@@ -32091,7 +33658,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>126</v>
       </c>
@@ -32117,7 +33684,7 @@
       </c>
       <c r="J46" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>396es!@</v>
+        <v>159es!@</v>
       </c>
       <c r="K46" t="str">
         <f t="shared" si="1"/>
@@ -32127,7 +33694,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>18</v>
       </c>
@@ -32153,7 +33720,7 @@
       </c>
       <c r="J47" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>073eb!@</v>
+        <v>122eb!@</v>
       </c>
       <c r="K47" t="str">
         <f t="shared" si="1"/>
@@ -32163,7 +33730,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>10</v>
       </c>
@@ -32189,7 +33756,7 @@
       </c>
       <c r="J48" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>688es!@</v>
+        <v>820es!@</v>
       </c>
       <c r="K48" t="str">
         <f t="shared" si="1"/>
@@ -32199,7 +33766,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>112</v>
       </c>
@@ -32225,7 +33792,7 @@
       </c>
       <c r="J49" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>116ei!@</v>
+        <v>967ei!@</v>
       </c>
       <c r="K49" t="str">
         <f t="shared" si="1"/>
@@ -32235,7 +33802,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>109</v>
       </c>
@@ -32261,7 +33828,7 @@
       </c>
       <c r="J50" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>792eb!@</v>
+        <v>373eb!@</v>
       </c>
       <c r="K50" t="str">
         <f t="shared" si="1"/>
@@ -32271,7 +33838,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>14</v>
       </c>
@@ -32297,7 +33864,7 @@
       </c>
       <c r="J51" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>641en!@</v>
+        <v>222en!@</v>
       </c>
       <c r="K51" t="str">
         <f t="shared" si="1"/>
@@ -32307,7 +33874,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>37</v>
       </c>
@@ -32333,7 +33900,7 @@
       </c>
       <c r="J52" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>955em!@</v>
+        <v>200em!@</v>
       </c>
       <c r="K52" t="str">
         <f t="shared" si="1"/>
@@ -32343,7 +33910,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>91</v>
       </c>
@@ -32369,7 +33936,7 @@
       </c>
       <c r="J53" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>251ep!@</v>
+        <v>216ep!@</v>
       </c>
       <c r="K53" t="str">
         <f t="shared" si="1"/>
@@ -32379,7 +33946,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>79</v>
       </c>
@@ -32405,7 +33972,7 @@
       </c>
       <c r="J54" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>201ds!@</v>
+        <v>752ds!@</v>
       </c>
       <c r="K54" t="str">
         <f t="shared" si="1"/>
@@ -32415,7 +33982,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>73</v>
       </c>
@@ -32441,7 +34008,7 @@
       </c>
       <c r="J55" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>476da!@</v>
+        <v>974da!@</v>
       </c>
       <c r="K55" t="str">
         <f t="shared" si="1"/>
@@ -32451,7 +34018,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>59</v>
       </c>
@@ -32477,7 +34044,7 @@
       </c>
       <c r="J56" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>847ds!@</v>
+        <v>925ds!@</v>
       </c>
       <c r="K56" t="str">
         <f t="shared" si="1"/>
@@ -32487,7 +34054,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>54</v>
       </c>
@@ -32513,7 +34080,7 @@
       </c>
       <c r="J57" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>518dc!@</v>
+        <v>459dc!@</v>
       </c>
       <c r="K57" t="str">
         <f t="shared" si="1"/>
@@ -32523,7 +34090,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>48</v>
       </c>
@@ -32549,7 +34116,7 @@
       </c>
       <c r="J58" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>064cg!@</v>
+        <v>690cg!@</v>
       </c>
       <c r="K58" t="str">
         <f t="shared" si="1"/>
@@ -32559,7 +34126,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>43</v>
       </c>
@@ -32585,7 +34152,7 @@
       </c>
       <c r="J59" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>336bc!@</v>
+        <v>491bc!@</v>
       </c>
       <c r="K59" t="str">
         <f t="shared" si="1"/>
@@ -32595,7 +34162,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>38</v>
       </c>
@@ -32621,7 +34188,7 @@
       </c>
       <c r="J60" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>208af!@</v>
+        <v>698af!@</v>
       </c>
       <c r="K60" t="str">
         <f t="shared" si="1"/>
@@ -32631,7 +34198,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>285</v>
       </c>
@@ -32657,7 +34224,7 @@
       </c>
       <c r="J61" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>371aa!@</v>
+        <v>620aa!@</v>
       </c>
       <c r="K61" t="str">
         <f t="shared" si="1"/>
@@ -32667,7 +34234,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>27</v>
       </c>
@@ -32693,7 +34260,7 @@
       </c>
       <c r="J62" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>130aa!@</v>
+        <v>877aa!@</v>
       </c>
       <c r="K62" t="str">
         <f t="shared" si="1"/>
@@ -32703,7 +34270,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>19</v>
       </c>
@@ -32729,7 +34296,7 @@
       </c>
       <c r="J63" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>209at!@</v>
+        <v>583at!@</v>
       </c>
       <c r="K63" t="str">
         <f t="shared" si="1"/>
@@ -32739,7 +34306,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>3</v>
       </c>
@@ -32765,7 +34332,7 @@
       </c>
       <c r="J64" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>618ac!@</v>
+        <v>043ac!@</v>
       </c>
       <c r="K64" t="str">
         <f t="shared" si="1"/>
@@ -32775,7 +34342,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>189</v>
       </c>
@@ -32803,7 +34370,7 @@
       </c>
       <c r="J65" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>737as!@</v>
+        <v>937as!@</v>
       </c>
       <c r="K65" t="str">
         <f t="shared" si="1"/>
@@ -32813,7 +34380,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>33</v>
       </c>
@@ -32839,7 +34406,7 @@
       </c>
       <c r="J66" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>267ad!@</v>
+        <v>759ad!@</v>
       </c>
       <c r="K66" t="str">
         <f t="shared" si="1"/>
@@ -32849,7 +34416,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>88</v>
       </c>
@@ -32877,7 +34444,7 @@
       </c>
       <c r="J67" t="str">
         <f t="shared" ref="J67:J130" ca="1" si="2">TEXT(RANDBETWEEN(1,999),"000") &amp; LEFT(H67,1) &amp; MID(H67,FIND(".",H67,1)+1,1) &amp; "!@"</f>
-        <v>593af!@</v>
+        <v>822af!@</v>
       </c>
       <c r="K67" t="str">
         <f t="shared" ref="K67:K130" si="3">"Update QuestRH_Pessoas set Senha = '" &amp; I67 &amp; "' Where Nome = '" &amp; A67 &amp; "';"</f>
@@ -32887,7 +34454,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>7</v>
       </c>
@@ -32915,7 +34482,7 @@
       </c>
       <c r="J68" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>568ap!@</v>
+        <v>192ap!@</v>
       </c>
       <c r="K68" t="str">
         <f t="shared" si="3"/>
@@ -32925,7 +34492,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>9</v>
       </c>
@@ -32953,7 +34520,7 @@
       </c>
       <c r="J69" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>933al!@</v>
+        <v>988al!@</v>
       </c>
       <c r="K69" t="str">
         <f t="shared" si="3"/>
@@ -32963,7 +34530,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>13</v>
       </c>
@@ -32991,7 +34558,7 @@
       </c>
       <c r="J70" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>443as!@</v>
+        <v>215as!@</v>
       </c>
       <c r="K70" t="str">
         <f t="shared" si="3"/>
@@ -33001,7 +34568,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>187</v>
       </c>
@@ -33029,7 +34596,7 @@
       </c>
       <c r="J71" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>343at!@</v>
+        <v>301at!@</v>
       </c>
       <c r="K71" t="str">
         <f t="shared" si="3"/>
@@ -33039,7 +34606,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
         <v>83</v>
       </c>
@@ -33067,7 +34634,7 @@
       </c>
       <c r="J72" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>732cm!@</v>
+        <v>555cm!@</v>
       </c>
       <c r="K72" t="str">
         <f t="shared" si="3"/>
@@ -33077,7 +34644,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
         <v>17</v>
       </c>
@@ -33105,7 +34672,7 @@
       </c>
       <c r="J73" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>197ds!@</v>
+        <v>392ds!@</v>
       </c>
       <c r="K73" t="str">
         <f t="shared" si="3"/>
@@ -33115,7 +34682,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>22</v>
       </c>
@@ -33143,7 +34710,7 @@
       </c>
       <c r="J74" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>694ds!@</v>
+        <v>181ds!@</v>
       </c>
       <c r="K74" t="str">
         <f t="shared" si="3"/>
@@ -33153,7 +34720,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
         <v>25</v>
       </c>
@@ -33181,7 +34748,7 @@
       </c>
       <c r="J75" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>227dc!@</v>
+        <v>938dc!@</v>
       </c>
       <c r="K75" t="str">
         <f t="shared" si="3"/>
@@ -33191,7 +34758,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
         <v>30</v>
       </c>
@@ -33219,7 +34786,7 @@
       </c>
       <c r="J76" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>014dd!@</v>
+        <v>661dd!@</v>
       </c>
       <c r="K76" t="str">
         <f t="shared" si="3"/>
@@ -33229,7 +34796,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
         <v>32</v>
       </c>
@@ -33257,7 +34824,7 @@
       </c>
       <c r="J77" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>308dm!@</v>
+        <v>034dm!@</v>
       </c>
       <c r="K77" t="str">
         <f t="shared" si="3"/>
@@ -33267,7 +34834,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
         <v>141</v>
       </c>
@@ -33295,7 +34862,7 @@
       </c>
       <c r="J78" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>852eg!@</v>
+        <v>978eg!@</v>
       </c>
       <c r="K78" t="str">
         <f t="shared" si="3"/>
@@ -33305,7 +34872,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
         <v>41</v>
       </c>
@@ -33333,7 +34900,7 @@
       </c>
       <c r="J79" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>574er!@</v>
+        <v>430er!@</v>
       </c>
       <c r="K79" t="str">
         <f t="shared" si="3"/>
@@ -33343,7 +34910,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
         <v>120</v>
       </c>
@@ -33369,7 +34936,7 @@
       </c>
       <c r="J80" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>871ep!@</v>
+        <v>668ep!@</v>
       </c>
       <c r="K80" t="str">
         <f t="shared" si="3"/>
@@ -33379,7 +34946,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
         <v>148</v>
       </c>
@@ -33405,7 +34972,7 @@
       </c>
       <c r="J81" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>433fs!@</v>
+        <v>333fs!@</v>
       </c>
       <c r="K81" t="str">
         <f t="shared" si="3"/>
@@ -33415,7 +34982,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
         <v>42</v>
       </c>
@@ -33443,7 +35010,7 @@
       </c>
       <c r="J82" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>499fs!@</v>
+        <v>682fs!@</v>
       </c>
       <c r="K82" t="str">
         <f t="shared" si="3"/>
@@ -33453,7 +35020,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
         <v>144</v>
       </c>
@@ -33481,7 +35048,7 @@
       </c>
       <c r="J83" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>147fo!@</v>
+        <v>230fo!@</v>
       </c>
       <c r="K83" t="str">
         <f t="shared" si="3"/>
@@ -33491,7 +35058,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
         <v>70</v>
       </c>
@@ -33519,7 +35086,7 @@
       </c>
       <c r="J84" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>510gs!@</v>
+        <v>388gs!@</v>
       </c>
       <c r="K84" t="str">
         <f t="shared" si="3"/>
@@ -33529,7 +35096,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
         <v>169</v>
       </c>
@@ -33555,7 +35122,7 @@
       </c>
       <c r="J85" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>220gs!@</v>
+        <v>681gs!@</v>
       </c>
       <c r="K85" t="str">
         <f t="shared" si="3"/>
@@ -33565,7 +35132,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
         <v>193</v>
       </c>
@@ -33591,7 +35158,7 @@
       </c>
       <c r="J86" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>129ia!@</v>
+        <v>830ia!@</v>
       </c>
       <c r="K86" t="str">
         <f t="shared" si="3"/>
@@ -33601,7 +35168,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
         <v>72</v>
       </c>
@@ -33629,7 +35196,7 @@
       </c>
       <c r="J87" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>669is!@</v>
+        <v>266is!@</v>
       </c>
       <c r="K87" t="str">
         <f t="shared" si="3"/>
@@ -33639,7 +35206,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
         <v>97</v>
       </c>
@@ -33667,7 +35234,7 @@
       </c>
       <c r="J88" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>265jc!@</v>
+        <v>137jc!@</v>
       </c>
       <c r="K88" t="str">
         <f t="shared" si="3"/>
@@ -33677,7 +35244,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
         <v>67</v>
       </c>
@@ -33703,7 +35270,7 @@
       </c>
       <c r="J89" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>377jf!@</v>
+        <v>534jf!@</v>
       </c>
       <c r="K89" t="str">
         <f t="shared" si="3"/>
@@ -33713,7 +35280,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
         <v>46</v>
       </c>
@@ -33741,7 +35308,7 @@
       </c>
       <c r="J90" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>939js!@</v>
+        <v>538js!@</v>
       </c>
       <c r="K90" t="str">
         <f t="shared" si="3"/>
@@ -33751,7 +35318,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
         <v>76</v>
       </c>
@@ -33779,7 +35346,7 @@
       </c>
       <c r="J91" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>760js!@</v>
+        <v>428js!@</v>
       </c>
       <c r="K91" t="str">
         <f t="shared" si="3"/>
@@ -33789,7 +35356,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
         <v>47</v>
       </c>
@@ -33817,7 +35384,7 @@
       </c>
       <c r="J92" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>527jp!@</v>
+        <v>574jp!@</v>
       </c>
       <c r="K92" t="str">
         <f t="shared" si="3"/>
@@ -33827,7 +35394,7 @@
         <v>669</v>
       </c>
     </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
         <v>203</v>
       </c>
@@ -33855,7 +35422,7 @@
       </c>
       <c r="J93" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>016jp!@</v>
+        <v>141jp!@</v>
       </c>
       <c r="K93" t="str">
         <f t="shared" si="3"/>
@@ -33865,7 +35432,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
         <v>78</v>
       </c>
@@ -33893,7 +35460,7 @@
       </c>
       <c r="J94" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>213jm!@</v>
+        <v>164jm!@</v>
       </c>
       <c r="K94" t="str">
         <f t="shared" si="3"/>
@@ -33903,7 +35470,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
         <v>82</v>
       </c>
@@ -33931,7 +35498,7 @@
       </c>
       <c r="J95" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>389jm!@</v>
+        <v>407jm!@</v>
       </c>
       <c r="K95" t="str">
         <f t="shared" si="3"/>
@@ -33941,7 +35508,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
         <v>181</v>
       </c>
@@ -33969,7 +35536,7 @@
       </c>
       <c r="J96" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>770js!@</v>
+        <v>661js!@</v>
       </c>
       <c r="K96" t="str">
         <f t="shared" si="3"/>
@@ -33979,7 +35546,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="97" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
         <v>86</v>
       </c>
@@ -34007,7 +35574,7 @@
       </c>
       <c r="J97" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>810js!@</v>
+        <v>804js!@</v>
       </c>
       <c r="K97" t="str">
         <f t="shared" si="3"/>
@@ -34017,7 +35584,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
         <v>85</v>
       </c>
@@ -34045,7 +35612,7 @@
       </c>
       <c r="J98" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>392ls!@</v>
+        <v>341ls!@</v>
       </c>
       <c r="K98" t="str">
         <f t="shared" si="3"/>
@@ -34055,7 +35622,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
         <v>129</v>
       </c>
@@ -34083,7 +35650,7 @@
       </c>
       <c r="J99" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>848ms!@</v>
+        <v>284ms!@</v>
       </c>
       <c r="K99" t="str">
         <f t="shared" si="3"/>
@@ -34093,7 +35660,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
         <v>225</v>
       </c>
@@ -34119,7 +35686,7 @@
       </c>
       <c r="J100" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>629mn!@</v>
+        <v>998mn!@</v>
       </c>
       <c r="K100" t="str">
         <f t="shared" si="3"/>
@@ -34129,7 +35696,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="101" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
         <v>237</v>
       </c>
@@ -34155,7 +35722,7 @@
       </c>
       <c r="J101" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>130ms!@</v>
+        <v>834ms!@</v>
       </c>
       <c r="K101" t="str">
         <f t="shared" si="3"/>
@@ -34165,7 +35732,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="102" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
         <v>191</v>
       </c>
@@ -34193,7 +35760,7 @@
       </c>
       <c r="J102" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>770mc!@</v>
+        <v>914mc!@</v>
       </c>
       <c r="K102" t="str">
         <f t="shared" si="3"/>
@@ -34203,7 +35770,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="103" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
         <v>57</v>
       </c>
@@ -34231,7 +35798,7 @@
       </c>
       <c r="J103" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>297nn!@</v>
+        <v>383nn!@</v>
       </c>
       <c r="K103" t="str">
         <f t="shared" si="3"/>
@@ -34241,7 +35808,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="104" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
         <v>102</v>
       </c>
@@ -34269,7 +35836,7 @@
       </c>
       <c r="J104" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>587pc!@</v>
+        <v>041pc!@</v>
       </c>
       <c r="K104" t="str">
         <f t="shared" si="3"/>
@@ -34279,7 +35846,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="105" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
         <v>104</v>
       </c>
@@ -34307,7 +35874,7 @@
       </c>
       <c r="J105" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>434rs!@</v>
+        <v>681rs!@</v>
       </c>
       <c r="K105" t="str">
         <f t="shared" si="3"/>
@@ -34317,7 +35884,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="106" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
         <v>251</v>
       </c>
@@ -34343,7 +35910,7 @@
       </c>
       <c r="J106" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>435rc!@</v>
+        <v>775rc!@</v>
       </c>
       <c r="K106" t="str">
         <f t="shared" si="3"/>
@@ -34353,7 +35920,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="107" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
         <v>58</v>
       </c>
@@ -34381,7 +35948,7 @@
       </c>
       <c r="J107" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>545rs!@</v>
+        <v>551rs!@</v>
       </c>
       <c r="K107" t="str">
         <f t="shared" si="3"/>
@@ -34391,7 +35958,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="108" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
         <v>62</v>
       </c>
@@ -34419,7 +35986,7 @@
       </c>
       <c r="J108" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>593ss!@</v>
+        <v>584ss!@</v>
       </c>
       <c r="K108" t="str">
         <f t="shared" si="3"/>
@@ -34429,7 +35996,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="109" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
         <v>11</v>
       </c>
@@ -34457,7 +36024,7 @@
       </c>
       <c r="J109" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>638sa!@</v>
+        <v>370sa!@</v>
       </c>
       <c r="K109" t="str">
         <f t="shared" si="3"/>
@@ -34467,7 +36034,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
         <v>274</v>
       </c>
@@ -34493,7 +36060,7 @@
       </c>
       <c r="J110" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>869tr!@</v>
+        <v>849tr!@</v>
       </c>
       <c r="K110" t="str">
         <f t="shared" si="3"/>
@@ -34503,7 +36070,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="111" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
         <v>281</v>
       </c>
@@ -34529,7 +36096,7 @@
       </c>
       <c r="J111" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>505vs!@</v>
+        <v>112vs!@</v>
       </c>
       <c r="K111" t="str">
         <f t="shared" si="3"/>
@@ -34539,7 +36106,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="112" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
         <v>206</v>
       </c>
@@ -34567,7 +36134,7 @@
       </c>
       <c r="J112" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>355wc!@</v>
+        <v>357wc!@</v>
       </c>
       <c r="K112" t="str">
         <f t="shared" si="3"/>
@@ -34577,7 +36144,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
         <v>175</v>
       </c>
@@ -34605,7 +36172,7 @@
       </c>
       <c r="J113" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>584ac!@</v>
+        <v>975ac!@</v>
       </c>
       <c r="K113" t="str">
         <f t="shared" si="3"/>
@@ -34615,7 +36182,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
         <v>51</v>
       </c>
@@ -34643,7 +36210,7 @@
       </c>
       <c r="J114" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>623ms!@</v>
+        <v>047ms!@</v>
       </c>
       <c r="K114" t="str">
         <f t="shared" si="3"/>
@@ -34653,7 +36220,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
         <v>530</v>
       </c>
@@ -34675,7 +36242,7 @@
       </c>
       <c r="J115" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>332tt!@</v>
+        <v>927tt!@</v>
       </c>
       <c r="K115" t="str">
         <f t="shared" si="3"/>
@@ -34685,7 +36252,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
         <v>532</v>
       </c>
@@ -34711,7 +36278,7 @@
       </c>
       <c r="J116" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>017ls!@</v>
+        <v>579ls!@</v>
       </c>
       <c r="K116" t="str">
         <f t="shared" si="3"/>
@@ -34721,7 +36288,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
         <v>536</v>
       </c>
@@ -34751,7 +36318,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="118" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
         <v>316</v>
       </c>
@@ -34779,7 +36346,7 @@
       </c>
       <c r="J118" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>676aa!@</v>
+        <v>566aa!@</v>
       </c>
       <c r="K118" t="str">
         <f t="shared" si="3"/>
@@ -34789,7 +36356,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="119" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
         <v>317</v>
       </c>
@@ -34817,7 +36384,7 @@
       </c>
       <c r="J119" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>759ap!@</v>
+        <v>212ap!@</v>
       </c>
       <c r="K119" t="str">
         <f t="shared" si="3"/>
@@ -34827,7 +36394,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="120" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
         <v>318</v>
       </c>
@@ -34855,7 +36422,7 @@
       </c>
       <c r="J120" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>061ao!@</v>
+        <v>587ao!@</v>
       </c>
       <c r="K120" t="str">
         <f t="shared" si="3"/>
@@ -34869,7 +36436,7 @@
         <v>Update QuestRH_Pessoas set Email = 'amanda.costa@enind.com.br' Where Nome = 'Amanda Silva Costa Oliveira';</v>
       </c>
     </row>
-    <row r="121" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
         <v>319</v>
       </c>
@@ -34897,7 +36464,7 @@
       </c>
       <c r="J121" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>144ae!@</v>
+        <v>865ae!@</v>
       </c>
       <c r="K121" t="str">
         <f t="shared" si="3"/>
@@ -34907,7 +36474,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="122" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
         <v>320</v>
       </c>
@@ -34935,7 +36502,7 @@
       </c>
       <c r="J122" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>967an!@</v>
+        <v>661an!@</v>
       </c>
       <c r="K122" t="str">
         <f t="shared" si="3"/>
@@ -34949,7 +36516,7 @@
         <v>Update QuestRH_Pessoas set Email = 'andre.nascimento@enindservicos.com.br' Where Nome = 'Andre Luiz do Nascimento';</v>
       </c>
     </row>
-    <row r="123" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
         <v>321</v>
       </c>
@@ -34977,7 +36544,7 @@
       </c>
       <c r="J123" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>079as!@</v>
+        <v>595as!@</v>
       </c>
       <c r="K123" t="str">
         <f t="shared" si="3"/>
@@ -34987,7 +36554,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="124" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
         <v>322</v>
       </c>
@@ -35015,7 +36582,7 @@
       </c>
       <c r="J124" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>037aa!@</v>
+        <v>521aa!@</v>
       </c>
       <c r="K124" t="str">
         <f t="shared" si="3"/>
@@ -35025,7 +36592,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="125" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
         <v>323</v>
       </c>
@@ -35053,7 +36620,7 @@
       </c>
       <c r="J125" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>551aj!@</v>
+        <v>717aj!@</v>
       </c>
       <c r="K125" t="str">
         <f t="shared" si="3"/>
@@ -35063,7 +36630,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="126" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
         <v>324</v>
       </c>
@@ -35091,7 +36658,7 @@
       </c>
       <c r="J126" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>322bs!@</v>
+        <v>346bs!@</v>
       </c>
       <c r="K126" t="str">
         <f t="shared" si="3"/>
@@ -35101,7 +36668,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="127" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
         <v>325</v>
       </c>
@@ -35129,7 +36696,7 @@
       </c>
       <c r="J127" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>967bl!@</v>
+        <v>318bl!@</v>
       </c>
       <c r="K127" t="str">
         <f t="shared" si="3"/>
@@ -35139,7 +36706,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="128" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
         <v>326</v>
       </c>
@@ -35167,7 +36734,7 @@
       </c>
       <c r="J128" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>322cm!@</v>
+        <v>939cm!@</v>
       </c>
       <c r="K128" t="str">
         <f t="shared" si="3"/>
@@ -35177,7 +36744,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="129" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
         <v>327</v>
       </c>
@@ -35205,7 +36772,7 @@
       </c>
       <c r="J129" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>183dc!@</v>
+        <v>182dc!@</v>
       </c>
       <c r="K129" t="str">
         <f t="shared" si="3"/>
@@ -35215,7 +36782,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="130" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
         <v>328</v>
       </c>
@@ -35243,7 +36810,7 @@
       </c>
       <c r="J130" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>379jm!@</v>
+        <v>870jm!@</v>
       </c>
       <c r="K130" t="str">
         <f t="shared" si="3"/>
@@ -35253,7 +36820,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="131" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
         <v>329</v>
       </c>
@@ -35281,7 +36848,7 @@
       </c>
       <c r="J131" t="str">
         <f t="shared" ref="J131:J155" ca="1" si="4">TEXT(RANDBETWEEN(1,999),"000") &amp; LEFT(H131,1) &amp; MID(H131,FIND(".",H131,1)+1,1) &amp; "!@"</f>
-        <v>151ef!@</v>
+        <v>385ef!@</v>
       </c>
       <c r="K131" t="str">
         <f t="shared" ref="K131:K155" si="5">"Update QuestRH_Pessoas set Senha = '" &amp; I131 &amp; "' Where Nome = '" &amp; A131 &amp; "';"</f>
@@ -35295,7 +36862,7 @@
         <v>Update QuestRH_Pessoas set Email = 'eder.fernandes@enindservicos.com.br' Where Nome = 'Eder da Silva Fernandes';</v>
       </c>
     </row>
-    <row r="132" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
         <v>330</v>
       </c>
@@ -35323,7 +36890,7 @@
       </c>
       <c r="J132" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>602el!@</v>
+        <v>001el!@</v>
       </c>
       <c r="K132" t="str">
         <f t="shared" si="5"/>
@@ -35337,7 +36904,7 @@
         <v>Update QuestRH_Pessoas set Email = 'emerson.leo@enindservicos.com.br' Where Nome = 'Emerson Marcelo Alves da Cunha de Leo';</v>
       </c>
     </row>
-    <row r="133" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
         <v>331</v>
       </c>
@@ -35365,7 +36932,7 @@
       </c>
       <c r="J133" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>881ia!@</v>
+        <v>513ia!@</v>
       </c>
       <c r="K133" t="str">
         <f t="shared" si="5"/>
@@ -35375,7 +36942,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="134" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
         <v>332</v>
       </c>
@@ -35403,7 +36970,7 @@
       </c>
       <c r="J134" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>395ia!@</v>
+        <v>652ia!@</v>
       </c>
       <c r="K134" t="str">
         <f t="shared" si="5"/>
@@ -35413,7 +36980,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="135" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
         <v>333</v>
       </c>
@@ -35441,7 +37008,7 @@
       </c>
       <c r="J135" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>374jr!@</v>
+        <v>998jr!@</v>
       </c>
       <c r="K135" t="str">
         <f t="shared" si="5"/>
@@ -35451,7 +37018,7 @@
         <v>711</v>
       </c>
     </row>
-    <row r="136" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
         <v>334</v>
       </c>
@@ -35479,7 +37046,7 @@
       </c>
       <c r="J136" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>436lr!@</v>
+        <v>738lr!@</v>
       </c>
       <c r="K136" t="str">
         <f t="shared" si="5"/>
@@ -35493,8 +37060,8 @@
       <c r="A137" s="2" t="s">
         <v>335</v>
       </c>
-      <c r="B137" s="2" t="s">
-        <v>372</v>
+      <c r="B137" s="3" t="s">
+        <v>434</v>
       </c>
       <c r="C137" s="2">
         <v>50000111</v>
@@ -35517,7 +37084,7 @@
       </c>
       <c r="J137" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>417jf!@</v>
+        <v>250jf!@</v>
       </c>
       <c r="K137" t="str">
         <f t="shared" si="5"/>
@@ -35527,7 +37094,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="138" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
         <v>336</v>
       </c>
@@ -35555,7 +37122,7 @@
       </c>
       <c r="J138" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>984lc!@</v>
+        <v>733lc!@</v>
       </c>
       <c r="K138" t="str">
         <f t="shared" si="5"/>
@@ -35565,7 +37132,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="139" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
         <v>337</v>
       </c>
@@ -35593,7 +37160,7 @@
       </c>
       <c r="J139" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>484lc!@</v>
+        <v>997lc!@</v>
       </c>
       <c r="K139" t="str">
         <f t="shared" si="5"/>
@@ -35603,7 +37170,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="140" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
         <v>338</v>
       </c>
@@ -35631,7 +37198,7 @@
       </c>
       <c r="J140" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>541ms!@</v>
+        <v>759ms!@</v>
       </c>
       <c r="K140" t="str">
         <f t="shared" si="5"/>
@@ -35641,7 +37208,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="141" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
         <v>339</v>
       </c>
@@ -35669,7 +37236,7 @@
       </c>
       <c r="J141" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>308ip!@</v>
+        <v>642ip!@</v>
       </c>
       <c r="K141" t="str">
         <f t="shared" si="5"/>
@@ -35679,7 +37246,7 @@
         <v>717</v>
       </c>
     </row>
-    <row r="142" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
         <v>340</v>
       </c>
@@ -35707,7 +37274,7 @@
       </c>
       <c r="J142" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>230mj!@</v>
+        <v>066mj!@</v>
       </c>
       <c r="K142" t="str">
         <f t="shared" si="5"/>
@@ -35717,7 +37284,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="143" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
         <v>341</v>
       </c>
@@ -35745,7 +37312,7 @@
       </c>
       <c r="J143" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>369mq!@</v>
+        <v>573mq!@</v>
       </c>
       <c r="K143" t="str">
         <f t="shared" si="5"/>
@@ -35759,7 +37326,7 @@
         <v>Update QuestRH_Pessoas set Email = 'marcos.queiroz@enindservicos.com.br' Where Nome = 'Marcos Souza Queiroz';</v>
       </c>
     </row>
-    <row r="144" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
         <v>342</v>
       </c>
@@ -35787,7 +37354,7 @@
       </c>
       <c r="J144" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>685mm!@</v>
+        <v>547mm!@</v>
       </c>
       <c r="K144" t="str">
         <f t="shared" si="5"/>
@@ -35797,7 +37364,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="145" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
         <v>343</v>
       </c>
@@ -35825,7 +37392,7 @@
       </c>
       <c r="J145" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>264ms!@</v>
+        <v>953ms!@</v>
       </c>
       <c r="K145" t="str">
         <f t="shared" si="5"/>
@@ -35835,7 +37402,7 @@
         <v>721</v>
       </c>
     </row>
-    <row r="146" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
         <v>344</v>
       </c>
@@ -35863,7 +37430,7 @@
       </c>
       <c r="J146" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>547ma!@</v>
+        <v>358ma!@</v>
       </c>
       <c r="K146" t="str">
         <f t="shared" si="5"/>
@@ -35877,7 +37444,7 @@
         <v>Update QuestRH_Pessoas set Email = 'milena.souza@enind.com.br' Where Nome = 'Milena Alkmin';</v>
       </c>
     </row>
-    <row r="147" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
         <v>345</v>
       </c>
@@ -35905,7 +37472,7 @@
       </c>
       <c r="J147" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>225ns!@</v>
+        <v>242ns!@</v>
       </c>
       <c r="K147" t="str">
         <f t="shared" si="5"/>
@@ -35915,7 +37482,7 @@
         <v>723</v>
       </c>
     </row>
-    <row r="148" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
         <v>346</v>
       </c>
@@ -35943,7 +37510,7 @@
       </c>
       <c r="J148" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>906nr!@</v>
+        <v>543nr!@</v>
       </c>
       <c r="K148" t="str">
         <f t="shared" si="5"/>
@@ -35953,7 +37520,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="149" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
         <v>347</v>
       </c>
@@ -35981,7 +37548,7 @@
       </c>
       <c r="J149" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>895rp!@</v>
+        <v>115rp!@</v>
       </c>
       <c r="K149" t="str">
         <f t="shared" si="5"/>
@@ -35991,7 +37558,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="150" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
         <v>348</v>
       </c>
@@ -36019,7 +37586,7 @@
       </c>
       <c r="J150" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>987ms!@</v>
+        <v>950ms!@</v>
       </c>
       <c r="K150" t="str">
         <f t="shared" si="5"/>
@@ -36029,7 +37596,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="151" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
         <v>349</v>
       </c>
@@ -36057,7 +37624,7 @@
       </c>
       <c r="J151" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>650rr!@</v>
+        <v>131rr!@</v>
       </c>
       <c r="K151" t="str">
         <f t="shared" si="5"/>
@@ -36067,7 +37634,7 @@
         <v>727</v>
       </c>
     </row>
-    <row r="152" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="s">
         <v>350</v>
       </c>
@@ -36095,7 +37662,7 @@
       </c>
       <c r="J152" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>584sp!@</v>
+        <v>790sp!@</v>
       </c>
       <c r="K152" t="str">
         <f t="shared" si="5"/>
@@ -36105,7 +37672,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="153" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
         <v>351</v>
       </c>
@@ -36133,7 +37700,7 @@
       </c>
       <c r="J153" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>454to!@</v>
+        <v>964to!@</v>
       </c>
       <c r="K153" t="str">
         <f t="shared" si="5"/>
@@ -36143,7 +37710,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="154" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
         <v>352</v>
       </c>
@@ -36171,7 +37738,7 @@
       </c>
       <c r="J154" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>119vs!@</v>
+        <v>121vs!@</v>
       </c>
       <c r="K154" t="str">
         <f t="shared" si="5"/>
@@ -36181,7 +37748,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="155" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
         <v>353</v>
       </c>
@@ -36209,7 +37776,7 @@
       </c>
       <c r="J155" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>605wb!@</v>
+        <v>546wb!@</v>
       </c>
       <c r="K155" t="str">
         <f t="shared" si="5"/>
@@ -36220,7 +37787,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L155" xr:uid="{C8A1FF41-FE38-442B-8F1A-E5C01AF500AB}"/>
+  <autoFilter ref="A1:L155" xr:uid="{C8A1FF41-FE38-442B-8F1A-E5C01AF500AB}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="Jose Martins Filho"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <hyperlinks>
     <hyperlink ref="B146" r:id="rId1" xr:uid="{CB604002-A099-420F-95F9-C5B760AE6CCF}"/>
     <hyperlink ref="B143" r:id="rId2" xr:uid="{57E8AD4A-C13E-4193-A104-E595FABE7BAB}"/>
@@ -36228,6 +37801,7 @@
     <hyperlink ref="B131" r:id="rId4" xr:uid="{7305BF19-2387-4BCE-9E6F-08C253156F83}"/>
     <hyperlink ref="B122" r:id="rId5" xr:uid="{0FC1207D-779B-4667-8897-E05E87AC0294}"/>
     <hyperlink ref="B120" r:id="rId6" xr:uid="{6C7E8E13-3570-4737-A8E5-2E4A62D64697}"/>
+    <hyperlink ref="B137" r:id="rId7" xr:uid="{DCCAE8D7-760C-40C9-AF58-2244010CCA4E}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/lista_emails.xlsx
+++ b/lista_emails.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Y:\Wagner\Programações\RH\Questionário ENIND\App\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://enindengenharia-my.sharepoint.com/personal/wagner_barreiro_enind_com_br/Documents/Área de Trabalho/Aplicativos/RH/App/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22BF655E-FB6C-4CA2-A20B-1C925A91A378}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="38" documentId="13_ncr:1_{22BF655E-FB6C-4CA2-A20B-1C925A91A378}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B7DFA2D4-2E65-4F48-9674-9A2BF43AC274}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4ABFC600-D865-440E-A0ED-FE29CA4E2163}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{4ABFC600-D865-440E-A0ED-FE29CA4E2163}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha2" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6547" uniqueCount="745">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6548" uniqueCount="745">
   <si>
     <t>Participante</t>
   </si>
@@ -2437,38 +2437,38 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
@@ -2477,407 +2477,7 @@
     <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="55">
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="15">
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -2971,9 +2571,20 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F3ADC3C7-E9A3-417B-9D36-7AAC353CADC8}" name="Tabela1" displayName="Tabela1" ref="A1:Q391" totalsRowShown="0">
   <autoFilter ref="A1:Q391" xr:uid="{F3ADC3C7-E9A3-417B-9D36-7AAC353CADC8}">
+    <filterColumn colId="3">
+      <filters>
+        <filter val="avaliador1"/>
+        <filter val="avaliador2"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="8">
+      <filters>
+        <filter val="Sim"/>
+      </filters>
+    </filterColumn>
     <filterColumn colId="11">
       <filters>
-        <filter val="A3"/>
+        <filter val="A2"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -2982,35 +2593,35 @@
     <tableColumn id="2" xr3:uid="{D83259D8-309A-419C-B320-342D6BCF6C73}" name="Avaliador"/>
     <tableColumn id="3" xr3:uid="{F718E0AE-C693-46A2-BFA3-CF2210C246D1}" name="Email"/>
     <tableColumn id="4" xr3:uid="{A5359983-F710-4EF4-8C33-6F6500DFDB37}" name="Tipo_aval"/>
-    <tableColumn id="5" xr3:uid="{96DAF741-F652-4764-BAFE-773BA36B7853}" name="login_aval" dataDxfId="54">
+    <tableColumn id="5" xr3:uid="{96DAF741-F652-4764-BAFE-773BA36B7853}" name="login_aval" dataDxfId="14">
       <calculatedColumnFormula>VLOOKUP(Tabela1[[#This Row],[Avaliador]],Usuários!A:I,COLUMN($H$1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{22419AAF-52BA-4B62-9776-309C5BEE8089}" name="senha_aval" dataDxfId="53">
+    <tableColumn id="6" xr3:uid="{22419AAF-52BA-4B62-9776-309C5BEE8089}" name="senha_aval" dataDxfId="13">
       <calculatedColumnFormula>VLOOKUP(Tabela1[[#This Row],[Avaliador]],Usuários!$A:$I,COLUMN($I$1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{47DDA20D-A3CB-45EC-8AE8-A9489754C0AC}" name="login_part" dataDxfId="52">
+    <tableColumn id="7" xr3:uid="{47DDA20D-A3CB-45EC-8AE8-A9489754C0AC}" name="login_part" dataDxfId="12">
       <calculatedColumnFormula>VLOOKUP(Tabela1[[#This Row],[Participante]],Usuários!$A:$I,COLUMN($H$1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{6430815F-B10A-450E-B596-4FE7DA66E86D}" name="senha_part" dataDxfId="51">
+    <tableColumn id="8" xr3:uid="{6430815F-B10A-450E-B596-4FE7DA66E86D}" name="senha_part" dataDxfId="11">
       <calculatedColumnFormula>VLOOKUP(Tabela1[[#This Row],[Participante]],Usuários!$A:$I,COLUMN($I$1),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{0330CC70-E56C-4012-A151-803C697AF08E}" name="Resp_Part" dataDxfId="50"/>
-    <tableColumn id="10" xr3:uid="{76F5BA88-8CFE-44F4-801E-8A7D571E304E}" name="Resp_Av1" dataDxfId="49"/>
+    <tableColumn id="9" xr3:uid="{0330CC70-E56C-4012-A151-803C697AF08E}" name="Resp_Part" dataDxfId="10"/>
+    <tableColumn id="10" xr3:uid="{76F5BA88-8CFE-44F4-801E-8A7D571E304E}" name="Resp_Av1" dataDxfId="9"/>
     <tableColumn id="11" xr3:uid="{047225E6-2D12-4983-8A0F-AED74119911D}" name="email_repres"/>
     <tableColumn id="12" xr3:uid="{99BA3D40-0EFE-4ADC-A508-AC5627461AC7}" name="Tipo_Av"/>
-    <tableColumn id="13" xr3:uid="{2F018D0F-7DDF-4FC2-99A7-3C257F39F107}" name="Status" dataDxfId="48">
+    <tableColumn id="13" xr3:uid="{2F018D0F-7DDF-4FC2-99A7-3C257F39F107}" name="Status" dataDxfId="8">
       <calculatedColumnFormula>IF(Tabela1[[#This Row],[Tipo_aval]]="auto","Ok",IF(ISERROR(VLOOKUP(Tabela1[[#This Row],[Participante]],Atualização!$B:$B,1,FALSE)),"Ok","Atualizar"))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{EB51F5FD-C129-4FA9-A58A-9531612CE03F}" name="Novo_Avaliador" dataDxfId="47">
+    <tableColumn id="14" xr3:uid="{EB51F5FD-C129-4FA9-A58A-9531612CE03F}" name="Novo_Avaliador" dataDxfId="7">
       <calculatedColumnFormula>IF(OR(Tabela1[[#This Row],[Status]]="Ok",Tabela1[[#This Row],[Tipo_aval]]="auto"),Tabela1[[#This Row],[Avaliador]],IF(Tabela1[[#This Row],[Tipo_aval]]="Avaliador1",VLOOKUP(Tabela1[[#This Row],[Participante]],Atualização!$B:$J,COLUMN($F$1)-1,FALSE),VLOOKUP(Tabela1[[#This Row],[Participante]],Atualização!$B:$J,COLUMN($H$1)-1,FALSE)))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{ACDBC65F-EC44-4DD7-AF4F-52D12A1BC0ED}" name="e-mail novo avaliador" dataDxfId="46">
+    <tableColumn id="15" xr3:uid="{ACDBC65F-EC44-4DD7-AF4F-52D12A1BC0ED}" name="e-mail novo avaliador" dataDxfId="6">
       <calculatedColumnFormula>IF(IFERROR(VLOOKUP(Tabela1[[#This Row],[Novo_Avaliador]],Usuários!$A:$B,2,FALSE),"")="","",IFERROR(VLOOKUP(Tabela1[[#This Row],[Novo_Avaliador]],Usuários!$A:$B,2,FALSE),""))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{C6408CAE-2C43-411D-B4E3-2615A2678B61}" name="Atualizado?" dataDxfId="45">
+    <tableColumn id="16" xr3:uid="{C6408CAE-2C43-411D-B4E3-2615A2678B61}" name="Atualizado?" dataDxfId="5">
       <calculatedColumnFormula>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{0B58B674-A96E-4F08-9366-C51A679445EC}" name="Coluna1" dataDxfId="44">
+    <tableColumn id="17" xr3:uid="{0B58B674-A96E-4F08-9366-C51A679445EC}" name="Coluna1" dataDxfId="4">
       <calculatedColumnFormula>Tabela1[[#This Row],[email_repres]]=Tabela1[[#This Row],[e-mail novo avaliador]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3340,7 +2951,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="37.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.85546875" customWidth="1"/>
     <col min="5" max="5" width="20.85546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13.140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
@@ -3471,7 +3082,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
@@ -6139,7 +5750,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>102</v>
       </c>
@@ -6201,7 +5812,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>25</v>
       </c>
@@ -6451,7 +6062,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>88</v>
       </c>
@@ -6513,7 +6124,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>83</v>
       </c>
@@ -6575,7 +6186,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>86</v>
       </c>
@@ -6823,7 +6434,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>97</v>
       </c>
@@ -6947,7 +6558,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>57</v>
       </c>
@@ -7009,7 +6620,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>102</v>
       </c>
@@ -7071,7 +6682,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>104</v>
       </c>
@@ -7133,7 +6744,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>32</v>
       </c>
@@ -7381,7 +6992,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>13</v>
       </c>
@@ -8749,7 +8360,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>9</v>
       </c>
@@ -8811,7 +8422,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
         <v>126</v>
       </c>
@@ -8873,7 +8484,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
         <v>72</v>
       </c>
@@ -8935,7 +8546,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
         <v>76</v>
       </c>
@@ -8997,7 +8608,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>47</v>
       </c>
@@ -9059,7 +8670,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>78</v>
       </c>
@@ -9121,7 +8732,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>82</v>
       </c>
@@ -9183,7 +8794,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
         <v>85</v>
       </c>
@@ -9245,7 +8856,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>129</v>
       </c>
@@ -9307,7 +8918,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>51</v>
       </c>
@@ -9431,7 +9042,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
         <v>72</v>
       </c>
@@ -9493,7 +9104,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>76</v>
       </c>
@@ -9555,7 +9166,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>78</v>
       </c>
@@ -9617,7 +9228,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>82</v>
       </c>
@@ -9679,7 +9290,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>85</v>
       </c>
@@ -9865,7 +9476,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
         <v>17</v>
       </c>
@@ -9927,7 +9538,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
         <v>141</v>
       </c>
@@ -9989,7 +9600,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
         <v>41</v>
       </c>
@@ -10051,7 +9662,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
         <v>144</v>
       </c>
@@ -10113,7 +9724,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>58</v>
       </c>
@@ -11730,7 +11341,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
         <v>13</v>
       </c>
@@ -12164,7 +11775,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
         <v>175</v>
       </c>
@@ -12226,7 +11837,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
         <v>189</v>
       </c>
@@ -12288,7 +11899,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>7</v>
       </c>
@@ -12350,7 +11961,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="146" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
         <v>187</v>
       </c>
@@ -12412,7 +12023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
         <v>30</v>
       </c>
@@ -12474,7 +12085,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="148" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
         <v>32</v>
       </c>
@@ -12598,7 +12209,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
         <v>42</v>
       </c>
@@ -12660,7 +12271,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
         <v>46</v>
       </c>
@@ -12722,7 +12333,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>181</v>
       </c>
@@ -12784,7 +12395,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>53</v>
       </c>
@@ -12846,7 +12457,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
         <v>191</v>
       </c>
@@ -12970,7 +12581,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="156" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
         <v>189</v>
       </c>
@@ -13032,7 +12643,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="157" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157" s="2" t="s">
         <v>187</v>
       </c>
@@ -13094,7 +12705,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="158" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>191</v>
       </c>
@@ -13156,7 +12767,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="159" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>11</v>
       </c>
@@ -13777,7 +13388,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="169" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="s">
         <v>22</v>
       </c>
@@ -13901,7 +13512,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="171" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A171" s="2" t="s">
         <v>70</v>
       </c>
@@ -13963,7 +13574,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>203</v>
       </c>
@@ -14025,7 +13636,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="173" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A173" s="2" t="s">
         <v>62</v>
       </c>
@@ -14087,7 +13698,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="174" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A174" s="2" t="s">
         <v>88</v>
       </c>
@@ -14149,7 +13760,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="175" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175" s="2" t="s">
         <v>83</v>
       </c>
@@ -14211,7 +13822,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="176" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176" s="2" t="s">
         <v>70</v>
       </c>
@@ -14273,7 +13884,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="177" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>86</v>
       </c>
@@ -14335,15 +13946,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="178" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>206</v>
       </c>
       <c r="B178" t="s">
         <v>67</v>
       </c>
-      <c r="C178" t="s">
-        <v>207</v>
+      <c r="C178" s="7" t="s">
+        <v>502</v>
       </c>
       <c r="D178" t="s">
         <v>297</v>
@@ -14354,7 +13965,7 @@
       </c>
       <c r="F178" s="2" t="str">
         <f>VLOOKUP(Tabela1[[#This Row],[Avaliador]],Usuários!$A:$I,COLUMN($I$1),0)</f>
-        <v>973jf!@</v>
+        <v>629jf!@</v>
       </c>
       <c r="G178" s="2" t="str">
         <f>VLOOKUP(Tabela1[[#This Row],[Participante]],Usuários!$A:$I,COLUMN($H$1),0)</f>
@@ -14365,13 +13976,13 @@
         <v>168wc!@</v>
       </c>
       <c r="I178" s="1" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="J178" s="1" t="s">
         <v>16</v>
       </c>
       <c r="K178" t="s">
-        <v>207</v>
+        <v>502</v>
       </c>
       <c r="L178" t="s">
         <v>307</v>
@@ -14386,7 +13997,7 @@
       </c>
       <c r="O178" t="str">
         <f>IF(IFERROR(VLOOKUP(Tabela1[[#This Row],[Novo_Avaliador]],Usuários!$A:$B,2,FALSE),"")="","",IFERROR(VLOOKUP(Tabela1[[#This Row],[Novo_Avaliador]],Usuários!$A:$B,2,FALSE),""))</f>
-        <v>joão.fernandes@enind.com.br</v>
+        <v>joao.fernandes@enind.com.br</v>
       </c>
       <c r="P178" t="str">
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
@@ -19053,7 +18664,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="254" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>17</v>
       </c>
@@ -22845,21 +22456,21 @@
         <v>321</v>
       </c>
       <c r="B315" t="s">
-        <v>291</v>
+        <v>77</v>
       </c>
       <c r="C315" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="D315" t="s">
         <v>303</v>
       </c>
       <c r="E315" s="2" t="str">
         <f>VLOOKUP(Tabela1[[#This Row],[Avaliador]],Usuários!A:I,COLUMN($H$1),0)</f>
-        <v>w.cristal</v>
+        <v>weslley.costa</v>
       </c>
       <c r="F315" s="2" t="str">
         <f>VLOOKUP(Tabela1[[#This Row],[Avaliador]],Usuários!$A:$I,COLUMN($I$1),0)</f>
-        <v>996wc!@</v>
+        <v>370wc!@</v>
       </c>
       <c r="G315" s="2" t="str">
         <f>VLOOKUP(Tabela1[[#This Row],[Participante]],Usuários!$A:$I,COLUMN($H$1),0)</f>
@@ -22876,7 +22487,7 @@
         <v>16</v>
       </c>
       <c r="K315" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="L315" t="s">
         <v>309</v>
@@ -22885,13 +22496,12 @@
         <f>IF(Tabela1[[#This Row],[Tipo_aval]]="auto","Ok",IF(ISERROR(VLOOKUP(Tabela1[[#This Row],[Participante]],Atualização!$B:$B,1,FALSE)),"Ok","Atualizar"))</f>
         <v>Ok</v>
       </c>
-      <c r="N315" t="str">
-        <f>IF(OR(Tabela1[[#This Row],[Status]]="Ok",Tabela1[[#This Row],[Tipo_aval]]="auto"),Tabela1[[#This Row],[Avaliador]],IF(Tabela1[[#This Row],[Tipo_aval]]="Avaliador1",VLOOKUP(Tabela1[[#This Row],[Participante]],Atualização!$B:$J,COLUMN($F$1)-1,FALSE),VLOOKUP(Tabela1[[#This Row],[Participante]],Atualização!$B:$J,COLUMN($H$1)-1,FALSE)))</f>
-        <v>Wiringhton Cristal Araujo</v>
+      <c r="N315" t="s">
+        <v>77</v>
       </c>
       <c r="O315" t="str">
         <f>IF(IFERROR(VLOOKUP(Tabela1[[#This Row],[Novo_Avaliador]],Usuários!$A:$B,2,FALSE),"")="","",IFERROR(VLOOKUP(Tabela1[[#This Row],[Novo_Avaliador]],Usuários!$A:$B,2,FALSE),""))</f>
-        <v>w.cristal@enind.com.br</v>
+        <v>weslley.costa@enind.com.br</v>
       </c>
       <c r="P315" t="str">
         <f>IF(Tabela1[[#This Row],[Novo_Avaliador]]=Tabela1[[#This Row],[Avaliador]],"Sim","Não")</f>
@@ -24954,7 +24564,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="349" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
         <v>25</v>
       </c>
@@ -25391,7 +25001,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="356" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
         <v>47</v>
       </c>
@@ -27631,10 +27241,10 @@
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="I1:J1048576">
-    <cfRule type="cellIs" dxfId="39" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
       <formula>"Não"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="38" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="4" operator="equal">
       <formula>"Sim"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -27652,11 +27262,12 @@
     <hyperlink ref="K194" r:id="rId11" xr:uid="{FA0BE04D-ACA5-4D25-B3BC-690007E40812}"/>
     <hyperlink ref="K366" r:id="rId12" xr:uid="{80DA185F-D7E7-4537-A466-7ADC2B6C98BE}"/>
     <hyperlink ref="K199" r:id="rId13" xr:uid="{9DE20185-22E7-4B36-AA47-9396DC30E6D9}"/>
+    <hyperlink ref="C178" r:id="rId14" display="joão.fernandes@enind.com.br" xr:uid="{99745A9E-1F05-4C29-A73A-2FA60787FE55}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId14"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId15"/>
   <tableParts count="1">
-    <tablePart r:id="rId15"/>
+    <tablePart r:id="rId16"/>
   </tableParts>
 </worksheet>
 </file>
@@ -32560,6 +32171,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8A1FF41-FE38-442B-8F1A-E5C01AF500AB}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:N154"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -32608,7 +32220,7 @@
         <v>738</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>71</v>
       </c>
@@ -32634,7 +32246,7 @@
       </c>
       <c r="J2" t="str">
         <f ca="1">TEXT(RANDBETWEEN(1,999),"000") &amp; LEFT(H2,1) &amp; MID(H2,FIND(".",H2,1)+1,1) &amp; "!@"</f>
-        <v>638wf!@</v>
+        <v>716wf!@</v>
       </c>
       <c r="K2" t="str">
         <f>"Update QuestRH_Pessoas set Senha = '" &amp; I2 &amp; "' Where Nome = '" &amp; A2 &amp; "';"</f>
@@ -32648,7 +32260,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>77</v>
       </c>
@@ -32674,7 +32286,7 @@
       </c>
       <c r="J3" t="str">
         <f t="shared" ref="J3:J65" ca="1" si="0">TEXT(RANDBETWEEN(1,999),"000") &amp; LEFT(H3,1) &amp; MID(H3,FIND(".",H3,1)+1,1) &amp; "!@"</f>
-        <v>815wc!@</v>
+        <v>419wc!@</v>
       </c>
       <c r="K3" t="str">
         <f t="shared" ref="K3:K65" si="1">"Update QuestRH_Pessoas set Senha = '" &amp; I3 &amp; "' Where Nome = '" &amp; A3 &amp; "';"</f>
@@ -32688,7 +32300,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>257</v>
       </c>
@@ -32714,7 +32326,7 @@
       </c>
       <c r="J4" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>090ws!@</v>
+        <v>950ws!@</v>
       </c>
       <c r="K4" t="str">
         <f t="shared" si="1"/>
@@ -32728,7 +32340,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>15</v>
       </c>
@@ -32754,7 +32366,7 @@
       </c>
       <c r="J5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>935wm!@</v>
+        <v>767wm!@</v>
       </c>
       <c r="K5" t="str">
         <f t="shared" si="1"/>
@@ -32768,7 +32380,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>272</v>
       </c>
@@ -32794,7 +32406,7 @@
       </c>
       <c r="J6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>573wf!@</v>
+        <v>438wf!@</v>
       </c>
       <c r="K6" t="str">
         <f t="shared" si="1"/>
@@ -32808,7 +32420,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>291</v>
       </c>
@@ -32834,7 +32446,7 @@
       </c>
       <c r="J7" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>398wc!@</v>
+        <v>382wc!@</v>
       </c>
       <c r="K7" t="str">
         <f t="shared" si="1"/>
@@ -32848,7 +32460,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>266</v>
       </c>
@@ -32874,7 +32486,7 @@
       </c>
       <c r="J8" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>194vx!@</v>
+        <v>389vx!@</v>
       </c>
       <c r="K8" t="str">
         <f t="shared" si="1"/>
@@ -32888,7 +32500,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>31</v>
       </c>
@@ -32914,7 +32526,7 @@
       </c>
       <c r="J9" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>314vs!@</v>
+        <v>138vs!@</v>
       </c>
       <c r="K9" t="str">
         <f t="shared" si="1"/>
@@ -32928,7 +32540,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>277</v>
       </c>
@@ -32954,7 +32566,7 @@
       </c>
       <c r="J10" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>194ub!@</v>
+        <v>204ub!@</v>
       </c>
       <c r="K10" t="str">
         <f t="shared" si="1"/>
@@ -32968,7 +32580,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>94</v>
       </c>
@@ -32994,7 +32606,7 @@
       </c>
       <c r="J11" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>844to!@</v>
+        <v>236to!@</v>
       </c>
       <c r="K11" t="str">
         <f t="shared" si="1"/>
@@ -33008,7 +32620,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>268</v>
       </c>
@@ -33034,7 +32646,7 @@
       </c>
       <c r="J12" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>542ta!@</v>
+        <v>670ta!@</v>
       </c>
       <c r="K12" t="str">
         <f t="shared" si="1"/>
@@ -33048,7 +32660,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>52</v>
       </c>
@@ -33074,7 +32686,7 @@
       </c>
       <c r="J13" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>127ta!@</v>
+        <v>383ta!@</v>
       </c>
       <c r="K13" t="str">
         <f t="shared" si="1"/>
@@ -33088,7 +32700,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>220</v>
       </c>
@@ -33114,7 +32726,7 @@
       </c>
       <c r="J14" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>158tp!@</v>
+        <v>618tp!@</v>
       </c>
       <c r="K14" t="str">
         <f t="shared" si="1"/>
@@ -33128,7 +32740,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>260</v>
       </c>
@@ -33154,7 +32766,7 @@
       </c>
       <c r="J15" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>504rs!@</v>
+        <v>224rs!@</v>
       </c>
       <c r="K15" t="str">
         <f t="shared" si="1"/>
@@ -33168,7 +32780,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>24</v>
       </c>
@@ -33194,7 +32806,7 @@
       </c>
       <c r="J16" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>807rm!@</v>
+        <v>421rm!@</v>
       </c>
       <c r="K16" t="str">
         <f t="shared" si="1"/>
@@ -33208,7 +32820,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>254</v>
       </c>
@@ -33234,7 +32846,7 @@
       </c>
       <c r="J17" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>068rm!@</v>
+        <v>237rm!@</v>
       </c>
       <c r="K17" t="str">
         <f t="shared" si="1"/>
@@ -33248,7 +32860,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>155</v>
       </c>
@@ -33274,7 +32886,7 @@
       </c>
       <c r="J18" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>366ra!@</v>
+        <v>433ra!@</v>
       </c>
       <c r="K18" t="str">
         <f t="shared" si="1"/>
@@ -33288,7 +32900,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>164</v>
       </c>
@@ -33314,7 +32926,7 @@
       </c>
       <c r="J19" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>150pm!@</v>
+        <v>375pm!@</v>
       </c>
       <c r="K19" t="str">
         <f t="shared" si="1"/>
@@ -33328,7 +32940,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>245</v>
       </c>
@@ -33354,7 +32966,7 @@
       </c>
       <c r="J20" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>842pa!@</v>
+        <v>089pa!@</v>
       </c>
       <c r="K20" t="str">
         <f t="shared" si="1"/>
@@ -33368,7 +32980,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>167</v>
       </c>
@@ -33394,7 +33006,7 @@
       </c>
       <c r="J21" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>592mg!@</v>
+        <v>771mg!@</v>
       </c>
       <c r="K21" t="str">
         <f t="shared" si="1"/>
@@ -33408,7 +33020,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>185</v>
       </c>
@@ -33434,7 +33046,7 @@
       </c>
       <c r="J22" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>870mc!@</v>
+        <v>894mc!@</v>
       </c>
       <c r="K22" t="str">
         <f t="shared" si="1"/>
@@ -33448,7 +33060,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>240</v>
       </c>
@@ -33474,7 +33086,7 @@
       </c>
       <c r="J23" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>743ms!@</v>
+        <v>658ms!@</v>
       </c>
       <c r="K23" t="str">
         <f t="shared" si="1"/>
@@ -33488,7 +33100,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>234</v>
       </c>
@@ -33514,7 +33126,7 @@
       </c>
       <c r="J24" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>067ms!@</v>
+        <v>740ms!@</v>
       </c>
       <c r="K24" t="str">
         <f t="shared" si="1"/>
@@ -33528,7 +33140,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>53</v>
       </c>
@@ -33552,7 +33164,7 @@
       </c>
       <c r="J25" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>719mb!@</v>
+        <v>565mb!@</v>
       </c>
       <c r="K25" t="str">
         <f t="shared" si="1"/>
@@ -33566,7 +33178,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>230</v>
       </c>
@@ -33592,7 +33204,7 @@
       </c>
       <c r="J26" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>758ms!@</v>
+        <v>311ms!@</v>
       </c>
       <c r="K26" t="str">
         <f t="shared" si="1"/>
@@ -33606,7 +33218,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>227</v>
       </c>
@@ -33632,7 +33244,7 @@
       </c>
       <c r="J27" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>092lf!@</v>
+        <v>342lf!@</v>
       </c>
       <c r="K27" t="str">
         <f t="shared" si="1"/>
@@ -33646,7 +33258,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>222</v>
       </c>
@@ -33672,7 +33284,7 @@
       </c>
       <c r="J28" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>107lb!@</v>
+        <v>665lb!@</v>
       </c>
       <c r="K28" t="str">
         <f t="shared" si="1"/>
@@ -33686,7 +33298,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>123</v>
       </c>
@@ -33712,7 +33324,7 @@
       </c>
       <c r="J29" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>741la!@</v>
+        <v>031la!@</v>
       </c>
       <c r="K29" t="str">
         <f t="shared" si="1"/>
@@ -33726,7 +33338,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>68</v>
       </c>
@@ -33752,7 +33364,7 @@
       </c>
       <c r="J30" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>244ls!@</v>
+        <v>448ls!@</v>
       </c>
       <c r="K30" t="str">
         <f t="shared" si="1"/>
@@ -33766,7 +33378,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>65</v>
       </c>
@@ -33792,7 +33404,7 @@
       </c>
       <c r="J31" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>045js!@</v>
+        <v>882js!@</v>
       </c>
       <c r="K31" t="str">
         <f t="shared" si="1"/>
@@ -33806,7 +33418,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>212</v>
       </c>
@@ -33832,7 +33444,7 @@
       </c>
       <c r="J32" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>941jm!@</v>
+        <v>632jm!@</v>
       </c>
       <c r="K32" t="str">
         <f t="shared" si="1"/>
@@ -33846,7 +33458,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>99</v>
       </c>
@@ -33872,7 +33484,7 @@
       </c>
       <c r="J33" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>024ja!@</v>
+        <v>993ja!@</v>
       </c>
       <c r="K33" t="str">
         <f t="shared" si="1"/>
@@ -33886,7 +33498,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>209</v>
       </c>
@@ -33912,7 +33524,7 @@
       </c>
       <c r="J34" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>200js!@</v>
+        <v>623js!@</v>
       </c>
       <c r="K34" t="str">
         <f t="shared" si="1"/>
@@ -33926,12 +33538,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>67</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>207</v>
+        <v>502</v>
       </c>
       <c r="C35" s="2">
         <v>50000121</v>
@@ -33948,15 +33560,15 @@
         <v>296</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>612</v>
+        <v>666</v>
       </c>
       <c r="J35" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>216jf!@</v>
+        <v>036jf!@</v>
       </c>
       <c r="K35" t="str">
         <f t="shared" si="1"/>
-        <v>Update QuestRH_Pessoas set Senha = '973jf!@' Where Nome = 'João Fernandes';</v>
+        <v>Update QuestRH_Pessoas set Senha = '629jf!@' Where Nome = 'João Fernandes';</v>
       </c>
       <c r="L35" s="2" t="s">
         <v>612</v>
@@ -33966,7 +33578,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>23</v>
       </c>
@@ -33992,7 +33604,7 @@
       </c>
       <c r="J36" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>912jr!@</v>
+        <v>920jr!@</v>
       </c>
       <c r="K36" t="str">
         <f t="shared" si="1"/>
@@ -34006,7 +33618,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>196</v>
       </c>
@@ -34032,7 +33644,7 @@
       </c>
       <c r="J37" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>851ja!@</v>
+        <v>965ja!@</v>
       </c>
       <c r="K37" t="str">
         <f t="shared" si="1"/>
@@ -34046,7 +33658,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>8</v>
       </c>
@@ -34072,7 +33684,7 @@
       </c>
       <c r="J38" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>938ht!@</v>
+        <v>569ht!@</v>
       </c>
       <c r="K38" t="str">
         <f t="shared" si="1"/>
@@ -34086,7 +33698,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>63</v>
       </c>
@@ -34112,7 +33724,7 @@
       </c>
       <c r="J39" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>031hk!@</v>
+        <v>080hk!@</v>
       </c>
       <c r="K39" t="str">
         <f t="shared" si="1"/>
@@ -34126,7 +33738,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>117</v>
       </c>
@@ -34152,7 +33764,7 @@
       </c>
       <c r="J40" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>778gl!@</v>
+        <v>780gl!@</v>
       </c>
       <c r="K40" t="str">
         <f t="shared" si="1"/>
@@ -34166,7 +33778,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>159</v>
       </c>
@@ -34192,7 +33804,7 @@
       </c>
       <c r="J41" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>757gp!@</v>
+        <v>155gp!@</v>
       </c>
       <c r="K41" t="str">
         <f t="shared" si="1"/>
@@ -34206,7 +33818,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>161</v>
       </c>
@@ -34232,7 +33844,7 @@
       </c>
       <c r="J42" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>758gl!@</v>
+        <v>375gl!@</v>
       </c>
       <c r="K42" t="str">
         <f t="shared" si="1"/>
@@ -34246,7 +33858,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>147</v>
       </c>
@@ -34272,7 +33884,7 @@
       </c>
       <c r="J43" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>194fc!@</v>
+        <v>090fc!@</v>
       </c>
       <c r="K43" t="str">
         <f t="shared" si="1"/>
@@ -34312,7 +33924,7 @@
       </c>
       <c r="J44" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>259fb!@</v>
+        <v>361fb!@</v>
       </c>
       <c r="K44" t="str">
         <f t="shared" si="1"/>
@@ -34326,7 +33938,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>151</v>
       </c>
@@ -34352,7 +33964,7 @@
       </c>
       <c r="J45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>168fc!@</v>
+        <v>345fc!@</v>
       </c>
       <c r="K45" t="str">
         <f t="shared" si="1"/>
@@ -34366,7 +33978,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>126</v>
       </c>
@@ -34392,7 +34004,7 @@
       </c>
       <c r="J46" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>825es!@</v>
+        <v>534es!@</v>
       </c>
       <c r="K46" t="str">
         <f t="shared" si="1"/>
@@ -34406,7 +34018,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>18</v>
       </c>
@@ -34432,7 +34044,7 @@
       </c>
       <c r="J47" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>896eb!@</v>
+        <v>598eb!@</v>
       </c>
       <c r="K47" t="str">
         <f t="shared" si="1"/>
@@ -34446,7 +34058,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>10</v>
       </c>
@@ -34472,7 +34084,7 @@
       </c>
       <c r="J48" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>101es!@</v>
+        <v>163es!@</v>
       </c>
       <c r="K48" t="str">
         <f t="shared" si="1"/>
@@ -34486,7 +34098,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>112</v>
       </c>
@@ -34512,7 +34124,7 @@
       </c>
       <c r="J49" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>974ei!@</v>
+        <v>359ei!@</v>
       </c>
       <c r="K49" t="str">
         <f t="shared" si="1"/>
@@ -34526,7 +34138,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>109</v>
       </c>
@@ -34552,7 +34164,7 @@
       </c>
       <c r="J50" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>656eb!@</v>
+        <v>900eb!@</v>
       </c>
       <c r="K50" t="str">
         <f t="shared" si="1"/>
@@ -34566,7 +34178,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>14</v>
       </c>
@@ -34592,7 +34204,7 @@
       </c>
       <c r="J51" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>316en!@</v>
+        <v>388en!@</v>
       </c>
       <c r="K51" t="str">
         <f t="shared" si="1"/>
@@ -34606,7 +34218,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>37</v>
       </c>
@@ -34632,7 +34244,7 @@
       </c>
       <c r="J52" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>376em!@</v>
+        <v>583em!@</v>
       </c>
       <c r="K52" t="str">
         <f t="shared" si="1"/>
@@ -34646,7 +34258,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>91</v>
       </c>
@@ -34672,7 +34284,7 @@
       </c>
       <c r="J53" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>250ep!@</v>
+        <v>974ep!@</v>
       </c>
       <c r="K53" t="str">
         <f t="shared" si="1"/>
@@ -34686,7 +34298,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>79</v>
       </c>
@@ -34712,7 +34324,7 @@
       </c>
       <c r="J54" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>202ds!@</v>
+        <v>465ds!@</v>
       </c>
       <c r="K54" t="str">
         <f t="shared" si="1"/>
@@ -34726,7 +34338,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>73</v>
       </c>
@@ -34752,7 +34364,7 @@
       </c>
       <c r="J55" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>494da!@</v>
+        <v>811da!@</v>
       </c>
       <c r="K55" t="str">
         <f t="shared" si="1"/>
@@ -34766,7 +34378,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>59</v>
       </c>
@@ -34792,7 +34404,7 @@
       </c>
       <c r="J56" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>642ds!@</v>
+        <v>723ds!@</v>
       </c>
       <c r="K56" t="str">
         <f t="shared" si="1"/>
@@ -34806,7 +34418,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>54</v>
       </c>
@@ -34832,7 +34444,7 @@
       </c>
       <c r="J57" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>919dc!@</v>
+        <v>486dc!@</v>
       </c>
       <c r="K57" t="str">
         <f t="shared" si="1"/>
@@ -34846,7 +34458,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>48</v>
       </c>
@@ -34872,7 +34484,7 @@
       </c>
       <c r="J58" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>910cg!@</v>
+        <v>918cg!@</v>
       </c>
       <c r="K58" t="str">
         <f t="shared" si="1"/>
@@ -34886,7 +34498,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>43</v>
       </c>
@@ -34912,7 +34524,7 @@
       </c>
       <c r="J59" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>289bc!@</v>
+        <v>011bc!@</v>
       </c>
       <c r="K59" t="str">
         <f t="shared" si="1"/>
@@ -34926,7 +34538,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>38</v>
       </c>
@@ -34952,7 +34564,7 @@
       </c>
       <c r="J60" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>988af!@</v>
+        <v>103af!@</v>
       </c>
       <c r="K60" t="str">
         <f t="shared" si="1"/>
@@ -34966,7 +34578,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>27</v>
       </c>
@@ -34992,7 +34604,7 @@
       </c>
       <c r="J61" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>792aa!@</v>
+        <v>415aa!@</v>
       </c>
       <c r="K61" t="str">
         <f t="shared" si="1"/>
@@ -35006,7 +34618,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>19</v>
       </c>
@@ -35032,7 +34644,7 @@
       </c>
       <c r="J62" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>034at!@</v>
+        <v>194at!@</v>
       </c>
       <c r="K62" t="str">
         <f t="shared" si="1"/>
@@ -35046,7 +34658,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>3</v>
       </c>
@@ -35072,7 +34684,7 @@
       </c>
       <c r="J63" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>350ac!@</v>
+        <v>931ac!@</v>
       </c>
       <c r="K63" t="str">
         <f t="shared" si="1"/>
@@ -35086,7 +34698,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>189</v>
       </c>
@@ -35114,7 +34726,7 @@
       </c>
       <c r="J64" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>151as!@</v>
+        <v>857as!@</v>
       </c>
       <c r="K64" t="str">
         <f t="shared" si="1"/>
@@ -35128,7 +34740,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>33</v>
       </c>
@@ -35154,7 +34766,7 @@
       </c>
       <c r="J65" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>306ad!@</v>
+        <v>074ad!@</v>
       </c>
       <c r="K65" t="str">
         <f t="shared" si="1"/>
@@ -35168,7 +34780,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>88</v>
       </c>
@@ -35196,7 +34808,7 @@
       </c>
       <c r="J66" t="str">
         <f t="shared" ref="J66:J129" ca="1" si="3">TEXT(RANDBETWEEN(1,999),"000") &amp; LEFT(H66,1) &amp; MID(H66,FIND(".",H66,1)+1,1) &amp; "!@"</f>
-        <v>607af!@</v>
+        <v>397af!@</v>
       </c>
       <c r="K66" t="str">
         <f t="shared" ref="K66:K129" si="4">"Update QuestRH_Pessoas set Senha = '" &amp; I66 &amp; "' Where Nome = '" &amp; A66 &amp; "';"</f>
@@ -35210,7 +34822,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>7</v>
       </c>
@@ -35238,7 +34850,7 @@
       </c>
       <c r="J67" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>450ap!@</v>
+        <v>297ap!@</v>
       </c>
       <c r="K67" t="str">
         <f t="shared" si="4"/>
@@ -35252,7 +34864,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>9</v>
       </c>
@@ -35280,7 +34892,7 @@
       </c>
       <c r="J68" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>775al!@</v>
+        <v>371al!@</v>
       </c>
       <c r="K68" t="str">
         <f t="shared" si="4"/>
@@ -35294,7 +34906,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>13</v>
       </c>
@@ -35322,7 +34934,7 @@
       </c>
       <c r="J69" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>879as!@</v>
+        <v>358as!@</v>
       </c>
       <c r="K69" t="str">
         <f t="shared" si="4"/>
@@ -35336,7 +34948,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>187</v>
       </c>
@@ -35364,7 +34976,7 @@
       </c>
       <c r="J70" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>831at!@</v>
+        <v>250at!@</v>
       </c>
       <c r="K70" t="str">
         <f t="shared" si="4"/>
@@ -35378,7 +34990,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>83</v>
       </c>
@@ -35406,7 +35018,7 @@
       </c>
       <c r="J71" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>960cm!@</v>
+        <v>326cm!@</v>
       </c>
       <c r="K71" t="str">
         <f t="shared" si="4"/>
@@ -35420,7 +35032,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
         <v>17</v>
       </c>
@@ -35448,7 +35060,7 @@
       </c>
       <c r="J72" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>374ds!@</v>
+        <v>258ds!@</v>
       </c>
       <c r="K72" t="str">
         <f t="shared" si="4"/>
@@ -35462,7 +35074,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
         <v>22</v>
       </c>
@@ -35490,7 +35102,7 @@
       </c>
       <c r="J73" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>395ds!@</v>
+        <v>961ds!@</v>
       </c>
       <c r="K73" t="str">
         <f t="shared" si="4"/>
@@ -35504,7 +35116,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>25</v>
       </c>
@@ -35532,7 +35144,7 @@
       </c>
       <c r="J74" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>378dc!@</v>
+        <v>672dc!@</v>
       </c>
       <c r="K74" t="str">
         <f t="shared" si="4"/>
@@ -35546,7 +35158,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
         <v>30</v>
       </c>
@@ -35574,7 +35186,7 @@
       </c>
       <c r="J75" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>112dd!@</v>
+        <v>682dd!@</v>
       </c>
       <c r="K75" t="str">
         <f t="shared" si="4"/>
@@ -35588,7 +35200,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
         <v>32</v>
       </c>
@@ -35616,7 +35228,7 @@
       </c>
       <c r="J76" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>821dm!@</v>
+        <v>647dm!@</v>
       </c>
       <c r="K76" t="str">
         <f t="shared" si="4"/>
@@ -35630,7 +35242,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
         <v>141</v>
       </c>
@@ -35658,7 +35270,7 @@
       </c>
       <c r="J77" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>452eg!@</v>
+        <v>197eg!@</v>
       </c>
       <c r="K77" t="str">
         <f t="shared" si="4"/>
@@ -35672,7 +35284,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
         <v>41</v>
       </c>
@@ -35700,7 +35312,7 @@
       </c>
       <c r="J78" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>334er!@</v>
+        <v>225er!@</v>
       </c>
       <c r="K78" t="str">
         <f t="shared" si="4"/>
@@ -35714,7 +35326,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
         <v>120</v>
       </c>
@@ -35740,7 +35352,7 @@
       </c>
       <c r="J79" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>078ep!@</v>
+        <v>436ep!@</v>
       </c>
       <c r="K79" t="str">
         <f t="shared" si="4"/>
@@ -35754,7 +35366,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
         <v>148</v>
       </c>
@@ -35780,7 +35392,7 @@
       </c>
       <c r="J80" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>051fs!@</v>
+        <v>457fs!@</v>
       </c>
       <c r="K80" t="str">
         <f t="shared" si="4"/>
@@ -35794,7 +35406,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
         <v>42</v>
       </c>
@@ -35822,7 +35434,7 @@
       </c>
       <c r="J81" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>665fs!@</v>
+        <v>645fs!@</v>
       </c>
       <c r="K81" t="str">
         <f t="shared" si="4"/>
@@ -35836,7 +35448,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
         <v>144</v>
       </c>
@@ -35864,7 +35476,7 @@
       </c>
       <c r="J82" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>427fo!@</v>
+        <v>190fo!@</v>
       </c>
       <c r="K82" t="str">
         <f t="shared" si="4"/>
@@ -35878,7 +35490,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
         <v>70</v>
       </c>
@@ -35906,7 +35518,7 @@
       </c>
       <c r="J83" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>453gs!@</v>
+        <v>286gs!@</v>
       </c>
       <c r="K83" t="str">
         <f t="shared" si="4"/>
@@ -35920,7 +35532,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
         <v>169</v>
       </c>
@@ -35946,7 +35558,7 @@
       </c>
       <c r="J84" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>558gs!@</v>
+        <v>288gs!@</v>
       </c>
       <c r="K84" t="str">
         <f t="shared" si="4"/>
@@ -35960,7 +35572,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
         <v>193</v>
       </c>
@@ -35986,7 +35598,7 @@
       </c>
       <c r="J85" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>249ia!@</v>
+        <v>470ia!@</v>
       </c>
       <c r="K85" t="str">
         <f t="shared" si="4"/>
@@ -36000,7 +35612,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
         <v>72</v>
       </c>
@@ -36028,7 +35640,7 @@
       </c>
       <c r="J86" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>685is!@</v>
+        <v>209is!@</v>
       </c>
       <c r="K86" t="str">
         <f t="shared" si="4"/>
@@ -36042,7 +35654,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
         <v>97</v>
       </c>
@@ -36070,7 +35682,7 @@
       </c>
       <c r="J87" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>586jc!@</v>
+        <v>385jc!@</v>
       </c>
       <c r="K87" t="str">
         <f t="shared" si="4"/>
@@ -36084,7 +35696,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
         <v>67</v>
       </c>
@@ -36110,7 +35722,7 @@
       </c>
       <c r="J88" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>250jf!@</v>
+        <v>950jf!@</v>
       </c>
       <c r="K88" t="str">
         <f t="shared" si="4"/>
@@ -36124,7 +35736,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
         <v>46</v>
       </c>
@@ -36152,7 +35764,7 @@
       </c>
       <c r="J89" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>234js!@</v>
+        <v>930js!@</v>
       </c>
       <c r="K89" t="str">
         <f t="shared" si="4"/>
@@ -36166,7 +35778,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
         <v>76</v>
       </c>
@@ -36194,7 +35806,7 @@
       </c>
       <c r="J90" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>912js!@</v>
+        <v>866js!@</v>
       </c>
       <c r="K90" t="str">
         <f t="shared" si="4"/>
@@ -36208,7 +35820,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
         <v>47</v>
       </c>
@@ -36236,7 +35848,7 @@
       </c>
       <c r="J91" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>994jp!@</v>
+        <v>156jp!@</v>
       </c>
       <c r="K91" t="str">
         <f t="shared" si="4"/>
@@ -36250,7 +35862,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
         <v>203</v>
       </c>
@@ -36278,7 +35890,7 @@
       </c>
       <c r="J92" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>046jp!@</v>
+        <v>724jp!@</v>
       </c>
       <c r="K92" t="str">
         <f t="shared" si="4"/>
@@ -36292,7 +35904,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
         <v>78</v>
       </c>
@@ -36320,7 +35932,7 @@
       </c>
       <c r="J93" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>407jm!@</v>
+        <v>335jm!@</v>
       </c>
       <c r="K93" t="str">
         <f t="shared" si="4"/>
@@ -36334,7 +35946,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
         <v>82</v>
       </c>
@@ -36362,7 +35974,7 @@
       </c>
       <c r="J94" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>470jm!@</v>
+        <v>177jm!@</v>
       </c>
       <c r="K94" t="str">
         <f t="shared" si="4"/>
@@ -36376,7 +35988,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
         <v>181</v>
       </c>
@@ -36404,7 +36016,7 @@
       </c>
       <c r="J95" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>661js!@</v>
+        <v>266js!@</v>
       </c>
       <c r="K95" t="str">
         <f t="shared" si="4"/>
@@ -36418,7 +36030,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
         <v>86</v>
       </c>
@@ -36446,7 +36058,7 @@
       </c>
       <c r="J96" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>722js!@</v>
+        <v>560js!@</v>
       </c>
       <c r="K96" t="str">
         <f t="shared" si="4"/>
@@ -36460,7 +36072,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
         <v>85</v>
       </c>
@@ -36488,7 +36100,7 @@
       </c>
       <c r="J97" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>157ls!@</v>
+        <v>269ls!@</v>
       </c>
       <c r="K97" t="str">
         <f t="shared" si="4"/>
@@ -36502,7 +36114,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
         <v>129</v>
       </c>
@@ -36530,7 +36142,7 @@
       </c>
       <c r="J98" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>225ms!@</v>
+        <v>785ms!@</v>
       </c>
       <c r="K98" t="str">
         <f t="shared" si="4"/>
@@ -36544,7 +36156,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
         <v>225</v>
       </c>
@@ -36570,7 +36182,7 @@
       </c>
       <c r="J99" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>228mn!@</v>
+        <v>528mn!@</v>
       </c>
       <c r="K99" t="str">
         <f t="shared" si="4"/>
@@ -36584,7 +36196,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
         <v>237</v>
       </c>
@@ -36610,7 +36222,7 @@
       </c>
       <c r="J100" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>300ms!@</v>
+        <v>497ms!@</v>
       </c>
       <c r="K100" t="str">
         <f t="shared" si="4"/>
@@ -36624,7 +36236,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
         <v>191</v>
       </c>
@@ -36652,7 +36264,7 @@
       </c>
       <c r="J101" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>265mc!@</v>
+        <v>891mc!@</v>
       </c>
       <c r="K101" t="str">
         <f t="shared" si="4"/>
@@ -36666,7 +36278,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
         <v>57</v>
       </c>
@@ -36694,7 +36306,7 @@
       </c>
       <c r="J102" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>477nn!@</v>
+        <v>761nn!@</v>
       </c>
       <c r="K102" t="str">
         <f t="shared" si="4"/>
@@ -36708,7 +36320,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
         <v>102</v>
       </c>
@@ -36736,7 +36348,7 @@
       </c>
       <c r="J103" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>058pc!@</v>
+        <v>747pc!@</v>
       </c>
       <c r="K103" t="str">
         <f t="shared" si="4"/>
@@ -36750,7 +36362,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
         <v>104</v>
       </c>
@@ -36778,7 +36390,7 @@
       </c>
       <c r="J104" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>983rs!@</v>
+        <v>488rs!@</v>
       </c>
       <c r="K104" t="str">
         <f t="shared" si="4"/>
@@ -36792,7 +36404,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
         <v>251</v>
       </c>
@@ -36818,7 +36430,7 @@
       </c>
       <c r="J105" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>156rc!@</v>
+        <v>672rc!@</v>
       </c>
       <c r="K105" t="str">
         <f t="shared" si="4"/>
@@ -36832,7 +36444,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
         <v>58</v>
       </c>
@@ -36860,7 +36472,7 @@
       </c>
       <c r="J106" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>098rs!@</v>
+        <v>645rs!@</v>
       </c>
       <c r="K106" t="str">
         <f t="shared" si="4"/>
@@ -36874,7 +36486,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
         <v>62</v>
       </c>
@@ -36902,7 +36514,7 @@
       </c>
       <c r="J107" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>551ss!@</v>
+        <v>146ss!@</v>
       </c>
       <c r="K107" t="str">
         <f t="shared" si="4"/>
@@ -36916,7 +36528,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
         <v>11</v>
       </c>
@@ -36944,7 +36556,7 @@
       </c>
       <c r="J108" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>179sa!@</v>
+        <v>421sa!@</v>
       </c>
       <c r="K108" t="str">
         <f t="shared" si="4"/>
@@ -36958,7 +36570,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
         <v>274</v>
       </c>
@@ -36984,7 +36596,7 @@
       </c>
       <c r="J109" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>747tr!@</v>
+        <v>514tr!@</v>
       </c>
       <c r="K109" t="str">
         <f t="shared" si="4"/>
@@ -36998,7 +36610,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
         <v>281</v>
       </c>
@@ -37024,7 +36636,7 @@
       </c>
       <c r="J110" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>725vs!@</v>
+        <v>871vs!@</v>
       </c>
       <c r="K110" t="str">
         <f t="shared" si="4"/>
@@ -37038,7 +36650,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
         <v>206</v>
       </c>
@@ -37066,7 +36678,7 @@
       </c>
       <c r="J111" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>536wc!@</v>
+        <v>942wc!@</v>
       </c>
       <c r="K111" t="str">
         <f t="shared" si="4"/>
@@ -37080,7 +36692,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
         <v>175</v>
       </c>
@@ -37108,7 +36720,7 @@
       </c>
       <c r="J112" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>780ac!@</v>
+        <v>392ac!@</v>
       </c>
       <c r="K112" t="str">
         <f t="shared" si="4"/>
@@ -37122,7 +36734,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
         <v>51</v>
       </c>
@@ -37150,7 +36762,7 @@
       </c>
       <c r="J113" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>032ms!@</v>
+        <v>252ms!@</v>
       </c>
       <c r="K113" t="str">
         <f t="shared" si="4"/>
@@ -37164,7 +36776,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
         <v>530</v>
       </c>
@@ -37186,7 +36798,7 @@
       </c>
       <c r="J114" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>372tt!@</v>
+        <v>585tt!@</v>
       </c>
       <c r="K114" t="str">
         <f t="shared" si="4"/>
@@ -37200,7 +36812,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
         <v>532</v>
       </c>
@@ -37226,7 +36838,7 @@
       </c>
       <c r="J115" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>635ls!@</v>
+        <v>288ls!@</v>
       </c>
       <c r="K115" t="str">
         <f t="shared" si="4"/>
@@ -37240,7 +36852,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
         <v>536</v>
       </c>
@@ -37274,7 +36886,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
         <v>316</v>
       </c>
@@ -37302,7 +36914,7 @@
       </c>
       <c r="J117" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>626aa!@</v>
+        <v>637aa!@</v>
       </c>
       <c r="K117" t="str">
         <f t="shared" si="4"/>
@@ -37316,7 +36928,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
         <v>317</v>
       </c>
@@ -37344,7 +36956,7 @@
       </c>
       <c r="J118" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>264ap!@</v>
+        <v>649ap!@</v>
       </c>
       <c r="K118" t="str">
         <f t="shared" si="4"/>
@@ -37358,7 +36970,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
         <v>318</v>
       </c>
@@ -37386,7 +36998,7 @@
       </c>
       <c r="J119" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>007ao!@</v>
+        <v>389ao!@</v>
       </c>
       <c r="K119" t="str">
         <f t="shared" si="4"/>
@@ -37404,7 +37016,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
         <v>319</v>
       </c>
@@ -37432,7 +37044,7 @@
       </c>
       <c r="J120" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>606ae!@</v>
+        <v>568ae!@</v>
       </c>
       <c r="K120" t="str">
         <f t="shared" si="4"/>
@@ -37446,7 +37058,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
         <v>320</v>
       </c>
@@ -37474,7 +37086,7 @@
       </c>
       <c r="J121" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>171an!@</v>
+        <v>843an!@</v>
       </c>
       <c r="K121" t="str">
         <f t="shared" si="4"/>
@@ -37492,7 +37104,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
         <v>321</v>
       </c>
@@ -37520,7 +37132,7 @@
       </c>
       <c r="J122" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>413as!@</v>
+        <v>071as!@</v>
       </c>
       <c r="K122" t="str">
         <f t="shared" si="4"/>
@@ -37534,7 +37146,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
         <v>322</v>
       </c>
@@ -37562,7 +37174,7 @@
       </c>
       <c r="J123" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>101aa!@</v>
+        <v>869aa!@</v>
       </c>
       <c r="K123" t="str">
         <f t="shared" si="4"/>
@@ -37576,7 +37188,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
         <v>323</v>
       </c>
@@ -37604,7 +37216,7 @@
       </c>
       <c r="J124" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>138aj!@</v>
+        <v>318aj!@</v>
       </c>
       <c r="K124" t="str">
         <f t="shared" si="4"/>
@@ -37618,7 +37230,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
         <v>324</v>
       </c>
@@ -37646,7 +37258,7 @@
       </c>
       <c r="J125" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>798bs!@</v>
+        <v>338bs!@</v>
       </c>
       <c r="K125" t="str">
         <f t="shared" si="4"/>
@@ -37660,7 +37272,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
         <v>325</v>
       </c>
@@ -37688,7 +37300,7 @@
       </c>
       <c r="J126" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>309bl!@</v>
+        <v>385bl!@</v>
       </c>
       <c r="K126" t="str">
         <f t="shared" si="4"/>
@@ -37702,7 +37314,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
         <v>326</v>
       </c>
@@ -37730,7 +37342,7 @@
       </c>
       <c r="J127" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>588cm!@</v>
+        <v>059cm!@</v>
       </c>
       <c r="K127" t="str">
         <f t="shared" si="4"/>
@@ -37744,7 +37356,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
         <v>327</v>
       </c>
@@ -37772,7 +37384,7 @@
       </c>
       <c r="J128" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>195dc!@</v>
+        <v>862dc!@</v>
       </c>
       <c r="K128" t="str">
         <f t="shared" si="4"/>
@@ -37786,7 +37398,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
         <v>328</v>
       </c>
@@ -37814,7 +37426,7 @@
       </c>
       <c r="J129" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>006jm!@</v>
+        <v>126jm!@</v>
       </c>
       <c r="K129" t="str">
         <f t="shared" si="4"/>
@@ -37828,7 +37440,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
         <v>329</v>
       </c>
@@ -37856,7 +37468,7 @@
       </c>
       <c r="J130" t="str">
         <f t="shared" ref="J130:J154" ca="1" si="6">TEXT(RANDBETWEEN(1,999),"000") &amp; LEFT(H130,1) &amp; MID(H130,FIND(".",H130,1)+1,1) &amp; "!@"</f>
-        <v>089ef!@</v>
+        <v>587ef!@</v>
       </c>
       <c r="K130" t="str">
         <f t="shared" ref="K130:K154" si="7">"Update QuestRH_Pessoas set Senha = '" &amp; I130 &amp; "' Where Nome = '" &amp; A130 &amp; "';"</f>
@@ -37874,7 +37486,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
         <v>330</v>
       </c>
@@ -37902,7 +37514,7 @@
       </c>
       <c r="J131" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>036el!@</v>
+        <v>712el!@</v>
       </c>
       <c r="K131" t="str">
         <f t="shared" si="7"/>
@@ -37920,7 +37532,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
         <v>331</v>
       </c>
@@ -37948,7 +37560,7 @@
       </c>
       <c r="J132" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>311ia!@</v>
+        <v>157ia!@</v>
       </c>
       <c r="K132" t="str">
         <f t="shared" si="7"/>
@@ -37962,7 +37574,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
         <v>332</v>
       </c>
@@ -37990,7 +37602,7 @@
       </c>
       <c r="J133" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>545ia!@</v>
+        <v>108ia!@</v>
       </c>
       <c r="K133" t="str">
         <f t="shared" si="7"/>
@@ -38004,7 +37616,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
         <v>333</v>
       </c>
@@ -38032,7 +37644,7 @@
       </c>
       <c r="J134" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>817jr!@</v>
+        <v>496jr!@</v>
       </c>
       <c r="K134" t="str">
         <f t="shared" si="7"/>
@@ -38046,7 +37658,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
         <v>334</v>
       </c>
@@ -38074,7 +37686,7 @@
       </c>
       <c r="J135" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>474lr!@</v>
+        <v>902lr!@</v>
       </c>
       <c r="K135" t="str">
         <f t="shared" si="7"/>
@@ -38088,7 +37700,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
         <v>335</v>
       </c>
@@ -38116,7 +37728,7 @@
       </c>
       <c r="J136" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>760jf!@</v>
+        <v>251jf!@</v>
       </c>
       <c r="K136" t="str">
         <f t="shared" si="7"/>
@@ -38130,7 +37742,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
         <v>336</v>
       </c>
@@ -38158,7 +37770,7 @@
       </c>
       <c r="J137" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>628lc!@</v>
+        <v>667lc!@</v>
       </c>
       <c r="K137" t="str">
         <f t="shared" si="7"/>
@@ -38172,7 +37784,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
         <v>337</v>
       </c>
@@ -38200,7 +37812,7 @@
       </c>
       <c r="J138" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>872lc!@</v>
+        <v>298lc!@</v>
       </c>
       <c r="K138" t="str">
         <f t="shared" si="7"/>
@@ -38214,7 +37826,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
         <v>338</v>
       </c>
@@ -38242,7 +37854,7 @@
       </c>
       <c r="J139" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>684ms!@</v>
+        <v>183ms!@</v>
       </c>
       <c r="K139" t="str">
         <f t="shared" si="7"/>
@@ -38256,7 +37868,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
         <v>339</v>
       </c>
@@ -38284,7 +37896,7 @@
       </c>
       <c r="J140" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>309ip!@</v>
+        <v>149ip!@</v>
       </c>
       <c r="K140" t="str">
         <f t="shared" si="7"/>
@@ -38298,7 +37910,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
         <v>340</v>
       </c>
@@ -38326,7 +37938,7 @@
       </c>
       <c r="J141" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>708mj!@</v>
+        <v>773mj!@</v>
       </c>
       <c r="K141" t="str">
         <f t="shared" si="7"/>
@@ -38340,7 +37952,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="142" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
         <v>341</v>
       </c>
@@ -38368,7 +37980,7 @@
       </c>
       <c r="J142" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>744mq!@</v>
+        <v>230mq!@</v>
       </c>
       <c r="K142" t="str">
         <f t="shared" si="7"/>
@@ -38386,7 +37998,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
         <v>342</v>
       </c>
@@ -38414,7 +38026,7 @@
       </c>
       <c r="J143" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>284mm!@</v>
+        <v>231mm!@</v>
       </c>
       <c r="K143" t="str">
         <f t="shared" si="7"/>
@@ -38428,7 +38040,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
         <v>343</v>
       </c>
@@ -38456,7 +38068,7 @@
       </c>
       <c r="J144" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>652ms!@</v>
+        <v>698ms!@</v>
       </c>
       <c r="K144" t="str">
         <f t="shared" si="7"/>
@@ -38470,7 +38082,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="145" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
         <v>344</v>
       </c>
@@ -38498,7 +38110,7 @@
       </c>
       <c r="J145" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>505ma!@</v>
+        <v>509ma!@</v>
       </c>
       <c r="K145" t="str">
         <f t="shared" si="7"/>
@@ -38516,7 +38128,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="146" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
         <v>345</v>
       </c>
@@ -38544,7 +38156,7 @@
       </c>
       <c r="J146" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>484ns!@</v>
+        <v>238ns!@</v>
       </c>
       <c r="K146" t="str">
         <f t="shared" si="7"/>
@@ -38558,7 +38170,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="147" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
         <v>346</v>
       </c>
@@ -38586,7 +38198,7 @@
       </c>
       <c r="J147" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>980nr!@</v>
+        <v>452nr!@</v>
       </c>
       <c r="K147" t="str">
         <f t="shared" si="7"/>
@@ -38600,7 +38212,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="148" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
         <v>347</v>
       </c>
@@ -38628,7 +38240,7 @@
       </c>
       <c r="J148" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>338rp!@</v>
+        <v>536rp!@</v>
       </c>
       <c r="K148" t="str">
         <f t="shared" si="7"/>
@@ -38642,7 +38254,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="149" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
         <v>348</v>
       </c>
@@ -38670,7 +38282,7 @@
       </c>
       <c r="J149" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>556ms!@</v>
+        <v>721ms!@</v>
       </c>
       <c r="K149" t="str">
         <f t="shared" si="7"/>
@@ -38684,7 +38296,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
         <v>349</v>
       </c>
@@ -38712,7 +38324,7 @@
       </c>
       <c r="J150" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>832rr!@</v>
+        <v>233rr!@</v>
       </c>
       <c r="K150" t="str">
         <f t="shared" si="7"/>
@@ -38726,7 +38338,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
         <v>350</v>
       </c>
@@ -38754,7 +38366,7 @@
       </c>
       <c r="J151" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>669sp!@</v>
+        <v>772sp!@</v>
       </c>
       <c r="K151" t="str">
         <f t="shared" si="7"/>
@@ -38768,7 +38380,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="s">
         <v>351</v>
       </c>
@@ -38796,7 +38408,7 @@
       </c>
       <c r="J152" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>785to!@</v>
+        <v>050to!@</v>
       </c>
       <c r="K152" t="str">
         <f t="shared" si="7"/>
@@ -38810,7 +38422,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
         <v>352</v>
       </c>
@@ -38838,7 +38450,7 @@
       </c>
       <c r="J153" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>075va!@</v>
+        <v>645va!@</v>
       </c>
       <c r="K153" t="str">
         <f t="shared" si="7"/>
@@ -38852,7 +38464,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
         <v>353</v>
       </c>
@@ -38880,7 +38492,7 @@
       </c>
       <c r="J154" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>611wb!@</v>
+        <v>653wb!@</v>
       </c>
       <c r="K154" t="str">
         <f t="shared" si="7"/>
@@ -38895,7 +38507,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N154" xr:uid="{C8A1FF41-FE38-442B-8F1A-E5C01AF500AB}"/>
+  <autoFilter ref="A1:N154" xr:uid="{C8A1FF41-FE38-442B-8F1A-E5C01AF500AB}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="Fabricio Romanini Bruschi"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <hyperlinks>
     <hyperlink ref="B145" r:id="rId1" xr:uid="{CB604002-A099-420F-95F9-C5B760AE6CCF}"/>
     <hyperlink ref="B142" r:id="rId2" xr:uid="{57E8AD4A-C13E-4193-A104-E595FABE7BAB}"/>
@@ -38906,6 +38524,7 @@
     <hyperlink ref="B136" r:id="rId7" xr:uid="{DCCAE8D7-760C-40C9-AF58-2244010CCA4E}"/>
     <hyperlink ref="B153" r:id="rId8" xr:uid="{7B7C6DAD-A14E-43EA-B613-E81398220C57}"/>
     <hyperlink ref="I153" r:id="rId9" xr:uid="{AF656605-F287-44F2-85D8-195616C66EBC}"/>
+    <hyperlink ref="B35" r:id="rId10" xr:uid="{F1C77723-013E-4D5F-B4EF-87358493038F}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -43596,10 +43215,10 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="I1:J39">
-    <cfRule type="cellIs" dxfId="41" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
       <formula>"Não"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="40" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
       <formula>"Sim"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/lista_emails.xlsx
+++ b/lista_emails.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://enindengenharia-my.sharepoint.com/personal/wagner_barreiro_enind_com_br/Documents/Área de Trabalho/Aplicativos/RH/App/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="38" documentId="13_ncr:1_{22BF655E-FB6C-4CA2-A20B-1C925A91A378}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B7DFA2D4-2E65-4F48-9674-9A2BF43AC274}"/>
+  <xr:revisionPtr revIDLastSave="41" documentId="13_ncr:1_{22BF655E-FB6C-4CA2-A20B-1C925A91A378}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BDE7D7FE-159F-462A-9B9A-3CDFA1C8223E}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{4ABFC600-D865-440E-A0ED-FE29CA4E2163}"/>
   </bookViews>
@@ -2566,6 +2566,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -32246,7 +32250,7 @@
       </c>
       <c r="J2" t="str">
         <f ca="1">TEXT(RANDBETWEEN(1,999),"000") &amp; LEFT(H2,1) &amp; MID(H2,FIND(".",H2,1)+1,1) &amp; "!@"</f>
-        <v>716wf!@</v>
+        <v>565wf!@</v>
       </c>
       <c r="K2" t="str">
         <f>"Update QuestRH_Pessoas set Senha = '" &amp; I2 &amp; "' Where Nome = '" &amp; A2 &amp; "';"</f>
@@ -32286,7 +32290,7 @@
       </c>
       <c r="J3" t="str">
         <f t="shared" ref="J3:J65" ca="1" si="0">TEXT(RANDBETWEEN(1,999),"000") &amp; LEFT(H3,1) &amp; MID(H3,FIND(".",H3,1)+1,1) &amp; "!@"</f>
-        <v>419wc!@</v>
+        <v>914wc!@</v>
       </c>
       <c r="K3" t="str">
         <f t="shared" ref="K3:K65" si="1">"Update QuestRH_Pessoas set Senha = '" &amp; I3 &amp; "' Where Nome = '" &amp; A3 &amp; "';"</f>
@@ -32326,7 +32330,7 @@
       </c>
       <c r="J4" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>950ws!@</v>
+        <v>865ws!@</v>
       </c>
       <c r="K4" t="str">
         <f t="shared" si="1"/>
@@ -32366,7 +32370,7 @@
       </c>
       <c r="J5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>767wm!@</v>
+        <v>377wm!@</v>
       </c>
       <c r="K5" t="str">
         <f t="shared" si="1"/>
@@ -32380,7 +32384,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>272</v>
       </c>
@@ -32406,7 +32410,7 @@
       </c>
       <c r="J6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>438wf!@</v>
+        <v>629wf!@</v>
       </c>
       <c r="K6" t="str">
         <f t="shared" si="1"/>
@@ -32446,7 +32450,7 @@
       </c>
       <c r="J7" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>382wc!@</v>
+        <v>469wc!@</v>
       </c>
       <c r="K7" t="str">
         <f t="shared" si="1"/>
@@ -32486,7 +32490,7 @@
       </c>
       <c r="J8" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>389vx!@</v>
+        <v>806vx!@</v>
       </c>
       <c r="K8" t="str">
         <f t="shared" si="1"/>
@@ -32526,7 +32530,7 @@
       </c>
       <c r="J9" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>138vs!@</v>
+        <v>954vs!@</v>
       </c>
       <c r="K9" t="str">
         <f t="shared" si="1"/>
@@ -32566,7 +32570,7 @@
       </c>
       <c r="J10" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>204ub!@</v>
+        <v>589ub!@</v>
       </c>
       <c r="K10" t="str">
         <f t="shared" si="1"/>
@@ -32606,7 +32610,7 @@
       </c>
       <c r="J11" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>236to!@</v>
+        <v>746to!@</v>
       </c>
       <c r="K11" t="str">
         <f t="shared" si="1"/>
@@ -32646,7 +32650,7 @@
       </c>
       <c r="J12" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>670ta!@</v>
+        <v>271ta!@</v>
       </c>
       <c r="K12" t="str">
         <f t="shared" si="1"/>
@@ -32686,7 +32690,7 @@
       </c>
       <c r="J13" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>383ta!@</v>
+        <v>141ta!@</v>
       </c>
       <c r="K13" t="str">
         <f t="shared" si="1"/>
@@ -32726,7 +32730,7 @@
       </c>
       <c r="J14" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>618tp!@</v>
+        <v>175tp!@</v>
       </c>
       <c r="K14" t="str">
         <f t="shared" si="1"/>
@@ -32766,7 +32770,7 @@
       </c>
       <c r="J15" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>224rs!@</v>
+        <v>320rs!@</v>
       </c>
       <c r="K15" t="str">
         <f t="shared" si="1"/>
@@ -32806,7 +32810,7 @@
       </c>
       <c r="J16" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>421rm!@</v>
+        <v>220rm!@</v>
       </c>
       <c r="K16" t="str">
         <f t="shared" si="1"/>
@@ -32846,7 +32850,7 @@
       </c>
       <c r="J17" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>237rm!@</v>
+        <v>898rm!@</v>
       </c>
       <c r="K17" t="str">
         <f t="shared" si="1"/>
@@ -32886,7 +32890,7 @@
       </c>
       <c r="J18" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>433ra!@</v>
+        <v>369ra!@</v>
       </c>
       <c r="K18" t="str">
         <f t="shared" si="1"/>
@@ -32926,7 +32930,7 @@
       </c>
       <c r="J19" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>375pm!@</v>
+        <v>405pm!@</v>
       </c>
       <c r="K19" t="str">
         <f t="shared" si="1"/>
@@ -32966,7 +32970,7 @@
       </c>
       <c r="J20" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>089pa!@</v>
+        <v>348pa!@</v>
       </c>
       <c r="K20" t="str">
         <f t="shared" si="1"/>
@@ -33006,7 +33010,7 @@
       </c>
       <c r="J21" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>771mg!@</v>
+        <v>069mg!@</v>
       </c>
       <c r="K21" t="str">
         <f t="shared" si="1"/>
@@ -33046,7 +33050,7 @@
       </c>
       <c r="J22" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>894mc!@</v>
+        <v>903mc!@</v>
       </c>
       <c r="K22" t="str">
         <f t="shared" si="1"/>
@@ -33086,7 +33090,7 @@
       </c>
       <c r="J23" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>658ms!@</v>
+        <v>443ms!@</v>
       </c>
       <c r="K23" t="str">
         <f t="shared" si="1"/>
@@ -33126,7 +33130,7 @@
       </c>
       <c r="J24" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>740ms!@</v>
+        <v>481ms!@</v>
       </c>
       <c r="K24" t="str">
         <f t="shared" si="1"/>
@@ -33164,7 +33168,7 @@
       </c>
       <c r="J25" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>565mb!@</v>
+        <v>501mb!@</v>
       </c>
       <c r="K25" t="str">
         <f t="shared" si="1"/>
@@ -33204,7 +33208,7 @@
       </c>
       <c r="J26" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>311ms!@</v>
+        <v>570ms!@</v>
       </c>
       <c r="K26" t="str">
         <f t="shared" si="1"/>
@@ -33244,7 +33248,7 @@
       </c>
       <c r="J27" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>342lf!@</v>
+        <v>474lf!@</v>
       </c>
       <c r="K27" t="str">
         <f t="shared" si="1"/>
@@ -33284,7 +33288,7 @@
       </c>
       <c r="J28" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>665lb!@</v>
+        <v>077lb!@</v>
       </c>
       <c r="K28" t="str">
         <f t="shared" si="1"/>
@@ -33324,7 +33328,7 @@
       </c>
       <c r="J29" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>031la!@</v>
+        <v>950la!@</v>
       </c>
       <c r="K29" t="str">
         <f t="shared" si="1"/>
@@ -33364,7 +33368,7 @@
       </c>
       <c r="J30" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>448ls!@</v>
+        <v>875ls!@</v>
       </c>
       <c r="K30" t="str">
         <f t="shared" si="1"/>
@@ -33404,7 +33408,7 @@
       </c>
       <c r="J31" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>882js!@</v>
+        <v>375js!@</v>
       </c>
       <c r="K31" t="str">
         <f t="shared" si="1"/>
@@ -33444,7 +33448,7 @@
       </c>
       <c r="J32" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>632jm!@</v>
+        <v>132jm!@</v>
       </c>
       <c r="K32" t="str">
         <f t="shared" si="1"/>
@@ -33484,7 +33488,7 @@
       </c>
       <c r="J33" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>993ja!@</v>
+        <v>036ja!@</v>
       </c>
       <c r="K33" t="str">
         <f t="shared" si="1"/>
@@ -33524,7 +33528,7 @@
       </c>
       <c r="J34" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>623js!@</v>
+        <v>879js!@</v>
       </c>
       <c r="K34" t="str">
         <f t="shared" si="1"/>
@@ -33564,7 +33568,7 @@
       </c>
       <c r="J35" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>036jf!@</v>
+        <v>273jf!@</v>
       </c>
       <c r="K35" t="str">
         <f t="shared" si="1"/>
@@ -33604,7 +33608,7 @@
       </c>
       <c r="J36" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>920jr!@</v>
+        <v>540jr!@</v>
       </c>
       <c r="K36" t="str">
         <f t="shared" si="1"/>
@@ -33644,7 +33648,7 @@
       </c>
       <c r="J37" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>965ja!@</v>
+        <v>973ja!@</v>
       </c>
       <c r="K37" t="str">
         <f t="shared" si="1"/>
@@ -33684,7 +33688,7 @@
       </c>
       <c r="J38" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>569ht!@</v>
+        <v>133ht!@</v>
       </c>
       <c r="K38" t="str">
         <f t="shared" si="1"/>
@@ -33724,7 +33728,7 @@
       </c>
       <c r="J39" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>080hk!@</v>
+        <v>492hk!@</v>
       </c>
       <c r="K39" t="str">
         <f t="shared" si="1"/>
@@ -33764,7 +33768,7 @@
       </c>
       <c r="J40" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>780gl!@</v>
+        <v>868gl!@</v>
       </c>
       <c r="K40" t="str">
         <f t="shared" si="1"/>
@@ -33804,7 +33808,7 @@
       </c>
       <c r="J41" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>155gp!@</v>
+        <v>677gp!@</v>
       </c>
       <c r="K41" t="str">
         <f t="shared" si="1"/>
@@ -33844,7 +33848,7 @@
       </c>
       <c r="J42" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>375gl!@</v>
+        <v>374gl!@</v>
       </c>
       <c r="K42" t="str">
         <f t="shared" si="1"/>
@@ -33884,7 +33888,7 @@
       </c>
       <c r="J43" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>090fc!@</v>
+        <v>990fc!@</v>
       </c>
       <c r="K43" t="str">
         <f t="shared" si="1"/>
@@ -33898,7 +33902,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>36</v>
       </c>
@@ -33924,7 +33928,7 @@
       </c>
       <c r="J44" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>361fb!@</v>
+        <v>746fb!@</v>
       </c>
       <c r="K44" t="str">
         <f t="shared" si="1"/>
@@ -33964,7 +33968,7 @@
       </c>
       <c r="J45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>345fc!@</v>
+        <v>786fc!@</v>
       </c>
       <c r="K45" t="str">
         <f t="shared" si="1"/>
@@ -34004,7 +34008,7 @@
       </c>
       <c r="J46" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>534es!@</v>
+        <v>302es!@</v>
       </c>
       <c r="K46" t="str">
         <f t="shared" si="1"/>
@@ -34044,7 +34048,7 @@
       </c>
       <c r="J47" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>598eb!@</v>
+        <v>873eb!@</v>
       </c>
       <c r="K47" t="str">
         <f t="shared" si="1"/>
@@ -34084,7 +34088,7 @@
       </c>
       <c r="J48" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>163es!@</v>
+        <v>736es!@</v>
       </c>
       <c r="K48" t="str">
         <f t="shared" si="1"/>
@@ -34124,7 +34128,7 @@
       </c>
       <c r="J49" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>359ei!@</v>
+        <v>045ei!@</v>
       </c>
       <c r="K49" t="str">
         <f t="shared" si="1"/>
@@ -34164,7 +34168,7 @@
       </c>
       <c r="J50" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>900eb!@</v>
+        <v>319eb!@</v>
       </c>
       <c r="K50" t="str">
         <f t="shared" si="1"/>
@@ -34204,7 +34208,7 @@
       </c>
       <c r="J51" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>388en!@</v>
+        <v>300en!@</v>
       </c>
       <c r="K51" t="str">
         <f t="shared" si="1"/>
@@ -34244,7 +34248,7 @@
       </c>
       <c r="J52" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>583em!@</v>
+        <v>285em!@</v>
       </c>
       <c r="K52" t="str">
         <f t="shared" si="1"/>
@@ -34284,7 +34288,7 @@
       </c>
       <c r="J53" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>974ep!@</v>
+        <v>241ep!@</v>
       </c>
       <c r="K53" t="str">
         <f t="shared" si="1"/>
@@ -34324,7 +34328,7 @@
       </c>
       <c r="J54" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>465ds!@</v>
+        <v>224ds!@</v>
       </c>
       <c r="K54" t="str">
         <f t="shared" si="1"/>
@@ -34364,7 +34368,7 @@
       </c>
       <c r="J55" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>811da!@</v>
+        <v>772da!@</v>
       </c>
       <c r="K55" t="str">
         <f t="shared" si="1"/>
@@ -34404,7 +34408,7 @@
       </c>
       <c r="J56" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>723ds!@</v>
+        <v>552ds!@</v>
       </c>
       <c r="K56" t="str">
         <f t="shared" si="1"/>
@@ -34444,7 +34448,7 @@
       </c>
       <c r="J57" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>486dc!@</v>
+        <v>283dc!@</v>
       </c>
       <c r="K57" t="str">
         <f t="shared" si="1"/>
@@ -34484,7 +34488,7 @@
       </c>
       <c r="J58" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>918cg!@</v>
+        <v>459cg!@</v>
       </c>
       <c r="K58" t="str">
         <f t="shared" si="1"/>
@@ -34524,7 +34528,7 @@
       </c>
       <c r="J59" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>011bc!@</v>
+        <v>539bc!@</v>
       </c>
       <c r="K59" t="str">
         <f t="shared" si="1"/>
@@ -34564,7 +34568,7 @@
       </c>
       <c r="J60" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>103af!@</v>
+        <v>160af!@</v>
       </c>
       <c r="K60" t="str">
         <f t="shared" si="1"/>
@@ -34604,7 +34608,7 @@
       </c>
       <c r="J61" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>415aa!@</v>
+        <v>296aa!@</v>
       </c>
       <c r="K61" t="str">
         <f t="shared" si="1"/>
@@ -34644,7 +34648,7 @@
       </c>
       <c r="J62" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>194at!@</v>
+        <v>759at!@</v>
       </c>
       <c r="K62" t="str">
         <f t="shared" si="1"/>
@@ -34684,7 +34688,7 @@
       </c>
       <c r="J63" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>931ac!@</v>
+        <v>723ac!@</v>
       </c>
       <c r="K63" t="str">
         <f t="shared" si="1"/>
@@ -34726,7 +34730,7 @@
       </c>
       <c r="J64" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>857as!@</v>
+        <v>916as!@</v>
       </c>
       <c r="K64" t="str">
         <f t="shared" si="1"/>
@@ -34766,7 +34770,7 @@
       </c>
       <c r="J65" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>074ad!@</v>
+        <v>472ad!@</v>
       </c>
       <c r="K65" t="str">
         <f t="shared" si="1"/>
@@ -34808,7 +34812,7 @@
       </c>
       <c r="J66" t="str">
         <f t="shared" ref="J66:J129" ca="1" si="3">TEXT(RANDBETWEEN(1,999),"000") &amp; LEFT(H66,1) &amp; MID(H66,FIND(".",H66,1)+1,1) &amp; "!@"</f>
-        <v>397af!@</v>
+        <v>039af!@</v>
       </c>
       <c r="K66" t="str">
         <f t="shared" ref="K66:K129" si="4">"Update QuestRH_Pessoas set Senha = '" &amp; I66 &amp; "' Where Nome = '" &amp; A66 &amp; "';"</f>
@@ -34850,7 +34854,7 @@
       </c>
       <c r="J67" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>297ap!@</v>
+        <v>423ap!@</v>
       </c>
       <c r="K67" t="str">
         <f t="shared" si="4"/>
@@ -34892,7 +34896,7 @@
       </c>
       <c r="J68" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>371al!@</v>
+        <v>513al!@</v>
       </c>
       <c r="K68" t="str">
         <f t="shared" si="4"/>
@@ -34934,7 +34938,7 @@
       </c>
       <c r="J69" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>358as!@</v>
+        <v>111as!@</v>
       </c>
       <c r="K69" t="str">
         <f t="shared" si="4"/>
@@ -34976,7 +34980,7 @@
       </c>
       <c r="J70" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>250at!@</v>
+        <v>274at!@</v>
       </c>
       <c r="K70" t="str">
         <f t="shared" si="4"/>
@@ -35018,7 +35022,7 @@
       </c>
       <c r="J71" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>326cm!@</v>
+        <v>953cm!@</v>
       </c>
       <c r="K71" t="str">
         <f t="shared" si="4"/>
@@ -35060,7 +35064,7 @@
       </c>
       <c r="J72" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>258ds!@</v>
+        <v>145ds!@</v>
       </c>
       <c r="K72" t="str">
         <f t="shared" si="4"/>
@@ -35102,7 +35106,7 @@
       </c>
       <c r="J73" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>961ds!@</v>
+        <v>139ds!@</v>
       </c>
       <c r="K73" t="str">
         <f t="shared" si="4"/>
@@ -35144,7 +35148,7 @@
       </c>
       <c r="J74" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>672dc!@</v>
+        <v>441dc!@</v>
       </c>
       <c r="K74" t="str">
         <f t="shared" si="4"/>
@@ -35186,7 +35190,7 @@
       </c>
       <c r="J75" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>682dd!@</v>
+        <v>006dd!@</v>
       </c>
       <c r="K75" t="str">
         <f t="shared" si="4"/>
@@ -35228,7 +35232,7 @@
       </c>
       <c r="J76" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>647dm!@</v>
+        <v>816dm!@</v>
       </c>
       <c r="K76" t="str">
         <f t="shared" si="4"/>
@@ -35270,7 +35274,7 @@
       </c>
       <c r="J77" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>197eg!@</v>
+        <v>574eg!@</v>
       </c>
       <c r="K77" t="str">
         <f t="shared" si="4"/>
@@ -35312,7 +35316,7 @@
       </c>
       <c r="J78" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>225er!@</v>
+        <v>057er!@</v>
       </c>
       <c r="K78" t="str">
         <f t="shared" si="4"/>
@@ -35352,7 +35356,7 @@
       </c>
       <c r="J79" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>436ep!@</v>
+        <v>708ep!@</v>
       </c>
       <c r="K79" t="str">
         <f t="shared" si="4"/>
@@ -35392,7 +35396,7 @@
       </c>
       <c r="J80" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>457fs!@</v>
+        <v>391fs!@</v>
       </c>
       <c r="K80" t="str">
         <f t="shared" si="4"/>
@@ -35434,7 +35438,7 @@
       </c>
       <c r="J81" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>645fs!@</v>
+        <v>529fs!@</v>
       </c>
       <c r="K81" t="str">
         <f t="shared" si="4"/>
@@ -35476,7 +35480,7 @@
       </c>
       <c r="J82" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>190fo!@</v>
+        <v>176fo!@</v>
       </c>
       <c r="K82" t="str">
         <f t="shared" si="4"/>
@@ -35518,7 +35522,7 @@
       </c>
       <c r="J83" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>286gs!@</v>
+        <v>068gs!@</v>
       </c>
       <c r="K83" t="str">
         <f t="shared" si="4"/>
@@ -35558,7 +35562,7 @@
       </c>
       <c r="J84" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>288gs!@</v>
+        <v>103gs!@</v>
       </c>
       <c r="K84" t="str">
         <f t="shared" si="4"/>
@@ -35598,7 +35602,7 @@
       </c>
       <c r="J85" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>470ia!@</v>
+        <v>406ia!@</v>
       </c>
       <c r="K85" t="str">
         <f t="shared" si="4"/>
@@ -35640,7 +35644,7 @@
       </c>
       <c r="J86" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>209is!@</v>
+        <v>339is!@</v>
       </c>
       <c r="K86" t="str">
         <f t="shared" si="4"/>
@@ -35682,7 +35686,7 @@
       </c>
       <c r="J87" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>385jc!@</v>
+        <v>421jc!@</v>
       </c>
       <c r="K87" t="str">
         <f t="shared" si="4"/>
@@ -35722,7 +35726,7 @@
       </c>
       <c r="J88" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>950jf!@</v>
+        <v>298jf!@</v>
       </c>
       <c r="K88" t="str">
         <f t="shared" si="4"/>
@@ -35764,7 +35768,7 @@
       </c>
       <c r="J89" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>930js!@</v>
+        <v>750js!@</v>
       </c>
       <c r="K89" t="str">
         <f t="shared" si="4"/>
@@ -35806,7 +35810,7 @@
       </c>
       <c r="J90" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>866js!@</v>
+        <v>407js!@</v>
       </c>
       <c r="K90" t="str">
         <f t="shared" si="4"/>
@@ -35848,7 +35852,7 @@
       </c>
       <c r="J91" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>156jp!@</v>
+        <v>768jp!@</v>
       </c>
       <c r="K91" t="str">
         <f t="shared" si="4"/>
@@ -35890,7 +35894,7 @@
       </c>
       <c r="J92" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>724jp!@</v>
+        <v>026jp!@</v>
       </c>
       <c r="K92" t="str">
         <f t="shared" si="4"/>
@@ -35932,7 +35936,7 @@
       </c>
       <c r="J93" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>335jm!@</v>
+        <v>851jm!@</v>
       </c>
       <c r="K93" t="str">
         <f t="shared" si="4"/>
@@ -35974,7 +35978,7 @@
       </c>
       <c r="J94" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>177jm!@</v>
+        <v>772jm!@</v>
       </c>
       <c r="K94" t="str">
         <f t="shared" si="4"/>
@@ -36016,7 +36020,7 @@
       </c>
       <c r="J95" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>266js!@</v>
+        <v>199js!@</v>
       </c>
       <c r="K95" t="str">
         <f t="shared" si="4"/>
@@ -36058,7 +36062,7 @@
       </c>
       <c r="J96" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>560js!@</v>
+        <v>984js!@</v>
       </c>
       <c r="K96" t="str">
         <f t="shared" si="4"/>
@@ -36100,7 +36104,7 @@
       </c>
       <c r="J97" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>269ls!@</v>
+        <v>752ls!@</v>
       </c>
       <c r="K97" t="str">
         <f t="shared" si="4"/>
@@ -36142,7 +36146,7 @@
       </c>
       <c r="J98" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>785ms!@</v>
+        <v>962ms!@</v>
       </c>
       <c r="K98" t="str">
         <f t="shared" si="4"/>
@@ -36182,7 +36186,7 @@
       </c>
       <c r="J99" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>528mn!@</v>
+        <v>622mn!@</v>
       </c>
       <c r="K99" t="str">
         <f t="shared" si="4"/>
@@ -36222,7 +36226,7 @@
       </c>
       <c r="J100" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>497ms!@</v>
+        <v>385ms!@</v>
       </c>
       <c r="K100" t="str">
         <f t="shared" si="4"/>
@@ -36264,7 +36268,7 @@
       </c>
       <c r="J101" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>891mc!@</v>
+        <v>747mc!@</v>
       </c>
       <c r="K101" t="str">
         <f t="shared" si="4"/>
@@ -36306,7 +36310,7 @@
       </c>
       <c r="J102" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>761nn!@</v>
+        <v>755nn!@</v>
       </c>
       <c r="K102" t="str">
         <f t="shared" si="4"/>
@@ -36348,7 +36352,7 @@
       </c>
       <c r="J103" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>747pc!@</v>
+        <v>532pc!@</v>
       </c>
       <c r="K103" t="str">
         <f t="shared" si="4"/>
@@ -36390,7 +36394,7 @@
       </c>
       <c r="J104" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>488rs!@</v>
+        <v>781rs!@</v>
       </c>
       <c r="K104" t="str">
         <f t="shared" si="4"/>
@@ -36430,7 +36434,7 @@
       </c>
       <c r="J105" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>672rc!@</v>
+        <v>272rc!@</v>
       </c>
       <c r="K105" t="str">
         <f t="shared" si="4"/>
@@ -36472,7 +36476,7 @@
       </c>
       <c r="J106" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>645rs!@</v>
+        <v>691rs!@</v>
       </c>
       <c r="K106" t="str">
         <f t="shared" si="4"/>
@@ -36514,7 +36518,7 @@
       </c>
       <c r="J107" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>146ss!@</v>
+        <v>184ss!@</v>
       </c>
       <c r="K107" t="str">
         <f t="shared" si="4"/>
@@ -36556,7 +36560,7 @@
       </c>
       <c r="J108" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>421sa!@</v>
+        <v>980sa!@</v>
       </c>
       <c r="K108" t="str">
         <f t="shared" si="4"/>
@@ -36596,7 +36600,7 @@
       </c>
       <c r="J109" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>514tr!@</v>
+        <v>338tr!@</v>
       </c>
       <c r="K109" t="str">
         <f t="shared" si="4"/>
@@ -36636,7 +36640,7 @@
       </c>
       <c r="J110" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>871vs!@</v>
+        <v>060vs!@</v>
       </c>
       <c r="K110" t="str">
         <f t="shared" si="4"/>
@@ -36650,7 +36654,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
         <v>206</v>
       </c>
@@ -36678,7 +36682,7 @@
       </c>
       <c r="J111" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>942wc!@</v>
+        <v>605wc!@</v>
       </c>
       <c r="K111" t="str">
         <f t="shared" si="4"/>
@@ -36720,7 +36724,7 @@
       </c>
       <c r="J112" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>392ac!@</v>
+        <v>849ac!@</v>
       </c>
       <c r="K112" t="str">
         <f t="shared" si="4"/>
@@ -36762,7 +36766,7 @@
       </c>
       <c r="J113" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>252ms!@</v>
+        <v>940ms!@</v>
       </c>
       <c r="K113" t="str">
         <f t="shared" si="4"/>
@@ -36798,7 +36802,7 @@
       </c>
       <c r="J114" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>585tt!@</v>
+        <v>499tt!@</v>
       </c>
       <c r="K114" t="str">
         <f t="shared" si="4"/>
@@ -36838,7 +36842,7 @@
       </c>
       <c r="J115" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>288ls!@</v>
+        <v>364ls!@</v>
       </c>
       <c r="K115" t="str">
         <f t="shared" si="4"/>
@@ -36914,7 +36918,7 @@
       </c>
       <c r="J117" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>637aa!@</v>
+        <v>678aa!@</v>
       </c>
       <c r="K117" t="str">
         <f t="shared" si="4"/>
@@ -36956,7 +36960,7 @@
       </c>
       <c r="J118" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>649ap!@</v>
+        <v>835ap!@</v>
       </c>
       <c r="K118" t="str">
         <f t="shared" si="4"/>
@@ -36998,7 +37002,7 @@
       </c>
       <c r="J119" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>389ao!@</v>
+        <v>710ao!@</v>
       </c>
       <c r="K119" t="str">
         <f t="shared" si="4"/>
@@ -37044,7 +37048,7 @@
       </c>
       <c r="J120" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>568ae!@</v>
+        <v>399ae!@</v>
       </c>
       <c r="K120" t="str">
         <f t="shared" si="4"/>
@@ -37086,7 +37090,7 @@
       </c>
       <c r="J121" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>843an!@</v>
+        <v>289an!@</v>
       </c>
       <c r="K121" t="str">
         <f t="shared" si="4"/>
@@ -37132,7 +37136,7 @@
       </c>
       <c r="J122" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>071as!@</v>
+        <v>746as!@</v>
       </c>
       <c r="K122" t="str">
         <f t="shared" si="4"/>
@@ -37174,7 +37178,7 @@
       </c>
       <c r="J123" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>869aa!@</v>
+        <v>155aa!@</v>
       </c>
       <c r="K123" t="str">
         <f t="shared" si="4"/>
@@ -37216,7 +37220,7 @@
       </c>
       <c r="J124" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>318aj!@</v>
+        <v>422aj!@</v>
       </c>
       <c r="K124" t="str">
         <f t="shared" si="4"/>
@@ -37258,7 +37262,7 @@
       </c>
       <c r="J125" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>338bs!@</v>
+        <v>925bs!@</v>
       </c>
       <c r="K125" t="str">
         <f t="shared" si="4"/>
@@ -37300,7 +37304,7 @@
       </c>
       <c r="J126" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>385bl!@</v>
+        <v>224bl!@</v>
       </c>
       <c r="K126" t="str">
         <f t="shared" si="4"/>
@@ -37342,7 +37346,7 @@
       </c>
       <c r="J127" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>059cm!@</v>
+        <v>932cm!@</v>
       </c>
       <c r="K127" t="str">
         <f t="shared" si="4"/>
@@ -37384,7 +37388,7 @@
       </c>
       <c r="J128" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>862dc!@</v>
+        <v>448dc!@</v>
       </c>
       <c r="K128" t="str">
         <f t="shared" si="4"/>
@@ -37426,7 +37430,7 @@
       </c>
       <c r="J129" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>126jm!@</v>
+        <v>550jm!@</v>
       </c>
       <c r="K129" t="str">
         <f t="shared" si="4"/>
@@ -37468,7 +37472,7 @@
       </c>
       <c r="J130" t="str">
         <f t="shared" ref="J130:J154" ca="1" si="6">TEXT(RANDBETWEEN(1,999),"000") &amp; LEFT(H130,1) &amp; MID(H130,FIND(".",H130,1)+1,1) &amp; "!@"</f>
-        <v>587ef!@</v>
+        <v>880ef!@</v>
       </c>
       <c r="K130" t="str">
         <f t="shared" ref="K130:K154" si="7">"Update QuestRH_Pessoas set Senha = '" &amp; I130 &amp; "' Where Nome = '" &amp; A130 &amp; "';"</f>
@@ -37514,7 +37518,7 @@
       </c>
       <c r="J131" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>712el!@</v>
+        <v>655el!@</v>
       </c>
       <c r="K131" t="str">
         <f t="shared" si="7"/>
@@ -37560,7 +37564,7 @@
       </c>
       <c r="J132" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>157ia!@</v>
+        <v>464ia!@</v>
       </c>
       <c r="K132" t="str">
         <f t="shared" si="7"/>
@@ -37602,7 +37606,7 @@
       </c>
       <c r="J133" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>108ia!@</v>
+        <v>976ia!@</v>
       </c>
       <c r="K133" t="str">
         <f t="shared" si="7"/>
@@ -37644,7 +37648,7 @@
       </c>
       <c r="J134" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>496jr!@</v>
+        <v>101jr!@</v>
       </c>
       <c r="K134" t="str">
         <f t="shared" si="7"/>
@@ -37686,7 +37690,7 @@
       </c>
       <c r="J135" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>902lr!@</v>
+        <v>108lr!@</v>
       </c>
       <c r="K135" t="str">
         <f t="shared" si="7"/>
@@ -37728,7 +37732,7 @@
       </c>
       <c r="J136" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>251jf!@</v>
+        <v>728jf!@</v>
       </c>
       <c r="K136" t="str">
         <f t="shared" si="7"/>
@@ -37770,7 +37774,7 @@
       </c>
       <c r="J137" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>667lc!@</v>
+        <v>956lc!@</v>
       </c>
       <c r="K137" t="str">
         <f t="shared" si="7"/>
@@ -37812,7 +37816,7 @@
       </c>
       <c r="J138" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>298lc!@</v>
+        <v>471lc!@</v>
       </c>
       <c r="K138" t="str">
         <f t="shared" si="7"/>
@@ -37854,7 +37858,7 @@
       </c>
       <c r="J139" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>183ms!@</v>
+        <v>594ms!@</v>
       </c>
       <c r="K139" t="str">
         <f t="shared" si="7"/>
@@ -37896,7 +37900,7 @@
       </c>
       <c r="J140" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>149ip!@</v>
+        <v>417ip!@</v>
       </c>
       <c r="K140" t="str">
         <f t="shared" si="7"/>
@@ -37938,7 +37942,7 @@
       </c>
       <c r="J141" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>773mj!@</v>
+        <v>801mj!@</v>
       </c>
       <c r="K141" t="str">
         <f t="shared" si="7"/>
@@ -37980,7 +37984,7 @@
       </c>
       <c r="J142" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>230mq!@</v>
+        <v>520mq!@</v>
       </c>
       <c r="K142" t="str">
         <f t="shared" si="7"/>
@@ -38026,7 +38030,7 @@
       </c>
       <c r="J143" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>231mm!@</v>
+        <v>776mm!@</v>
       </c>
       <c r="K143" t="str">
         <f t="shared" si="7"/>
@@ -38068,7 +38072,7 @@
       </c>
       <c r="J144" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>698ms!@</v>
+        <v>381ms!@</v>
       </c>
       <c r="K144" t="str">
         <f t="shared" si="7"/>
@@ -38110,7 +38114,7 @@
       </c>
       <c r="J145" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>509ma!@</v>
+        <v>859ma!@</v>
       </c>
       <c r="K145" t="str">
         <f t="shared" si="7"/>
@@ -38156,7 +38160,7 @@
       </c>
       <c r="J146" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>238ns!@</v>
+        <v>793ns!@</v>
       </c>
       <c r="K146" t="str">
         <f t="shared" si="7"/>
@@ -38198,7 +38202,7 @@
       </c>
       <c r="J147" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>452nr!@</v>
+        <v>576nr!@</v>
       </c>
       <c r="K147" t="str">
         <f t="shared" si="7"/>
@@ -38240,7 +38244,7 @@
       </c>
       <c r="J148" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>536rp!@</v>
+        <v>596rp!@</v>
       </c>
       <c r="K148" t="str">
         <f t="shared" si="7"/>
@@ -38282,7 +38286,7 @@
       </c>
       <c r="J149" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>721ms!@</v>
+        <v>954ms!@</v>
       </c>
       <c r="K149" t="str">
         <f t="shared" si="7"/>
@@ -38324,7 +38328,7 @@
       </c>
       <c r="J150" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>233rr!@</v>
+        <v>556rr!@</v>
       </c>
       <c r="K150" t="str">
         <f t="shared" si="7"/>
@@ -38366,7 +38370,7 @@
       </c>
       <c r="J151" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>772sp!@</v>
+        <v>867sp!@</v>
       </c>
       <c r="K151" t="str">
         <f t="shared" si="7"/>
@@ -38408,7 +38412,7 @@
       </c>
       <c r="J152" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>050to!@</v>
+        <v>070to!@</v>
       </c>
       <c r="K152" t="str">
         <f t="shared" si="7"/>
@@ -38450,7 +38454,7 @@
       </c>
       <c r="J153" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>645va!@</v>
+        <v>773va!@</v>
       </c>
       <c r="K153" t="str">
         <f t="shared" si="7"/>
@@ -38464,7 +38468,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
         <v>353</v>
       </c>
@@ -38492,7 +38496,7 @@
       </c>
       <c r="J154" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>653wb!@</v>
+        <v>303wb!@</v>
       </c>
       <c r="K154" t="str">
         <f t="shared" si="7"/>
@@ -38510,7 +38514,9 @@
   <autoFilter ref="A1:N154" xr:uid="{C8A1FF41-FE38-442B-8F1A-E5C01AF500AB}">
     <filterColumn colId="0">
       <filters>
-        <filter val="Fabricio Romanini Bruschi"/>
+        <filter val="Wagner Aparecido Pedroso Candido"/>
+        <filter val="Wagner Araujo Sequeira Barreiro"/>
+        <filter val="Wagner Souza Ferreira"/>
       </filters>
     </filterColumn>
   </autoFilter>
